--- a/api/files/prices.xlsx
+++ b/api/files/prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\la_union_api_prices\api\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF53150-D0F6-44C1-BB4C-FDF2C8A9FBA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{685D5E8F-0106-477E-854D-31D4BDF4A01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="502">
   <si>
     <r>
       <rPr>
@@ -4633,16 +4633,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t>F68 / F42</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t>F43</t>
     </r>
   </si>
@@ -5014,6 +5004,39 @@
         <family val="1"/>
       </rPr>
       <t>F89</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>F41</t>
+    </r>
+  </si>
+  <si>
+    <t>F42</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>F81</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>F85</t>
     </r>
   </si>
 </sst>
@@ -5227,7 +5250,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -5309,6 +5332,15 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5342,6 +5374,51 @@
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAB20BB6-AF5B-4EF6-B432-2689822C7E67}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="131445000"/>
+          <a:ext cx="12262" cy="178676"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>690</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="12262" cy="178676"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="image10.png">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AC2DD65-C898-4242-8BA5-1CFB081C3173}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5663,15 +5740,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B900"/>
+  <dimension ref="A1:B903"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2">
         <v>110375</v>
       </c>
       <c r="B1" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5679,7 +5760,7 @@
         <v>117809</v>
       </c>
       <c r="B2" s="1">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5687,7 +5768,7 @@
         <v>110371</v>
       </c>
       <c r="B3" s="1">
-        <v>80</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5695,7 +5776,7 @@
         <v>117808</v>
       </c>
       <c r="B4" s="1">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5703,7 +5784,7 @@
         <v>110540</v>
       </c>
       <c r="B5" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5711,7 +5792,7 @@
         <v>110376</v>
       </c>
       <c r="B6" s="1">
-        <v>83</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5719,7 +5800,7 @@
         <v>110372</v>
       </c>
       <c r="B7" s="1">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5727,7 +5808,7 @@
         <v>141148</v>
       </c>
       <c r="B8" s="1">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5735,7 +5816,7 @@
         <v>141202</v>
       </c>
       <c r="B9" s="1">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5743,7 +5824,7 @@
         <v>110373</v>
       </c>
       <c r="B10" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5751,7 +5832,7 @@
         <v>117820</v>
       </c>
       <c r="B11" s="1">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5759,7 +5840,7 @@
         <v>110529</v>
       </c>
       <c r="B12" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5767,7 +5848,7 @@
         <v>117822</v>
       </c>
       <c r="B13" s="1">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5775,7 +5856,7 @@
         <v>110325</v>
       </c>
       <c r="B14" s="1">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5783,7 +5864,7 @@
         <v>110374</v>
       </c>
       <c r="B15" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
     </row>
     <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5791,7 +5872,7 @@
         <v>107830</v>
       </c>
       <c r="B16" s="1">
-        <v>99</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5799,7 +5880,7 @@
         <v>117830</v>
       </c>
       <c r="B17" s="1">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5807,7 +5888,7 @@
         <v>117833</v>
       </c>
       <c r="B18" s="1">
-        <v>89</v>
+        <v>93</v>
       </c>
     </row>
     <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5815,7 +5896,7 @@
         <v>141048</v>
       </c>
       <c r="B19" s="1">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5823,7 +5904,7 @@
         <v>108794</v>
       </c>
       <c r="B20" s="1">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5831,7 +5912,7 @@
         <v>111463</v>
       </c>
       <c r="B21" s="1">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5839,7 +5920,7 @@
         <v>141823</v>
       </c>
       <c r="B22" s="1">
-        <v>108</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5847,7 +5928,7 @@
         <v>111466</v>
       </c>
       <c r="B23" s="1">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5855,7 +5936,7 @@
         <v>106855</v>
       </c>
       <c r="B24" s="1">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5863,7 +5944,7 @@
         <v>118330</v>
       </c>
       <c r="B25" s="1">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5871,7 +5952,7 @@
         <v>108711</v>
       </c>
       <c r="B26" s="1">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5879,7 +5960,7 @@
         <v>111462</v>
       </c>
       <c r="B27" s="1">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5887,7 +5968,7 @@
         <v>117831</v>
       </c>
       <c r="B28" s="1">
-        <v>96</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5895,7 +5976,7 @@
         <v>107236</v>
       </c>
       <c r="B29" s="1">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5903,7 +5984,7 @@
         <v>117821</v>
       </c>
       <c r="B30" s="1">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5911,7 +5992,7 @@
         <v>110787</v>
       </c>
       <c r="B31" s="1">
-        <v>125</v>
+        <v>131</v>
       </c>
     </row>
     <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5919,7 +6000,7 @@
         <v>111469</v>
       </c>
       <c r="B32" s="1">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5927,7 +6008,7 @@
         <v>118140</v>
       </c>
       <c r="B33" s="1">
-        <v>130</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5935,7 +6016,7 @@
         <v>111468</v>
       </c>
       <c r="B34" s="1">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5943,7 +6024,7 @@
         <v>105333</v>
       </c>
       <c r="B35" s="1">
-        <v>188</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5951,7 +6032,7 @@
         <v>117787</v>
       </c>
       <c r="B36" s="1">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5959,7 +6040,7 @@
         <v>111743</v>
       </c>
       <c r="B37" s="1">
-        <v>163</v>
+        <v>171</v>
       </c>
     </row>
     <row r="38" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5967,7 +6048,7 @@
         <v>141271</v>
       </c>
       <c r="B38" s="1">
-        <v>153</v>
+        <v>161</v>
       </c>
     </row>
     <row r="39" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5975,7 +6056,7 @@
         <v>111172</v>
       </c>
       <c r="B39" s="1">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="40" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5983,7 +6064,7 @@
         <v>108795</v>
       </c>
       <c r="B40" s="1">
-        <v>136</v>
+        <v>143</v>
       </c>
     </row>
     <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5991,7 +6072,7 @@
         <v>111418</v>
       </c>
       <c r="B41" s="1">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5999,7 +6080,7 @@
         <v>117785</v>
       </c>
       <c r="B42" s="1">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6007,7 +6088,7 @@
         <v>105894</v>
       </c>
       <c r="B43" s="1">
-        <v>172</v>
+        <v>181</v>
       </c>
     </row>
     <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6015,7 +6096,7 @@
         <v>108303</v>
       </c>
       <c r="B44" s="1">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6023,7 +6104,7 @@
         <v>107263</v>
       </c>
       <c r="B45" s="1">
-        <v>196</v>
+        <v>205</v>
       </c>
     </row>
     <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6031,7 +6112,7 @@
         <v>106698</v>
       </c>
       <c r="B46" s="1">
-        <v>226</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6039,7 +6120,7 @@
         <v>118298</v>
       </c>
       <c r="B47" s="1">
-        <v>141</v>
+        <v>148</v>
       </c>
     </row>
     <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6047,7 +6128,7 @@
         <v>118337</v>
       </c>
       <c r="B48" s="1">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6055,7 +6136,7 @@
         <v>141066</v>
       </c>
       <c r="B49" s="1">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6063,7 +6144,7 @@
         <v>110733</v>
       </c>
       <c r="B50" s="1">
-        <v>197</v>
+        <v>207</v>
       </c>
     </row>
     <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6071,15 +6152,15 @@
         <v>118338</v>
       </c>
       <c r="B51" s="1">
-        <v>204</v>
+        <v>215</v>
       </c>
     </row>
     <row r="52" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="2">
+      <c r="A52" s="9">
         <v>108701</v>
       </c>
       <c r="B52" s="3">
-        <v>215</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6087,7 +6168,7 @@
         <v>117706</v>
       </c>
       <c r="B53" s="1">
-        <v>226</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6095,7 +6176,7 @@
         <v>117862</v>
       </c>
       <c r="B54" s="1">
-        <v>151</v>
+        <v>158</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6103,7 +6184,7 @@
         <v>118094</v>
       </c>
       <c r="B55" s="1">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6111,7 +6192,7 @@
         <v>107629</v>
       </c>
       <c r="B56" s="1">
-        <v>158</v>
+        <v>166</v>
       </c>
     </row>
     <row r="57" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6119,7 +6200,7 @@
         <v>117861</v>
       </c>
       <c r="B57" s="1">
-        <v>142</v>
+        <v>149</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6127,7 +6208,7 @@
         <v>117786</v>
       </c>
       <c r="B58" s="1">
-        <v>132</v>
+        <v>139</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6135,7 +6216,7 @@
         <v>111467</v>
       </c>
       <c r="B59" s="1">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6143,7 +6224,7 @@
         <v>108583</v>
       </c>
       <c r="B60" s="1">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6151,7 +6232,7 @@
         <v>110581</v>
       </c>
       <c r="B61" s="1">
-        <v>339</v>
+        <v>356</v>
       </c>
     </row>
     <row r="62" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6159,7 +6240,7 @@
         <v>110711</v>
       </c>
       <c r="B62" s="1">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="63" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6167,7 +6248,7 @@
         <v>117935</v>
       </c>
       <c r="B63" s="1">
-        <v>231</v>
+        <v>242</v>
       </c>
     </row>
     <row r="64" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6175,7 +6256,7 @@
         <v>118381</v>
       </c>
       <c r="B64" s="1">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="65" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6183,7 +6264,7 @@
         <v>106565</v>
       </c>
       <c r="B65" s="1">
-        <v>219</v>
+        <v>230</v>
       </c>
     </row>
     <row r="66" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6191,7 +6272,7 @@
         <v>108361</v>
       </c>
       <c r="B66" s="1">
-        <v>235</v>
+        <v>247</v>
       </c>
     </row>
     <row r="67" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6199,7 +6280,7 @@
         <v>118382</v>
       </c>
       <c r="B67" s="1">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="68" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6207,7 +6288,7 @@
         <v>118286</v>
       </c>
       <c r="B68" s="1">
-        <v>247</v>
+        <v>259</v>
       </c>
     </row>
     <row r="69" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6215,7 +6296,7 @@
         <v>107495</v>
       </c>
       <c r="B69" s="1">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="70" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6223,7 +6304,7 @@
         <v>110233</v>
       </c>
       <c r="B70" s="1">
-        <v>270</v>
+        <v>284</v>
       </c>
     </row>
     <row r="71" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6231,7 +6312,7 @@
         <v>109493</v>
       </c>
       <c r="B71" s="1">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="72" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6239,7 +6320,7 @@
         <v>110580</v>
       </c>
       <c r="B72" s="1">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="73" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6247,7 +6328,7 @@
         <v>111110</v>
       </c>
       <c r="B73" s="1">
-        <v>262</v>
+        <v>275</v>
       </c>
     </row>
     <row r="74" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6255,7 +6336,7 @@
         <v>118379</v>
       </c>
       <c r="B74" s="1">
-        <v>267</v>
+        <v>280</v>
       </c>
     </row>
     <row r="75" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6263,7 +6344,7 @@
         <v>118392</v>
       </c>
       <c r="B75" s="1">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="76" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6271,7 +6352,7 @@
         <v>117948</v>
       </c>
       <c r="B76" s="1">
-        <v>267</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6279,7 +6360,7 @@
         <v>118383</v>
       </c>
       <c r="B77" s="1">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="78" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6287,7 +6368,7 @@
         <v>118376</v>
       </c>
       <c r="B78" s="1">
-        <v>275</v>
+        <v>289</v>
       </c>
     </row>
     <row r="79" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6295,7 +6376,7 @@
         <v>117859</v>
       </c>
       <c r="B79" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="80" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6303,7 +6384,7 @@
         <v>118391</v>
       </c>
       <c r="B80" s="1">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="81" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6311,7 +6392,7 @@
         <v>118621</v>
       </c>
       <c r="B81" s="1">
-        <v>289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="82" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6319,7 +6400,7 @@
         <v>118320</v>
       </c>
       <c r="B82" s="1">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6327,7 +6408,7 @@
         <v>117789</v>
       </c>
       <c r="B83" s="1">
-        <v>290</v>
+        <v>304</v>
       </c>
     </row>
     <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6335,7 +6416,7 @@
         <v>141565</v>
       </c>
       <c r="B84" s="1">
-        <v>491</v>
+        <v>515</v>
       </c>
     </row>
     <row r="85" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6343,7 +6424,7 @@
         <v>117840</v>
       </c>
       <c r="B85" s="1">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="86" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6351,7 +6432,7 @@
         <v>111442</v>
       </c>
       <c r="B86" s="1">
-        <v>143</v>
+        <v>150</v>
       </c>
     </row>
     <row r="87" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6359,7 +6440,7 @@
         <v>110745</v>
       </c>
       <c r="B87" s="1">
-        <v>140</v>
+        <v>147</v>
       </c>
     </row>
     <row r="88" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6367,7 +6448,7 @@
         <v>110751</v>
       </c>
       <c r="B88" s="1">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="89" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6375,7 +6456,7 @@
         <v>111434</v>
       </c>
       <c r="B89" s="1">
-        <v>176</v>
+        <v>185</v>
       </c>
     </row>
     <row r="90" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6383,7 +6464,7 @@
         <v>111381</v>
       </c>
       <c r="B90" s="1">
-        <v>182</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6391,7 +6472,7 @@
         <v>116241</v>
       </c>
       <c r="B91" s="1">
-        <v>280</v>
+        <v>294</v>
       </c>
     </row>
     <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6399,7 +6480,7 @@
         <v>109338</v>
       </c>
       <c r="B92" s="1">
-        <v>208</v>
+        <v>218</v>
       </c>
     </row>
     <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6407,7 +6488,7 @@
         <v>140922</v>
       </c>
       <c r="B93" s="1">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6415,7 +6496,7 @@
         <v>108022</v>
       </c>
       <c r="B94" s="1">
-        <v>189</v>
+        <v>198</v>
       </c>
     </row>
     <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6423,7 +6504,7 @@
         <v>111532</v>
       </c>
       <c r="B95" s="1">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6431,7 +6512,7 @@
         <v>111383</v>
       </c>
       <c r="B96" s="1">
-        <v>241</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6439,7 +6520,7 @@
         <v>117854</v>
       </c>
       <c r="B97" s="1">
-        <v>180</v>
+        <v>189</v>
       </c>
     </row>
     <row r="98" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6447,7 +6528,7 @@
         <v>111443</v>
       </c>
       <c r="B98" s="1">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="99" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6455,7 +6536,7 @@
         <v>117315</v>
       </c>
       <c r="B99" s="1">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6463,7 +6544,7 @@
         <v>110740</v>
       </c>
       <c r="B100" s="1">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="101" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6471,7 +6552,7 @@
         <v>110762</v>
       </c>
       <c r="B101" s="1">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="102" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6479,7 +6560,7 @@
         <v>100761</v>
       </c>
       <c r="B102" s="1">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6487,7 +6568,7 @@
         <v>111435</v>
       </c>
       <c r="B103" s="1">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6495,7 +6576,7 @@
         <v>117841</v>
       </c>
       <c r="B104" s="1">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6503,7 +6584,7 @@
         <v>110743</v>
       </c>
       <c r="B105" s="1">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6511,7 +6592,7 @@
         <v>117838</v>
       </c>
       <c r="B106" s="1">
-        <v>192</v>
+        <v>201</v>
       </c>
     </row>
     <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6519,7 +6600,7 @@
         <v>111433</v>
       </c>
       <c r="B107" s="1">
-        <v>229</v>
+        <v>241</v>
       </c>
     </row>
     <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6527,7 +6608,7 @@
         <v>111430</v>
       </c>
       <c r="B108" s="1">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6535,7 +6616,7 @@
         <v>117834</v>
       </c>
       <c r="B109" s="1">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6543,15 +6624,15 @@
         <v>117289</v>
       </c>
       <c r="B110" s="1">
-        <v>274</v>
+        <v>288</v>
       </c>
     </row>
     <row r="111" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="2">
+      <c r="A111" s="9">
         <v>116527</v>
       </c>
       <c r="B111" s="3">
-        <v>232</v>
+        <v>244</v>
       </c>
     </row>
     <row r="112" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6559,7 +6640,7 @@
         <v>107472</v>
       </c>
       <c r="B112" s="1">
-        <v>231</v>
+        <v>243</v>
       </c>
     </row>
     <row r="113" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6567,7 +6648,7 @@
         <v>110746</v>
       </c>
       <c r="B113" s="1">
-        <v>220</v>
+        <v>231</v>
       </c>
     </row>
     <row r="114" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6575,7 +6656,7 @@
         <v>111569</v>
       </c>
       <c r="B114" s="1">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="115" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6583,7 +6664,7 @@
         <v>110742</v>
       </c>
       <c r="B115" s="1">
-        <v>225</v>
+        <v>236</v>
       </c>
     </row>
     <row r="116" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6591,7 +6672,7 @@
         <v>118306</v>
       </c>
       <c r="B116" s="1">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6599,7 +6680,7 @@
         <v>107474</v>
       </c>
       <c r="B117" s="1">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="118" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6607,7 +6688,7 @@
         <v>111602</v>
       </c>
       <c r="B118" s="1">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="119" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6615,7 +6696,7 @@
         <v>140923</v>
       </c>
       <c r="B119" s="1">
-        <v>223</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6623,7 +6704,7 @@
         <v>111530</v>
       </c>
       <c r="B120" s="1">
-        <v>243</v>
+        <v>255</v>
       </c>
     </row>
     <row r="121" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6631,7 +6712,7 @@
         <v>110752</v>
       </c>
       <c r="B121" s="1">
-        <v>281</v>
+        <v>295</v>
       </c>
     </row>
     <row r="122" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6639,7 +6720,7 @@
         <v>141318</v>
       </c>
       <c r="B122" s="1">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="123" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6647,7 +6728,7 @@
         <v>107890</v>
       </c>
       <c r="B123" s="1">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="124" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6655,7 +6736,7 @@
         <v>141047</v>
       </c>
       <c r="B124" s="1">
-        <v>227</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6663,7 +6744,7 @@
         <v>111439</v>
       </c>
       <c r="B125" s="1">
-        <v>229</v>
+        <v>240</v>
       </c>
     </row>
     <row r="126" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6671,7 +6752,7 @@
         <v>110756</v>
       </c>
       <c r="B126" s="1">
-        <v>314</v>
+        <v>330</v>
       </c>
     </row>
     <row r="127" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6679,7 +6760,7 @@
         <v>107886</v>
       </c>
       <c r="B127" s="1">
-        <v>276</v>
+        <v>290</v>
       </c>
     </row>
     <row r="128" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6687,7 +6768,7 @@
         <v>110753</v>
       </c>
       <c r="B128" s="1">
-        <v>253</v>
+        <v>266</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6695,7 +6776,7 @@
         <v>110750</v>
       </c>
       <c r="B129" s="1">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6703,7 +6784,7 @@
         <v>111879</v>
       </c>
       <c r="B130" s="1">
-        <v>254</v>
+        <v>267</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6711,7 +6792,7 @@
         <v>111437</v>
       </c>
       <c r="B131" s="1">
-        <v>228</v>
+        <v>239</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6719,7 +6800,7 @@
         <v>110749</v>
       </c>
       <c r="B132" s="1">
-        <v>218</v>
+        <v>229</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6727,7 +6808,7 @@
         <v>111447</v>
       </c>
       <c r="B133" s="1">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6735,7 +6816,7 @@
         <v>107532</v>
       </c>
       <c r="B134" s="1">
-        <v>264</v>
+        <v>277</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6743,7 +6824,7 @@
         <v>109933</v>
       </c>
       <c r="B135" s="1">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6751,7 +6832,7 @@
         <v>111655</v>
       </c>
       <c r="B136" s="1">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6759,7 +6840,7 @@
         <v>111438</v>
       </c>
       <c r="B137" s="1">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6767,7 +6848,7 @@
         <v>110747</v>
       </c>
       <c r="B138" s="1">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6775,7 +6856,7 @@
         <v>111445</v>
       </c>
       <c r="B139" s="1">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6783,7 +6864,7 @@
         <v>106955</v>
       </c>
       <c r="B140" s="1">
-        <v>382</v>
+        <v>401</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6791,7 +6872,7 @@
         <v>110313</v>
       </c>
       <c r="B141" s="1">
-        <v>250</v>
+        <v>263</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6799,7 +6880,7 @@
         <v>117853</v>
       </c>
       <c r="B142" s="1">
-        <v>238</v>
+        <v>250</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6807,7 +6888,7 @@
         <v>110339</v>
       </c>
       <c r="B143" s="1">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6815,7 +6896,7 @@
         <v>117856</v>
       </c>
       <c r="B144" s="1">
-        <v>245</v>
+        <v>258</v>
       </c>
     </row>
     <row r="145" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6823,7 +6904,7 @@
         <v>117855</v>
       </c>
       <c r="B145" s="1">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="146" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6831,7 +6912,7 @@
         <v>108772</v>
       </c>
       <c r="B146" s="1">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="147" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6839,7 +6920,7 @@
         <v>108592</v>
       </c>
       <c r="B147" s="1">
-        <v>321</v>
+        <v>337</v>
       </c>
     </row>
     <row r="148" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6847,7 +6928,7 @@
         <v>111876</v>
       </c>
       <c r="B148" s="1">
-        <v>270</v>
+        <v>283</v>
       </c>
     </row>
     <row r="149" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6855,7 +6936,7 @@
         <v>110741</v>
       </c>
       <c r="B149" s="1">
-        <v>245</v>
+        <v>257</v>
       </c>
     </row>
     <row r="150" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6863,7 +6944,7 @@
         <v>107888</v>
       </c>
       <c r="B150" s="1">
-        <v>278</v>
+        <v>292</v>
       </c>
     </row>
     <row r="151" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6871,7 +6952,7 @@
         <v>111436</v>
       </c>
       <c r="B151" s="1">
-        <v>251</v>
+        <v>263</v>
       </c>
     </row>
     <row r="152" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6879,7 +6960,7 @@
         <v>111660</v>
       </c>
       <c r="B152" s="1">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
     <row r="153" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6887,7 +6968,7 @@
         <v>111441</v>
       </c>
       <c r="B153" s="1">
-        <v>246</v>
+        <v>258</v>
       </c>
     </row>
     <row r="154" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6895,7 +6976,7 @@
         <v>118222</v>
       </c>
       <c r="B154" s="1">
-        <v>269</v>
+        <v>283</v>
       </c>
     </row>
     <row r="155" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6903,7 +6984,7 @@
         <v>110755</v>
       </c>
       <c r="B155" s="1">
-        <v>266</v>
+        <v>280</v>
       </c>
     </row>
     <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6911,7 +6992,7 @@
         <v>107109</v>
       </c>
       <c r="B156" s="1">
-        <v>365</v>
+        <v>383</v>
       </c>
     </row>
     <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6919,7 +7000,7 @@
         <v>118304</v>
       </c>
       <c r="B157" s="1">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="158" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6927,7 +7008,7 @@
         <v>110895</v>
       </c>
       <c r="B158" s="1">
-        <v>310</v>
+        <v>325</v>
       </c>
     </row>
     <row r="159" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6935,7 +7016,7 @@
         <v>111850</v>
       </c>
       <c r="B159" s="1">
-        <v>409</v>
+        <v>430</v>
       </c>
     </row>
     <row r="160" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6943,7 +7024,7 @@
         <v>108770</v>
       </c>
       <c r="B160" s="1">
-        <v>324</v>
+        <v>340</v>
       </c>
     </row>
     <row r="161" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6951,7 +7032,7 @@
         <v>107892</v>
       </c>
       <c r="B161" s="1">
-        <v>345</v>
+        <v>362</v>
       </c>
     </row>
     <row r="162" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6959,7 +7040,7 @@
         <v>111440</v>
       </c>
       <c r="B162" s="1">
-        <v>360</v>
+        <v>377</v>
       </c>
     </row>
     <row r="163" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6967,7 +7048,7 @@
         <v>111690</v>
       </c>
       <c r="B163" s="1">
-        <v>525</v>
+        <v>552</v>
       </c>
     </row>
     <row r="164" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6975,7 +7056,7 @@
         <v>107537</v>
       </c>
       <c r="B164" s="1">
-        <v>445</v>
+        <v>467</v>
       </c>
     </row>
     <row r="165" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6983,7 +7064,7 @@
         <v>109646</v>
       </c>
       <c r="B165" s="1">
-        <v>244</v>
+        <v>256</v>
       </c>
     </row>
     <row r="166" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6991,7 +7072,7 @@
         <v>109645</v>
       </c>
       <c r="B166" s="1">
-        <v>242</v>
+        <v>254</v>
       </c>
     </row>
     <row r="167" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6999,7 +7080,7 @@
         <v>109647</v>
       </c>
       <c r="B167" s="1">
-        <v>259</v>
+        <v>272</v>
       </c>
     </row>
     <row r="168" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7007,7 +7088,7 @@
         <v>105111</v>
       </c>
       <c r="B168" s="1">
-        <v>255</v>
+        <v>268</v>
       </c>
     </row>
     <row r="169" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7015,7 +7096,7 @@
         <v>111182</v>
       </c>
       <c r="B169" s="1">
-        <v>185</v>
+        <v>194</v>
       </c>
     </row>
     <row r="170" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7023,7 +7104,7 @@
         <v>109641</v>
       </c>
       <c r="B170" s="1">
-        <v>209</v>
+        <v>219</v>
       </c>
     </row>
     <row r="171" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7031,7 +7112,7 @@
         <v>105705</v>
       </c>
       <c r="B171" s="1">
-        <v>260</v>
+        <v>274</v>
       </c>
     </row>
     <row r="172" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7039,7 +7120,7 @@
         <v>109640</v>
       </c>
       <c r="B172" s="1">
-        <v>236</v>
+        <v>248</v>
       </c>
     </row>
     <row r="173" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7047,7 +7128,7 @@
         <v>111330</v>
       </c>
       <c r="B173" s="1">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="174" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7055,7 +7136,7 @@
         <v>108871</v>
       </c>
       <c r="B174" s="4">
-        <v>200</v>
+        <v>210</v>
       </c>
     </row>
     <row r="175" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7063,7 +7144,7 @@
         <v>118166</v>
       </c>
       <c r="B175" s="4">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="176" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7071,7 +7152,7 @@
         <v>118168</v>
       </c>
       <c r="B176" s="4">
-        <v>269</v>
+        <v>282</v>
       </c>
     </row>
     <row r="177" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7079,7 +7160,7 @@
         <v>118171</v>
       </c>
       <c r="B177" s="4">
-        <v>410</v>
+        <v>431</v>
       </c>
     </row>
     <row r="178" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7087,7 +7168,7 @@
         <v>118169</v>
       </c>
       <c r="B178" s="4">
-        <v>292</v>
+        <v>306</v>
       </c>
     </row>
     <row r="179" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7095,7 +7176,7 @@
         <v>111813</v>
       </c>
       <c r="B179" s="4">
-        <v>375</v>
+        <v>393</v>
       </c>
     </row>
     <row r="180" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7103,7 +7184,7 @@
         <v>118226</v>
       </c>
       <c r="B180" s="1">
-        <v>387</v>
+        <v>407</v>
       </c>
     </row>
     <row r="181" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7111,7 +7192,7 @@
         <v>118253</v>
       </c>
       <c r="B181" s="4">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="182" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7119,7 +7200,7 @@
         <v>118066</v>
       </c>
       <c r="B182" s="1">
-        <v>407</v>
+        <v>427</v>
       </c>
     </row>
     <row r="183" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7127,7 +7208,7 @@
         <v>118257</v>
       </c>
       <c r="B183" s="6">
-        <v>410</v>
+        <v>431</v>
       </c>
     </row>
     <row r="184" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7135,7 +7216,7 @@
         <v>118119</v>
       </c>
       <c r="B184" s="8">
-        <v>441</v>
+        <v>463</v>
       </c>
     </row>
     <row r="185" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7143,7 +7224,7 @@
         <v>118187</v>
       </c>
       <c r="B185" s="8">
-        <v>429</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7151,7 +7232,7 @@
         <v>118229</v>
       </c>
       <c r="B186" s="8">
-        <v>482</v>
+        <v>507</v>
       </c>
     </row>
     <row r="187" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7159,7 +7240,7 @@
         <v>118419</v>
       </c>
       <c r="B187" s="10">
-        <v>446</v>
+        <v>468</v>
       </c>
     </row>
     <row r="188" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7167,7 +7248,7 @@
         <v>118333</v>
       </c>
       <c r="B188" s="1">
-        <v>479</v>
+        <v>503</v>
       </c>
     </row>
     <row r="189" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7175,7 +7256,7 @@
         <v>118205</v>
       </c>
       <c r="B189" s="4">
-        <v>511</v>
+        <v>536</v>
       </c>
     </row>
     <row r="190" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7183,7 +7264,7 @@
         <v>118113</v>
       </c>
       <c r="B190" s="1">
-        <v>521</v>
+        <v>547</v>
       </c>
     </row>
     <row r="191" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7191,7 +7272,7 @@
         <v>118530</v>
       </c>
       <c r="B191" s="4">
-        <v>546</v>
+        <v>574</v>
       </c>
     </row>
     <row r="192" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7199,7 +7280,7 @@
         <v>118528</v>
       </c>
       <c r="B192" s="1">
-        <v>557</v>
+        <v>585</v>
       </c>
     </row>
     <row r="193" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7207,7 +7288,7 @@
         <v>118200</v>
       </c>
       <c r="B193" s="12">
-        <v>549</v>
+        <v>576</v>
       </c>
     </row>
     <row r="194" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7215,7 +7296,7 @@
         <v>107921</v>
       </c>
       <c r="B194" s="1">
-        <v>298</v>
+        <v>313</v>
       </c>
     </row>
     <row r="195" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7223,7 +7304,7 @@
         <v>118337</v>
       </c>
       <c r="B195" s="1">
-        <v>198</v>
+        <v>208</v>
       </c>
     </row>
     <row r="196" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7231,7 +7312,7 @@
         <v>108961</v>
       </c>
       <c r="B196" s="1">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="197" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7239,7 +7320,7 @@
         <v>105470</v>
       </c>
       <c r="B197" s="1">
-        <v>357</v>
+        <v>375</v>
       </c>
     </row>
     <row r="198" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7247,7 +7328,7 @@
         <v>110063</v>
       </c>
       <c r="B198" s="1">
-        <v>372</v>
+        <v>390</v>
       </c>
     </row>
     <row r="199" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7255,7 +7336,7 @@
         <v>105368</v>
       </c>
       <c r="B199" s="1">
-        <v>426</v>
+        <v>447</v>
       </c>
     </row>
     <row r="200" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7263,7 +7344,7 @@
         <v>118497</v>
       </c>
       <c r="B200" s="1">
-        <v>414</v>
+        <v>435</v>
       </c>
     </row>
     <row r="201" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7271,7 +7352,7 @@
         <v>118620</v>
       </c>
       <c r="B201" s="1">
-        <v>440</v>
+        <v>462</v>
       </c>
     </row>
     <row r="202" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7279,7 +7360,7 @@
         <v>110841</v>
       </c>
       <c r="B202" s="1">
-        <v>480</v>
+        <v>504</v>
       </c>
     </row>
     <row r="203" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7287,7 +7368,7 @@
         <v>110563</v>
       </c>
       <c r="B203" s="1">
-        <v>574</v>
+        <v>603</v>
       </c>
     </row>
     <row r="204" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7295,7 +7376,7 @@
         <v>120002</v>
       </c>
       <c r="B204" s="1">
-        <v>284</v>
+        <v>298</v>
       </c>
     </row>
     <row r="205" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7303,7 +7384,7 @@
         <v>124592</v>
       </c>
       <c r="B205" s="1">
-        <v>287</v>
+        <v>301</v>
       </c>
     </row>
     <row r="206" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7311,7 +7392,7 @@
         <v>120050</v>
       </c>
       <c r="B206" s="1">
-        <v>147</v>
+        <v>154</v>
       </c>
     </row>
     <row r="207" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7319,7 +7400,7 @@
         <v>120098</v>
       </c>
       <c r="B207" s="1">
-        <v>234</v>
+        <v>246</v>
       </c>
     </row>
     <row r="208" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7327,7 +7408,7 @@
         <v>122968</v>
       </c>
       <c r="B208" s="1">
-        <v>533</v>
+        <v>560</v>
       </c>
     </row>
     <row r="209" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7335,7 +7416,7 @@
         <v>122967</v>
       </c>
       <c r="B209" s="1">
-        <v>594</v>
+        <v>624</v>
       </c>
     </row>
     <row r="210" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7343,7 +7424,7 @@
         <v>123492</v>
       </c>
       <c r="B210" s="1">
-        <v>517</v>
+        <v>543</v>
       </c>
     </row>
     <row r="211" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7351,7 +7432,7 @@
         <v>123345</v>
       </c>
       <c r="B211" s="1">
-        <v>320</v>
+        <v>336</v>
       </c>
     </row>
     <row r="212" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7359,7 +7440,7 @@
         <v>123343</v>
       </c>
       <c r="B212" s="1">
-        <v>381</v>
+        <v>400</v>
       </c>
     </row>
     <row r="213" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7367,7 +7448,7 @@
         <v>120389</v>
       </c>
       <c r="B213" s="1">
-        <v>438</v>
+        <v>460</v>
       </c>
     </row>
     <row r="214" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7375,7 +7456,7 @@
         <v>123822</v>
       </c>
       <c r="B214" s="1">
-        <v>477</v>
+        <v>501</v>
       </c>
     </row>
     <row r="215" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7383,7 +7464,7 @@
         <v>124487</v>
       </c>
       <c r="B215" s="1">
-        <v>503</v>
+        <v>528</v>
       </c>
     </row>
     <row r="216" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7391,7 +7472,7 @@
         <v>124486</v>
       </c>
       <c r="B216" s="1">
-        <v>533</v>
+        <v>560</v>
       </c>
     </row>
     <row r="217" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7399,7 +7480,7 @@
         <v>121304</v>
       </c>
       <c r="B217" s="1">
-        <v>623</v>
+        <v>654</v>
       </c>
     </row>
     <row r="218" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7407,7 +7488,7 @@
         <v>122673</v>
       </c>
       <c r="B218" s="1">
-        <v>443</v>
+        <v>465</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7415,7 +7496,7 @@
         <v>122647</v>
       </c>
       <c r="B219" s="1">
-        <v>555</v>
+        <v>583</v>
       </c>
     </row>
     <row r="220" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7423,7 +7504,7 @@
         <v>123313</v>
       </c>
       <c r="B220" s="1">
-        <v>340</v>
+        <v>357</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7431,7 +7512,7 @@
         <v>123012</v>
       </c>
       <c r="B221" s="1">
-        <v>515</v>
+        <v>541</v>
       </c>
     </row>
     <row r="222" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7439,7 +7520,7 @@
         <v>122671</v>
       </c>
       <c r="B222" s="1">
-        <v>572</v>
+        <v>601</v>
       </c>
     </row>
     <row r="223" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7447,7 +7528,7 @@
         <v>122962</v>
       </c>
       <c r="B223" s="1">
-        <v>594</v>
+        <v>624</v>
       </c>
     </row>
     <row r="224" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7455,7 +7536,7 @@
         <v>120285</v>
       </c>
       <c r="B224" s="1">
-        <v>560</v>
+        <v>588</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7463,7 +7544,7 @@
         <v>121307</v>
       </c>
       <c r="B225" s="1">
-        <v>685</v>
+        <v>719</v>
       </c>
     </row>
     <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7471,7 +7552,7 @@
         <v>123284</v>
       </c>
       <c r="B226" s="1">
-        <v>442</v>
+        <v>464</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7479,7 +7560,7 @@
         <v>120028</v>
       </c>
       <c r="B227" s="1">
-        <v>509</v>
+        <v>534</v>
       </c>
     </row>
     <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7487,7 +7568,7 @@
         <v>120008</v>
       </c>
       <c r="B228" s="1">
-        <v>725</v>
+        <v>761</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7495,7 +7576,7 @@
         <v>123153</v>
       </c>
       <c r="B229" s="1">
-        <v>503</v>
+        <v>528</v>
       </c>
     </row>
     <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7503,7 +7584,7 @@
         <v>124624</v>
       </c>
       <c r="B230" s="1">
-        <v>323</v>
+        <v>339</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7511,7 +7592,7 @@
         <v>124594</v>
       </c>
       <c r="B231" s="1">
-        <v>385</v>
+        <v>404</v>
       </c>
     </row>
     <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7519,7 +7600,7 @@
         <v>123084</v>
       </c>
       <c r="B232" s="1">
-        <v>600</v>
+        <v>630</v>
       </c>
     </row>
     <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7527,7 +7608,7 @@
         <v>124247</v>
       </c>
       <c r="B233" s="1">
-        <v>517</v>
+        <v>543</v>
       </c>
     </row>
     <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7535,7 +7616,7 @@
         <v>120339</v>
       </c>
       <c r="B234" s="1">
-        <v>471</v>
+        <v>495</v>
       </c>
     </row>
     <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7543,7 +7624,7 @@
         <v>124248</v>
       </c>
       <c r="B235" s="1">
-        <v>571</v>
+        <v>600</v>
       </c>
     </row>
     <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7551,7 +7632,7 @@
         <v>124548</v>
       </c>
       <c r="B236" s="1">
-        <v>514</v>
+        <v>540</v>
       </c>
     </row>
     <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7559,7 +7640,7 @@
         <v>123445</v>
       </c>
       <c r="B237" s="1">
-        <v>742</v>
+        <v>779</v>
       </c>
     </row>
     <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7567,7 +7648,7 @@
         <v>124246</v>
       </c>
       <c r="B238" s="1">
-        <v>916</v>
+        <v>962</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7575,7 +7656,7 @@
         <v>122188</v>
       </c>
       <c r="B239" s="1">
-        <v>666</v>
+        <v>699</v>
       </c>
     </row>
     <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7583,7 +7664,7 @@
         <v>122195</v>
       </c>
       <c r="B240" s="1">
-        <v>741</v>
+        <v>778</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7591,7 +7672,7 @@
         <v>122983</v>
       </c>
       <c r="B241" s="1">
-        <v>561</v>
+        <v>589</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7599,7 +7680,7 @@
         <v>122984</v>
       </c>
       <c r="B242" s="1">
-        <v>620</v>
+        <v>651</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7607,7 +7688,7 @@
         <v>123862</v>
       </c>
       <c r="B243" s="1">
-        <v>888</v>
+        <v>932</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7615,7 +7696,7 @@
         <v>122650</v>
       </c>
       <c r="B244" s="1">
-        <v>922</v>
+        <v>968</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7623,7 +7704,7 @@
         <v>124433</v>
       </c>
       <c r="B245" s="1">
-        <v>879</v>
+        <v>923</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7631,7 +7712,7 @@
         <v>120995</v>
       </c>
       <c r="B246" s="1">
-        <v>741</v>
+        <v>778</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7639,7 +7720,7 @@
         <v>123222</v>
       </c>
       <c r="B247" s="1">
-        <v>915</v>
+        <v>961</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7647,7 +7728,7 @@
         <v>120240</v>
       </c>
       <c r="B248" s="1">
-        <v>465</v>
+        <v>488</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7655,7 +7736,7 @@
         <v>123833</v>
       </c>
       <c r="B249" s="1">
-        <v>535</v>
+        <v>562</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7663,7 +7744,7 @@
         <v>124477</v>
       </c>
       <c r="B250" s="1">
-        <v>256</v>
+        <v>269</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7671,7 +7752,7 @@
         <v>123344</v>
       </c>
       <c r="B251" s="1">
-        <v>233</v>
+        <v>245</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7679,7 +7760,7 @@
         <v>124475</v>
       </c>
       <c r="B252" s="1">
-        <v>392</v>
+        <v>412</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7687,7 +7768,7 @@
         <v>121760</v>
       </c>
       <c r="B253" s="1">
-        <v>373</v>
+        <v>392</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7695,7 +7776,7 @@
         <v>124476</v>
       </c>
       <c r="B254" s="1">
-        <v>469</v>
+        <v>492</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7703,7 +7784,7 @@
         <v>124370</v>
       </c>
       <c r="B255" s="1">
-        <v>456</v>
+        <v>479</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7711,7 +7792,7 @@
         <v>121651</v>
       </c>
       <c r="B256" s="1">
-        <v>409</v>
+        <v>429</v>
       </c>
     </row>
     <row r="257" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7719,7 +7800,7 @@
         <v>124371</v>
       </c>
       <c r="B257" s="1">
-        <v>502</v>
+        <v>527</v>
       </c>
     </row>
     <row r="258" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7727,7 +7808,7 @@
         <v>122703</v>
       </c>
       <c r="B258" s="1">
-        <v>456</v>
+        <v>479</v>
       </c>
     </row>
     <row r="259" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7735,7 +7816,7 @@
         <v>123560</v>
       </c>
       <c r="B259" s="1">
-        <v>428</v>
+        <v>449</v>
       </c>
     </row>
     <row r="260" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7743,7 +7824,7 @@
         <v>123561</v>
       </c>
       <c r="B260" s="1">
-        <v>510</v>
+        <v>536</v>
       </c>
     </row>
     <row r="261" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7751,7 +7832,7 @@
         <v>160052</v>
       </c>
       <c r="B261" s="1">
-        <v>82</v>
+        <v>86</v>
       </c>
     </row>
     <row r="262" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7759,7 +7840,7 @@
         <v>160054</v>
       </c>
       <c r="B262" s="1">
-        <v>131</v>
+        <v>138</v>
       </c>
     </row>
     <row r="263" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7767,7 +7848,7 @@
         <v>160051</v>
       </c>
       <c r="B263" s="1">
-        <v>145</v>
+        <v>152</v>
       </c>
     </row>
     <row r="264" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7775,7 +7856,7 @@
         <v>160055</v>
       </c>
       <c r="B264" s="15">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="265" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7783,7 +7864,7 @@
         <v>0</v>
       </c>
       <c r="B265" s="17">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7791,7 +7872,7 @@
         <v>1</v>
       </c>
       <c r="B266" s="1">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7799,7 +7880,7 @@
         <v>2</v>
       </c>
       <c r="B267" s="1">
-        <v>257</v>
+        <v>263</v>
       </c>
     </row>
     <row r="268" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7807,7 +7888,7 @@
         <v>3</v>
       </c>
       <c r="B268" s="1">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="269" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7815,7 +7896,7 @@
         <v>4</v>
       </c>
       <c r="B269" s="1">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="270" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7823,7 +7904,7 @@
         <v>5</v>
       </c>
       <c r="B270" s="1">
-        <v>282</v>
+        <v>287</v>
       </c>
     </row>
     <row r="271" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7831,7 +7912,7 @@
         <v>6</v>
       </c>
       <c r="B271" s="1">
-        <v>273</v>
+        <v>279</v>
       </c>
     </row>
     <row r="272" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7847,7 +7928,7 @@
         <v>8</v>
       </c>
       <c r="B273" s="1">
-        <v>395</v>
+        <v>405</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7855,7 +7936,7 @@
         <v>9</v>
       </c>
       <c r="B274" s="1">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7863,7 +7944,7 @@
         <v>10</v>
       </c>
       <c r="B275" s="1">
-        <v>301</v>
+        <v>308</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7871,7 +7952,7 @@
         <v>11</v>
       </c>
       <c r="B276" s="1">
-        <v>317</v>
+        <v>325</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7879,15 +7960,15 @@
         <v>12</v>
       </c>
       <c r="B277" s="1">
-        <v>314</v>
+        <v>322</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="20" t="s">
+      <c r="A278" s="28" t="s">
         <v>13</v>
       </c>
       <c r="B278" s="3">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7895,7 +7976,7 @@
         <v>14</v>
       </c>
       <c r="B279" s="1">
-        <v>661</v>
+        <v>678</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7903,7 +7984,7 @@
         <v>15</v>
       </c>
       <c r="B280" s="1">
-        <v>355</v>
+        <v>361</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7911,7 +7992,7 @@
         <v>16</v>
       </c>
       <c r="B281" s="1">
-        <v>348</v>
+        <v>357</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7919,7 +8000,7 @@
         <v>17</v>
       </c>
       <c r="B282" s="1">
-        <v>383</v>
+        <v>391</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7927,7 +8008,7 @@
         <v>18</v>
       </c>
       <c r="B283" s="1">
-        <v>405</v>
+        <v>413</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7935,7 +8016,7 @@
         <v>19</v>
       </c>
       <c r="B284" s="1">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7943,7 +8024,7 @@
         <v>20</v>
       </c>
       <c r="B285" s="19">
-        <v>6369</v>
+        <v>6464</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7951,7 +8032,7 @@
         <v>21</v>
       </c>
       <c r="B286" s="1">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7959,7 +8040,7 @@
         <v>22</v>
       </c>
       <c r="B287" s="1">
-        <v>213</v>
+        <v>219</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7967,7 +8048,7 @@
         <v>23</v>
       </c>
       <c r="B288" s="1">
-        <v>247</v>
+        <v>253</v>
       </c>
     </row>
     <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7975,7 +8056,7 @@
         <v>24</v>
       </c>
       <c r="B289" s="1">
-        <v>181</v>
+        <v>185</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7983,7 +8064,7 @@
         <v>25</v>
       </c>
       <c r="B290" s="1">
-        <v>223</v>
+        <v>229</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7991,7 +8072,7 @@
         <v>26</v>
       </c>
       <c r="B291" s="1">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7999,7 +8080,7 @@
         <v>27</v>
       </c>
       <c r="B292" s="1">
-        <v>219</v>
+        <v>226</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8007,7 +8088,7 @@
         <v>28</v>
       </c>
       <c r="B293" s="1">
-        <v>218</v>
+        <v>226</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8015,7 +8096,7 @@
         <v>29</v>
       </c>
       <c r="B294" s="1">
-        <v>254</v>
+        <v>261</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8023,7 +8104,7 @@
         <v>30</v>
       </c>
       <c r="B295" s="1">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8031,7 +8112,7 @@
         <v>31</v>
       </c>
       <c r="B296" s="1">
-        <v>267</v>
+        <v>274</v>
       </c>
     </row>
     <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8039,7 +8120,7 @@
         <v>32</v>
       </c>
       <c r="B297" s="1">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8047,7 +8128,7 @@
         <v>33</v>
       </c>
       <c r="B298" s="1">
-        <v>273</v>
+        <v>280</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8055,7 +8136,7 @@
         <v>34</v>
       </c>
       <c r="B299" s="19">
-        <v>1696</v>
+        <v>1738</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8063,7 +8144,7 @@
         <v>35</v>
       </c>
       <c r="B300" s="1">
-        <v>396</v>
+        <v>404</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8071,7 +8152,7 @@
         <v>36</v>
       </c>
       <c r="B301" s="1">
-        <v>652</v>
+        <v>662</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8079,7 +8160,7 @@
         <v>37</v>
       </c>
       <c r="B302" s="1">
-        <v>429</v>
+        <v>438</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8087,7 +8168,7 @@
         <v>38</v>
       </c>
       <c r="B303" s="1">
-        <v>453</v>
+        <v>465</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8095,7 +8176,7 @@
         <v>39</v>
       </c>
       <c r="B304" s="1">
-        <v>412</v>
+        <v>420</v>
       </c>
     </row>
     <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8103,7 +8184,7 @@
         <v>40</v>
       </c>
       <c r="B305" s="1">
-        <v>369</v>
+        <v>377</v>
       </c>
     </row>
     <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8111,7 +8192,7 @@
         <v>41</v>
       </c>
       <c r="B306" s="1">
-        <v>375</v>
+        <v>382</v>
       </c>
     </row>
     <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8119,7 +8200,7 @@
         <v>42</v>
       </c>
       <c r="B307" s="1">
-        <v>354</v>
+        <v>361</v>
       </c>
     </row>
     <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8127,7 +8208,7 @@
         <v>43</v>
       </c>
       <c r="B308" s="1">
-        <v>427</v>
+        <v>440</v>
       </c>
     </row>
     <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8135,7 +8216,7 @@
         <v>44</v>
       </c>
       <c r="B309" s="1">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8143,7 +8224,7 @@
         <v>45</v>
       </c>
       <c r="B310" s="1">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8151,7 +8232,7 @@
         <v>46</v>
       </c>
       <c r="B311" s="1">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8159,7 +8240,7 @@
         <v>47</v>
       </c>
       <c r="B312" s="1">
-        <v>630</v>
+        <v>640</v>
       </c>
     </row>
     <row r="313" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8167,7 +8248,7 @@
         <v>48</v>
       </c>
       <c r="B313" s="1">
-        <v>589</v>
+        <v>598</v>
       </c>
     </row>
     <row r="314" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8175,7 +8256,7 @@
         <v>49</v>
       </c>
       <c r="B314" s="1">
-        <v>509</v>
+        <v>519</v>
       </c>
     </row>
     <row r="315" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8183,7 +8264,7 @@
         <v>50</v>
       </c>
       <c r="B315" s="1">
-        <v>552</v>
+        <v>566</v>
       </c>
     </row>
     <row r="316" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8191,7 +8272,7 @@
         <v>51</v>
       </c>
       <c r="B316" s="1">
-        <v>619</v>
+        <v>634</v>
       </c>
     </row>
     <row r="317" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8199,7 +8280,7 @@
         <v>52</v>
       </c>
       <c r="B317" s="1">
-        <v>622</v>
+        <v>635</v>
       </c>
     </row>
     <row r="318" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8207,7 +8288,7 @@
         <v>53</v>
       </c>
       <c r="B318" s="1">
-        <v>606</v>
+        <v>621</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8215,7 +8296,7 @@
         <v>54</v>
       </c>
       <c r="B319" s="1">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="320" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8223,7 +8304,7 @@
         <v>55</v>
       </c>
       <c r="B320" s="1">
-        <v>427</v>
+        <v>438</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8231,7 +8312,7 @@
         <v>56</v>
       </c>
       <c r="B321" s="1">
-        <v>376</v>
+        <v>384</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8239,7 +8320,7 @@
         <v>57</v>
       </c>
       <c r="B322" s="1">
-        <v>395</v>
+        <v>403</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8247,7 +8328,7 @@
         <v>58</v>
       </c>
       <c r="B323" s="1">
-        <v>440</v>
+        <v>449</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8255,7 +8336,7 @@
         <v>59</v>
       </c>
       <c r="B324" s="1">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8263,7 +8344,7 @@
         <v>60</v>
       </c>
       <c r="B325" s="1">
-        <v>208</v>
+        <v>213</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8271,7 +8352,7 @@
         <v>61</v>
       </c>
       <c r="B326" s="1">
-        <v>257</v>
+        <v>262</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8287,7 +8368,7 @@
         <v>63</v>
       </c>
       <c r="B328" s="1">
-        <v>336</v>
+        <v>345</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8303,7 +8384,7 @@
         <v>65</v>
       </c>
       <c r="B330" s="1">
-        <v>701</v>
+        <v>718</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8311,7 +8392,7 @@
         <v>66</v>
       </c>
       <c r="B331" s="1">
-        <v>723</v>
+        <v>742</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8319,7 +8400,7 @@
         <v>67</v>
       </c>
       <c r="B332" s="1">
-        <v>669</v>
+        <v>686</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8327,7 +8408,7 @@
         <v>68</v>
       </c>
       <c r="B333" s="1">
-        <v>786</v>
+        <v>805</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8335,7 +8416,7 @@
         <v>69</v>
       </c>
       <c r="B334" s="1">
-        <v>513</v>
+        <v>526</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8343,7 +8424,7 @@
         <v>70</v>
       </c>
       <c r="B335" s="1">
-        <v>582</v>
+        <v>590</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8351,7 +8432,7 @@
         <v>71</v>
       </c>
       <c r="B336" s="1">
-        <v>793</v>
+        <v>805</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8359,15 +8440,15 @@
         <v>72</v>
       </c>
       <c r="B337" s="1">
-        <v>678</v>
+        <v>692</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="20" t="s">
+      <c r="A338" s="28" t="s">
         <v>73</v>
       </c>
       <c r="B338" s="3">
-        <v>760</v>
+        <v>779</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8391,7 +8472,7 @@
         <v>76</v>
       </c>
       <c r="B341" s="1">
-        <v>753</v>
+        <v>772</v>
       </c>
     </row>
     <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8399,7 +8480,7 @@
         <v>77</v>
       </c>
       <c r="B342" s="1">
-        <v>755</v>
+        <v>774</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8423,7 +8504,7 @@
         <v>80</v>
       </c>
       <c r="B345" s="1">
-        <v>543</v>
+        <v>557</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8431,7 +8512,7 @@
         <v>81</v>
       </c>
       <c r="B346" s="1">
-        <v>822</v>
+        <v>842</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8439,7 +8520,7 @@
         <v>82</v>
       </c>
       <c r="B347" s="1">
-        <v>592</v>
+        <v>607</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8447,7 +8528,7 @@
         <v>83</v>
       </c>
       <c r="B348" s="1">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8455,7 +8536,7 @@
         <v>84</v>
       </c>
       <c r="B349" s="1">
-        <v>649</v>
+        <v>658</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8463,7 +8544,7 @@
         <v>85</v>
       </c>
       <c r="B350" s="1">
-        <v>642</v>
+        <v>658</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8471,7 +8552,7 @@
         <v>86</v>
       </c>
       <c r="B351" s="1">
-        <v>580</v>
+        <v>594</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8479,7 +8560,7 @@
         <v>87</v>
       </c>
       <c r="B352" s="1">
-        <v>568</v>
+        <v>579</v>
       </c>
     </row>
     <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8487,7 +8568,7 @@
         <v>88</v>
       </c>
       <c r="B353" s="1">
-        <v>500</v>
+        <v>510</v>
       </c>
     </row>
     <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8495,7 +8576,7 @@
         <v>89</v>
       </c>
       <c r="B354" s="1">
-        <v>571</v>
+        <v>585</v>
       </c>
     </row>
     <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8503,7 +8584,7 @@
         <v>90</v>
       </c>
       <c r="B355" s="1">
-        <v>521</v>
+        <v>534</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8511,7 +8592,7 @@
         <v>91</v>
       </c>
       <c r="B356" s="1">
-        <v>486</v>
+        <v>498</v>
       </c>
     </row>
     <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8519,7 +8600,7 @@
         <v>92</v>
       </c>
       <c r="B357" s="1">
-        <v>441</v>
+        <v>450</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8527,7 +8608,7 @@
         <v>93</v>
       </c>
       <c r="B358" s="1">
-        <v>861</v>
+        <v>874</v>
       </c>
     </row>
     <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8535,7 +8616,7 @@
         <v>94</v>
       </c>
       <c r="B359" s="1">
-        <v>544</v>
+        <v>557</v>
       </c>
     </row>
     <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8543,7 +8624,7 @@
         <v>95</v>
       </c>
       <c r="B360" s="1">
-        <v>630</v>
+        <v>639</v>
       </c>
     </row>
     <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8551,7 +8632,7 @@
         <v>96</v>
       </c>
       <c r="B361" s="1">
-        <v>581</v>
+        <v>596</v>
       </c>
     </row>
     <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8559,7 +8640,7 @@
         <v>97</v>
       </c>
       <c r="B362" s="1">
-        <v>613</v>
+        <v>628</v>
       </c>
     </row>
     <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8567,7 +8648,7 @@
         <v>98</v>
       </c>
       <c r="B363" s="1">
-        <v>582</v>
+        <v>597</v>
       </c>
     </row>
     <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8575,7 +8656,7 @@
         <v>99</v>
       </c>
       <c r="B364" s="1">
-        <v>616</v>
+        <v>629</v>
       </c>
     </row>
     <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8583,7 +8664,7 @@
         <v>100</v>
       </c>
       <c r="B365" s="1">
-        <v>670</v>
+        <v>686</v>
       </c>
     </row>
     <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8591,7 +8672,7 @@
         <v>101</v>
       </c>
       <c r="B366" s="1">
-        <v>630</v>
+        <v>646</v>
       </c>
     </row>
     <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8599,7 +8680,7 @@
         <v>102</v>
       </c>
       <c r="B367" s="1">
-        <v>595</v>
+        <v>610</v>
       </c>
     </row>
     <row r="368" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8607,7 +8688,7 @@
         <v>103</v>
       </c>
       <c r="B368" s="1">
-        <v>650</v>
+        <v>666</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8615,7 +8696,7 @@
         <v>104</v>
       </c>
       <c r="B369" s="1">
-        <v>750</v>
+        <v>768</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8623,7 +8704,7 @@
         <v>105</v>
       </c>
       <c r="B370" s="1">
-        <v>716</v>
+        <v>734</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8631,7 +8712,7 @@
         <v>106</v>
       </c>
       <c r="B371" s="1">
-        <v>609</v>
+        <v>624</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8639,7 +8720,7 @@
         <v>107</v>
       </c>
       <c r="B372" s="1">
-        <v>625</v>
+        <v>640</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8647,7 +8728,7 @@
         <v>108</v>
       </c>
       <c r="B373" s="1">
-        <v>454</v>
+        <v>466</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8655,7 +8736,7 @@
         <v>109</v>
       </c>
       <c r="B374" s="1">
-        <v>515</v>
+        <v>527</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8663,7 +8744,7 @@
         <v>110</v>
       </c>
       <c r="B375" s="1">
-        <v>812</v>
+        <v>833</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8671,7 +8752,7 @@
         <v>111</v>
       </c>
       <c r="B376" s="1">
-        <v>766</v>
+        <v>786</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8679,7 +8760,7 @@
         <v>112</v>
       </c>
       <c r="B377" s="1">
-        <v>762</v>
+        <v>781</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8687,7 +8768,7 @@
         <v>113</v>
       </c>
       <c r="B378" s="1">
-        <v>599</v>
+        <v>614</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8695,7 +8776,7 @@
         <v>114</v>
       </c>
       <c r="B379" s="1">
-        <v>669</v>
+        <v>686</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8703,7 +8784,7 @@
         <v>115</v>
       </c>
       <c r="B380" s="19">
-        <v>3565</v>
+        <v>3654</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8711,7 +8792,7 @@
         <v>116</v>
       </c>
       <c r="B381" s="1">
-        <v>738</v>
+        <v>749</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8719,7 +8800,7 @@
         <v>117</v>
       </c>
       <c r="B382" s="1">
-        <v>944</v>
+        <v>958</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8727,7 +8808,7 @@
         <v>118</v>
       </c>
       <c r="B383" s="1">
-        <v>648</v>
+        <v>664</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8735,7 +8816,7 @@
         <v>119</v>
       </c>
       <c r="B384" s="1">
-        <v>775</v>
+        <v>794</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8743,7 +8824,7 @@
         <v>120</v>
       </c>
       <c r="B385" s="1">
-        <v>723</v>
+        <v>733</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8751,7 +8832,7 @@
         <v>121</v>
       </c>
       <c r="B386" s="1">
-        <v>662</v>
+        <v>679</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8759,7 +8840,7 @@
         <v>122</v>
       </c>
       <c r="B387" s="1">
-        <v>801</v>
+        <v>785</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8767,7 +8848,7 @@
         <v>123</v>
       </c>
       <c r="B388" s="1">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8775,7 +8856,7 @@
         <v>124</v>
       </c>
       <c r="B389" s="1">
-        <v>924</v>
+        <v>938</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8783,7 +8864,7 @@
         <v>125</v>
       </c>
       <c r="B390" s="1">
-        <v>812</v>
+        <v>828</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8791,7 +8872,7 @@
         <v>126</v>
       </c>
       <c r="B391" s="1">
-        <v>807</v>
+        <v>824</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8799,7 +8880,7 @@
         <v>127</v>
       </c>
       <c r="B392" s="19">
-        <v>1138</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8807,23 +8888,21 @@
         <v>128</v>
       </c>
       <c r="B393" s="1">
-        <v>809</v>
+        <v>826</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="B394" s="1">
-        <v>971</v>
-      </c>
+      <c r="B394" s="27"/>
     </row>
     <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="20" t="s">
         <v>130</v>
       </c>
       <c r="B395" s="19">
-        <v>1144</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8831,7 +8910,7 @@
         <v>131</v>
       </c>
       <c r="B396" s="1">
-        <v>952</v>
+        <v>976</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8839,7 +8918,7 @@
         <v>132</v>
       </c>
       <c r="B397" s="1">
-        <v>963</v>
+        <v>987</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8847,7 +8926,7 @@
         <v>133</v>
       </c>
       <c r="B398" s="19">
-        <v>1681</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8862,8 +8941,8 @@
       <c r="A400" s="20" t="s">
         <v>135</v>
       </c>
-      <c r="B400" s="1">
-        <v>988</v>
+      <c r="B400" s="19">
+        <v>1002</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8871,7 +8950,7 @@
         <v>136</v>
       </c>
       <c r="B401" s="19">
-        <v>1134</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8879,7 +8958,7 @@
         <v>137</v>
       </c>
       <c r="B402" s="1">
-        <v>916</v>
+        <v>934</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8887,15 +8966,15 @@
         <v>138</v>
       </c>
       <c r="B403" s="1">
-        <v>983</v>
+        <v>998</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="B404" s="1">
-        <v>994</v>
+      <c r="B404" s="19">
+        <v>1018</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8903,7 +8982,7 @@
         <v>140</v>
       </c>
       <c r="B405" s="19">
-        <v>1385</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8911,7 +8990,7 @@
         <v>141</v>
       </c>
       <c r="B406" s="19">
-        <v>1310</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8919,7 +8998,7 @@
         <v>142</v>
       </c>
       <c r="B407" s="19">
-        <v>1307</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8927,7 +9006,7 @@
         <v>143</v>
       </c>
       <c r="B408" s="1">
-        <v>865</v>
+        <v>886</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8935,7 +9014,7 @@
         <v>144</v>
       </c>
       <c r="B409" s="1">
-        <v>953</v>
+        <v>977</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8943,7 +9022,7 @@
         <v>145</v>
       </c>
       <c r="B410" s="1">
-        <v>919</v>
+        <v>951</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8951,7 +9030,7 @@
         <v>146</v>
       </c>
       <c r="B411" s="19">
-        <v>1030</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8959,7 +9038,7 @@
         <v>147</v>
       </c>
       <c r="B412" s="19">
-        <v>1017</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8967,7 +9046,7 @@
         <v>148</v>
       </c>
       <c r="B413" s="19">
-        <v>1427</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8975,7 +9054,7 @@
         <v>149</v>
       </c>
       <c r="B414" s="19">
-        <v>1388</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8983,7 +9062,7 @@
         <v>150</v>
       </c>
       <c r="B415" s="19">
-        <v>1334</v>
+        <v>1368</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8991,7 +9070,7 @@
         <v>151</v>
       </c>
       <c r="B416" s="1">
-        <v>919</v>
+        <v>937</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8999,7 +9078,7 @@
         <v>152</v>
       </c>
       <c r="B417" s="1">
-        <v>951</v>
+        <v>970</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9007,7 +9086,7 @@
         <v>153</v>
       </c>
       <c r="B418" s="19">
-        <v>1060</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9015,7 +9094,7 @@
         <v>154</v>
       </c>
       <c r="B419" s="1">
-        <v>938</v>
+        <v>971</v>
       </c>
     </row>
     <row r="420" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9023,7 +9102,7 @@
         <v>155</v>
       </c>
       <c r="B420" s="19">
-        <v>1068</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="421" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9031,7 +9110,7 @@
         <v>156</v>
       </c>
       <c r="B421" s="19">
-        <v>1113</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="422" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9047,7 +9126,7 @@
         <v>158</v>
       </c>
       <c r="B423" s="19">
-        <v>1134</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="424" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9055,7 +9134,7 @@
         <v>159</v>
       </c>
       <c r="B424" s="19">
-        <v>1006</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="425" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9063,7 +9142,7 @@
         <v>160</v>
       </c>
       <c r="B425" s="1">
-        <v>855</v>
+        <v>877</v>
       </c>
     </row>
     <row r="426" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9071,7 +9150,7 @@
         <v>161</v>
       </c>
       <c r="B426" s="1">
-        <v>794</v>
+        <v>814</v>
       </c>
     </row>
     <row r="427" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9079,7 +9158,7 @@
         <v>162</v>
       </c>
       <c r="B427" s="1">
-        <v>913</v>
+        <v>927</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9087,7 +9166,7 @@
         <v>163</v>
       </c>
       <c r="B428" s="19">
-        <v>1594</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="429" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9095,7 +9174,7 @@
         <v>164</v>
       </c>
       <c r="B429" s="19">
-        <v>1684</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9111,7 +9190,7 @@
         <v>166</v>
       </c>
       <c r="B431" s="19">
-        <v>2755</v>
+        <v>2824</v>
       </c>
     </row>
     <row r="432" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9119,7 +9198,7 @@
         <v>167</v>
       </c>
       <c r="B432" s="19">
-        <v>1907</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9127,7 +9206,7 @@
         <v>168</v>
       </c>
       <c r="B433" s="19">
-        <v>2011</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9135,7 +9214,7 @@
         <v>169</v>
       </c>
       <c r="B434" s="19">
-        <v>2001</v>
+        <v>2051</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9143,7 +9222,7 @@
         <v>170</v>
       </c>
       <c r="B435" s="19">
-        <v>1338</v>
+        <v>1365</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9151,7 +9230,7 @@
         <v>171</v>
       </c>
       <c r="B436" s="19">
-        <v>1544</v>
+        <v>1567</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9159,7 +9238,7 @@
         <v>172</v>
       </c>
       <c r="B437" s="19">
-        <v>1607</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9167,7 +9246,7 @@
         <v>173</v>
       </c>
       <c r="B438" s="19">
-        <v>1868</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9175,7 +9254,7 @@
         <v>174</v>
       </c>
       <c r="B439" s="19">
-        <v>1914</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9183,7 +9262,7 @@
         <v>175</v>
       </c>
       <c r="B440" s="19">
-        <v>1043</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9191,7 +9270,7 @@
         <v>176</v>
       </c>
       <c r="B441" s="19">
-        <v>1160</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9199,7 +9278,7 @@
         <v>177</v>
       </c>
       <c r="B442" s="19">
-        <v>1584</v>
+        <v>1623</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9207,7 +9286,7 @@
         <v>178</v>
       </c>
       <c r="B443" s="19">
-        <v>1542</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9215,7 +9294,7 @@
         <v>179</v>
       </c>
       <c r="B444" s="19">
-        <v>1676</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9223,7 +9302,7 @@
         <v>180</v>
       </c>
       <c r="B445" s="19">
-        <v>1550</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9231,7 +9310,7 @@
         <v>181</v>
       </c>
       <c r="B446" s="19">
-        <v>1543</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9239,7 +9318,7 @@
         <v>182</v>
       </c>
       <c r="B447" s="19">
-        <v>1943</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9247,7 +9326,7 @@
         <v>183</v>
       </c>
       <c r="B448" s="19">
-        <v>1552</v>
+        <v>1591</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9255,7 +9334,7 @@
         <v>184</v>
       </c>
       <c r="B449" s="19">
-        <v>1656</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9263,7 +9342,7 @@
         <v>185</v>
       </c>
       <c r="B450" s="19">
-        <v>1425</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9271,7 +9350,7 @@
         <v>186</v>
       </c>
       <c r="B451" s="19">
-        <v>1671</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9279,7 +9358,7 @@
         <v>187</v>
       </c>
       <c r="B452" s="19">
-        <v>1348</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9287,7 +9366,7 @@
         <v>188</v>
       </c>
       <c r="B453" s="19">
-        <v>1357</v>
+        <v>1391</v>
       </c>
     </row>
     <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9295,7 +9374,7 @@
         <v>189</v>
       </c>
       <c r="B454" s="19">
-        <v>1813</v>
+        <v>1849</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9303,7 +9382,7 @@
         <v>190</v>
       </c>
       <c r="B455" s="19">
-        <v>1920</v>
+        <v>1987</v>
       </c>
     </row>
     <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9311,7 +9390,7 @@
         <v>191</v>
       </c>
       <c r="B456" s="19">
-        <v>1952</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9319,7 +9398,7 @@
         <v>192</v>
       </c>
       <c r="B457" s="19">
-        <v>1369</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9327,7 +9406,7 @@
         <v>193</v>
       </c>
       <c r="B458" s="19">
-        <v>1398</v>
+        <v>1433</v>
       </c>
     </row>
     <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9335,7 +9414,7 @@
         <v>194</v>
       </c>
       <c r="B459" s="19">
-        <v>2107</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9351,7 +9430,7 @@
         <v>196</v>
       </c>
       <c r="B461" s="19">
-        <v>1711</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9359,7 +9438,7 @@
         <v>197</v>
       </c>
       <c r="B462" s="19">
-        <v>1766</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9367,7 +9446,7 @@
         <v>198</v>
       </c>
       <c r="B463" s="19">
-        <v>2246</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9375,7 +9454,7 @@
         <v>199</v>
       </c>
       <c r="B464" s="19">
-        <v>1755</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9383,7 +9462,7 @@
         <v>200</v>
       </c>
       <c r="B465" s="19">
-        <v>1809</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9391,7 +9470,7 @@
         <v>201</v>
       </c>
       <c r="B466" s="1">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9415,7 +9494,7 @@
         <v>204</v>
       </c>
       <c r="B469" s="19">
-        <v>1761</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9423,7 +9502,7 @@
         <v>205</v>
       </c>
       <c r="B470" s="19">
-        <v>1906</v>
+        <v>1954</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9431,7 +9510,7 @@
         <v>206</v>
       </c>
       <c r="B471" s="19">
-        <v>1735</v>
+        <v>1778</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9455,7 +9534,7 @@
         <v>209</v>
       </c>
       <c r="B474" s="19">
-        <v>2165</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9463,7 +9542,7 @@
         <v>210</v>
       </c>
       <c r="B475" s="19">
-        <v>2209</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9471,7 +9550,7 @@
         <v>211</v>
       </c>
       <c r="B476" s="19">
-        <v>4365</v>
+        <v>4431</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9479,7 +9558,7 @@
         <v>212</v>
       </c>
       <c r="B477" s="19">
-        <v>2154</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9487,7 +9566,7 @@
         <v>213</v>
       </c>
       <c r="B478" s="1">
-        <v>627</v>
+        <v>643</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9495,7 +9574,7 @@
         <v>214</v>
       </c>
       <c r="B479" s="19">
-        <v>1006</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9503,7 +9582,7 @@
         <v>215</v>
       </c>
       <c r="B480" s="19">
-        <v>1006</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9511,7 +9590,7 @@
         <v>216</v>
       </c>
       <c r="B481" s="19">
-        <v>1296</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9519,7 +9598,7 @@
         <v>217</v>
       </c>
       <c r="B482" s="19">
-        <v>1364</v>
+        <v>1392</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9527,7 +9606,7 @@
         <v>218</v>
       </c>
       <c r="B483" s="19">
-        <v>1385</v>
+        <v>1419</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9535,7 +9614,7 @@
         <v>219</v>
       </c>
       <c r="B484" s="19">
-        <v>1211</v>
+        <v>1241</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9543,7 +9622,7 @@
         <v>220</v>
       </c>
       <c r="B485" s="19">
-        <v>1247</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9551,7 +9630,7 @@
         <v>221</v>
       </c>
       <c r="B486" s="19">
-        <v>1288</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9559,7 +9638,7 @@
         <v>222</v>
       </c>
       <c r="B487" s="19">
-        <v>1403</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9567,7 +9646,7 @@
         <v>223</v>
       </c>
       <c r="B488" s="19">
-        <v>1309</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9575,7 +9654,7 @@
         <v>224</v>
       </c>
       <c r="B489" s="1">
-        <v>915</v>
+        <v>929</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9583,7 +9662,7 @@
         <v>225</v>
       </c>
       <c r="B490" s="19">
-        <v>1725</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9591,7 +9670,7 @@
         <v>226</v>
       </c>
       <c r="B491" s="19">
-        <v>1810</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9599,7 +9678,7 @@
         <v>227</v>
       </c>
       <c r="B492" s="19">
-        <v>1744</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -9607,7 +9686,7 @@
         <v>228</v>
       </c>
       <c r="B493" s="19">
-        <v>1713</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9615,7 +9694,7 @@
         <v>229</v>
       </c>
       <c r="B494" s="1">
-        <v>623</v>
+        <v>639</v>
       </c>
     </row>
     <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9631,7 +9710,7 @@
         <v>231</v>
       </c>
       <c r="B496" s="1">
-        <v>354</v>
+        <v>368</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9647,7 +9726,7 @@
         <v>233</v>
       </c>
       <c r="B498" s="1">
-        <v>362</v>
+        <v>369</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9655,7 +9734,7 @@
         <v>234</v>
       </c>
       <c r="B499" s="19">
-        <v>1224</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9663,7 +9742,7 @@
         <v>235</v>
       </c>
       <c r="B500" s="19">
-        <v>1486</v>
+        <v>1523</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9671,7 +9750,7 @@
         <v>236</v>
       </c>
       <c r="B501" s="19">
-        <v>1442</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9679,7 +9758,7 @@
         <v>237</v>
       </c>
       <c r="B502" s="19">
-        <v>1452</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9687,7 +9766,7 @@
         <v>238</v>
       </c>
       <c r="B503" s="19">
-        <v>1575</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9695,7 +9774,7 @@
         <v>239</v>
       </c>
       <c r="B504" s="19">
-        <v>1575</v>
+        <v>1614</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9703,7 +9782,7 @@
         <v>240</v>
       </c>
       <c r="B505" s="1">
-        <v>95</v>
+        <v>98</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9711,7 +9790,7 @@
         <v>241</v>
       </c>
       <c r="B506" s="1">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9727,7 +9806,7 @@
         <v>243</v>
       </c>
       <c r="B508" s="1">
-        <v>745</v>
+        <v>763</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9735,7 +9814,7 @@
         <v>244</v>
       </c>
       <c r="B509" s="19">
-        <v>1055</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9743,7 +9822,7 @@
         <v>245</v>
       </c>
       <c r="B510" s="19">
-        <v>1724</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9751,7 +9830,7 @@
         <v>246</v>
       </c>
       <c r="B511" s="19">
-        <v>1888</v>
+        <v>1925</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9767,7 +9846,7 @@
         <v>248</v>
       </c>
       <c r="B513" s="19">
-        <v>2201</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9775,7 +9854,7 @@
         <v>249</v>
       </c>
       <c r="B514" s="19">
-        <v>2515</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9783,7 +9862,7 @@
         <v>250</v>
       </c>
       <c r="B515" s="19">
-        <v>1850</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9791,7 +9870,7 @@
         <v>251</v>
       </c>
       <c r="B516" s="19">
-        <v>2157</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9799,7 +9878,7 @@
         <v>252</v>
       </c>
       <c r="B517" s="1">
-        <v>781</v>
+        <v>801</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9807,7 +9886,7 @@
         <v>253</v>
       </c>
       <c r="B518" s="19">
-        <v>1673</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9823,7 +9902,7 @@
         <v>255</v>
       </c>
       <c r="B520" s="1">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9831,7 +9910,7 @@
         <v>256</v>
       </c>
       <c r="B521" s="1">
-        <v>123</v>
+        <v>127</v>
       </c>
     </row>
     <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9839,7 +9918,7 @@
         <v>257</v>
       </c>
       <c r="B522" s="1">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9847,7 +9926,7 @@
         <v>258</v>
       </c>
       <c r="B523" s="1">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9855,7 +9934,7 @@
         <v>259</v>
       </c>
       <c r="B524" s="1">
-        <v>137</v>
+        <v>141</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9863,15 +9942,15 @@
         <v>260</v>
       </c>
       <c r="B525" s="1">
-        <v>180</v>
+        <v>185</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="20" t="s">
         <v>261</v>
       </c>
-      <c r="B526" s="1">
-        <v>982</v>
+      <c r="B526" s="19">
+        <v>1006</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9879,7 +9958,7 @@
         <v>262</v>
       </c>
       <c r="B527" s="19">
-        <v>1019</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9887,7 +9966,7 @@
         <v>263</v>
       </c>
       <c r="B528" s="19">
-        <v>1021</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9895,7 +9974,7 @@
         <v>264</v>
       </c>
       <c r="B529" s="19">
-        <v>2575</v>
+        <v>2640</v>
       </c>
     </row>
     <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9903,7 +9982,7 @@
         <v>265</v>
       </c>
       <c r="B530" s="19">
-        <v>1758</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9911,7 +9990,7 @@
         <v>266</v>
       </c>
       <c r="B531" s="19">
-        <v>1988</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9919,7 +9998,7 @@
         <v>267</v>
       </c>
       <c r="B532" s="19">
-        <v>1692</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9935,7 +10014,7 @@
         <v>269</v>
       </c>
       <c r="B534" s="19">
-        <v>1586</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9943,7 +10022,7 @@
         <v>270</v>
       </c>
       <c r="B535" s="19">
-        <v>2019</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9951,7 +10030,7 @@
         <v>271</v>
       </c>
       <c r="B536" s="19">
-        <v>2286</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9959,7 +10038,7 @@
         <v>272</v>
       </c>
       <c r="B537" s="19">
-        <v>2019</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9967,7 +10046,7 @@
         <v>273</v>
       </c>
       <c r="B538" s="19">
-        <v>2999</v>
+        <v>3074</v>
       </c>
     </row>
     <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9983,7 +10062,7 @@
         <v>275</v>
       </c>
       <c r="B540" s="19">
-        <v>2905</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9991,7 +10070,7 @@
         <v>276</v>
       </c>
       <c r="B541" s="19">
-        <v>2520</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -9999,7 +10078,7 @@
         <v>277</v>
       </c>
       <c r="B542" s="19">
-        <v>4123</v>
+        <v>4226</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10007,7 +10086,7 @@
         <v>278</v>
       </c>
       <c r="B543" s="19">
-        <v>4121</v>
+        <v>4224</v>
       </c>
     </row>
     <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10015,7 +10094,7 @@
         <v>279</v>
       </c>
       <c r="B544" s="19">
-        <v>2529</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10023,7 +10102,7 @@
         <v>280</v>
       </c>
       <c r="B545" s="19">
-        <v>3156</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="546" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10031,7 +10110,7 @@
         <v>281</v>
       </c>
       <c r="B546" s="19">
-        <v>3561</v>
+        <v>3650</v>
       </c>
     </row>
     <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10039,7 +10118,7 @@
         <v>282</v>
       </c>
       <c r="B547" s="1">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10047,7 +10126,7 @@
         <v>283</v>
       </c>
       <c r="B548" s="1">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10055,7 +10134,7 @@
         <v>284</v>
       </c>
       <c r="B549" s="1">
-        <v>288</v>
+        <v>295</v>
       </c>
     </row>
     <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10063,7 +10142,7 @@
         <v>285</v>
       </c>
       <c r="B550" s="1">
-        <v>186</v>
+        <v>190</v>
       </c>
     </row>
     <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10071,7 +10150,7 @@
         <v>286</v>
       </c>
       <c r="B551" s="1">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10079,7 +10158,7 @@
         <v>287</v>
       </c>
       <c r="B552" s="1">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10087,7 +10166,7 @@
         <v>288</v>
       </c>
       <c r="B553" s="1">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10103,7 +10182,7 @@
         <v>290</v>
       </c>
       <c r="B555" s="1">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10111,7 +10190,7 @@
         <v>291</v>
       </c>
       <c r="B556" s="1">
-        <v>219</v>
+        <v>224</v>
       </c>
     </row>
     <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10119,7 +10198,7 @@
         <v>292</v>
       </c>
       <c r="B557" s="1">
-        <v>165</v>
+        <v>168</v>
       </c>
     </row>
     <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10127,7 +10206,7 @@
         <v>293</v>
       </c>
       <c r="B558" s="1">
-        <v>167</v>
+        <v>169</v>
       </c>
     </row>
     <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10135,7 +10214,7 @@
         <v>294</v>
       </c>
       <c r="B559" s="1">
-        <v>206</v>
+        <v>210</v>
       </c>
     </row>
     <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10143,7 +10222,7 @@
         <v>295</v>
       </c>
       <c r="B560" s="19">
-        <v>1415</v>
+        <v>1443</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10151,7 +10230,7 @@
         <v>296</v>
       </c>
       <c r="B561" s="19">
-        <v>3753</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10159,7 +10238,7 @@
         <v>297</v>
       </c>
       <c r="B562" s="19">
-        <v>3753</v>
+        <v>3810</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10167,7 +10246,7 @@
         <v>298</v>
       </c>
       <c r="B563" s="19">
-        <v>3247</v>
+        <v>3295</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10199,7 +10278,7 @@
         <v>302</v>
       </c>
       <c r="B567" s="1">
-        <v>185</v>
+        <v>188</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10207,7 +10286,7 @@
         <v>303</v>
       </c>
       <c r="B568" s="19">
-        <v>3116</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10215,7 +10294,7 @@
         <v>304</v>
       </c>
       <c r="B569" s="19">
-        <v>3356</v>
+        <v>3440</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10223,7 +10302,7 @@
         <v>305</v>
       </c>
       <c r="B570" s="19">
-        <v>3169</v>
+        <v>3233</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10231,7 +10310,7 @@
         <v>306</v>
       </c>
       <c r="B571" s="19">
-        <v>4786</v>
+        <v>4858</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10239,7 +10318,7 @@
         <v>307</v>
       </c>
       <c r="B572" s="1">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10247,7 +10326,7 @@
         <v>308</v>
       </c>
       <c r="B573" s="1">
-        <v>207</v>
+        <v>211</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10255,7 +10334,7 @@
         <v>309</v>
       </c>
       <c r="B574" s="1">
-        <v>208</v>
+        <v>212</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10263,7 +10342,7 @@
         <v>310</v>
       </c>
       <c r="B575" s="1">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10271,7 +10350,7 @@
         <v>311</v>
       </c>
       <c r="B576" s="1">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10279,7 +10358,7 @@
         <v>312</v>
       </c>
       <c r="B577" s="1">
-        <v>274</v>
+        <v>281</v>
       </c>
     </row>
     <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10287,7 +10366,7 @@
         <v>313</v>
       </c>
       <c r="B578" s="1">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10295,7 +10374,7 @@
         <v>314</v>
       </c>
       <c r="B579" s="19">
-        <v>3788</v>
+        <v>3882</v>
       </c>
     </row>
     <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10303,7 +10382,7 @@
         <v>6009</v>
       </c>
       <c r="B580" s="1">
-        <v>88</v>
+        <v>95</v>
       </c>
     </row>
     <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10311,7 +10390,7 @@
         <v>70012</v>
       </c>
       <c r="B581" s="1">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10319,7 +10398,7 @@
         <v>1016</v>
       </c>
       <c r="B582" s="1">
-        <v>136</v>
+        <v>146</v>
       </c>
     </row>
     <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10327,7 +10406,7 @@
         <v>65016</v>
       </c>
       <c r="B583" s="1">
-        <v>77</v>
+        <v>83</v>
       </c>
     </row>
     <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10335,7 +10414,7 @@
         <v>70016</v>
       </c>
       <c r="B584" s="1">
-        <v>200</v>
+        <v>216</v>
       </c>
     </row>
     <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10343,7 +10422,7 @@
         <v>14175</v>
       </c>
       <c r="B585" s="1">
-        <v>293</v>
+        <v>316</v>
       </c>
     </row>
     <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10351,7 +10430,7 @@
         <v>315</v>
       </c>
       <c r="B586" s="1">
-        <v>653</v>
+        <v>705</v>
       </c>
     </row>
     <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10359,7 +10438,7 @@
         <v>130024</v>
       </c>
       <c r="B587" s="1">
-        <v>476</v>
+        <v>514</v>
       </c>
     </row>
     <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10367,7 +10446,7 @@
         <v>19524</v>
       </c>
       <c r="B588" s="1">
-        <v>538</v>
+        <v>581</v>
       </c>
     </row>
     <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10375,7 +10454,7 @@
         <v>316</v>
       </c>
       <c r="B589" s="1">
-        <v>631</v>
+        <v>682</v>
       </c>
     </row>
     <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10383,7 +10462,7 @@
         <v>13188</v>
       </c>
       <c r="B590" s="19">
-        <v>3517</v>
+        <v>3798</v>
       </c>
     </row>
     <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10391,15 +10470,15 @@
         <v>317</v>
       </c>
       <c r="B591" s="19">
-        <v>1056</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="20" t="s">
         <v>318</v>
       </c>
-      <c r="B592" s="1">
-        <v>974</v>
+      <c r="B592" s="19">
+        <v>1052</v>
       </c>
     </row>
     <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10407,7 +10486,7 @@
         <v>319</v>
       </c>
       <c r="B593" s="19">
-        <v>1874</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10415,7 +10494,7 @@
         <v>320</v>
       </c>
       <c r="B594" s="19">
-        <v>1357</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10423,7 +10502,7 @@
         <v>321</v>
       </c>
       <c r="B595" s="19">
-        <v>1668</v>
+        <v>1801</v>
       </c>
     </row>
     <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10431,7 +10510,7 @@
         <v>322</v>
       </c>
       <c r="B596" s="19">
-        <v>2110</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10439,7 +10518,7 @@
         <v>323</v>
       </c>
       <c r="B597" s="19">
-        <v>2363</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10447,7 +10526,7 @@
         <v>324</v>
       </c>
       <c r="B598" s="19">
-        <v>2361</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10455,7 +10534,7 @@
         <v>325</v>
       </c>
       <c r="B599" s="19">
-        <v>2628</v>
+        <v>2838</v>
       </c>
     </row>
     <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10463,7 +10542,7 @@
         <v>326</v>
       </c>
       <c r="B600" s="19">
-        <v>4946</v>
+        <v>5342</v>
       </c>
     </row>
     <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10471,7 +10550,7 @@
         <v>29525</v>
       </c>
       <c r="B601" s="19">
-        <v>5205</v>
+        <v>5622</v>
       </c>
     </row>
     <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10479,7 +10558,7 @@
         <v>29529</v>
       </c>
       <c r="B602" s="19">
-        <v>3803</v>
+        <v>4108</v>
       </c>
     </row>
     <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10757,7 +10836,7 @@
         <v>336</v>
       </c>
       <c r="B637" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10765,7 +10844,7 @@
         <v>337</v>
       </c>
       <c r="B638" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10773,7 +10852,7 @@
         <v>338</v>
       </c>
       <c r="B639" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10781,7 +10860,7 @@
         <v>339</v>
       </c>
       <c r="B640" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10789,7 +10868,7 @@
         <v>340</v>
       </c>
       <c r="B641" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10797,7 +10876,7 @@
         <v>341</v>
       </c>
       <c r="B642" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10805,7 +10884,7 @@
         <v>342</v>
       </c>
       <c r="B643" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10813,7 +10892,7 @@
         <v>343</v>
       </c>
       <c r="B644" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10821,7 +10900,7 @@
         <v>344</v>
       </c>
       <c r="B645" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="646" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10829,7 +10908,7 @@
         <v>345</v>
       </c>
       <c r="B646" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10837,7 +10916,7 @@
         <v>346</v>
       </c>
       <c r="B647" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10845,7 +10924,7 @@
         <v>347</v>
       </c>
       <c r="B648" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10853,7 +10932,7 @@
         <v>348</v>
       </c>
       <c r="B649" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10861,7 +10940,7 @@
         <v>349</v>
       </c>
       <c r="B650" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10869,7 +10948,7 @@
         <v>350</v>
       </c>
       <c r="B651" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10877,7 +10956,7 @@
         <v>351</v>
       </c>
       <c r="B652" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10885,7 +10964,7 @@
         <v>352</v>
       </c>
       <c r="B653" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10893,7 +10972,7 @@
         <v>353</v>
       </c>
       <c r="B654" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10901,7 +10980,7 @@
         <v>354</v>
       </c>
       <c r="B655" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10909,7 +10988,7 @@
         <v>355</v>
       </c>
       <c r="B656" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="657" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10917,7 +10996,7 @@
         <v>356</v>
       </c>
       <c r="B657" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="658" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10925,7 +11004,7 @@
         <v>357</v>
       </c>
       <c r="B658" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="659" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10933,7 +11012,7 @@
         <v>358</v>
       </c>
       <c r="B659" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="660" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10941,7 +11020,7 @@
         <v>359</v>
       </c>
       <c r="B660" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="661" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10949,7 +11028,7 @@
         <v>360</v>
       </c>
       <c r="B661" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="662" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10957,7 +11036,7 @@
         <v>361</v>
       </c>
       <c r="B662" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="663" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10965,7 +11044,7 @@
         <v>362</v>
       </c>
       <c r="B663" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="664" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10973,7 +11052,7 @@
         <v>363</v>
       </c>
       <c r="B664" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="665" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10981,7 +11060,7 @@
         <v>364</v>
       </c>
       <c r="B665" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="666" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10989,7 +11068,7 @@
         <v>365</v>
       </c>
       <c r="B666" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="667" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -10997,7 +11076,7 @@
         <v>366</v>
       </c>
       <c r="B667" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="668" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11005,7 +11084,7 @@
         <v>367</v>
       </c>
       <c r="B668" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="669" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11013,7 +11092,7 @@
         <v>368</v>
       </c>
       <c r="B669" s="1">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="670" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11021,7 +11100,7 @@
         <v>369</v>
       </c>
       <c r="B670" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="671" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11029,7 +11108,7 @@
         <v>370</v>
       </c>
       <c r="B671" s="1">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="672" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11037,7 +11116,7 @@
         <v>371</v>
       </c>
       <c r="B672" s="1">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11045,7 +11124,7 @@
         <v>372</v>
       </c>
       <c r="B673" s="1">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11053,7 +11132,7 @@
         <v>373</v>
       </c>
       <c r="B674" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11061,7 +11140,7 @@
         <v>374</v>
       </c>
       <c r="B675" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11069,7 +11148,7 @@
         <v>375</v>
       </c>
       <c r="B676" s="1">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11077,7 +11156,7 @@
         <v>376</v>
       </c>
       <c r="B677" s="1">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11085,7 +11164,7 @@
         <v>377</v>
       </c>
       <c r="B678" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11093,15 +11172,15 @@
         <v>378</v>
       </c>
       <c r="B679" s="1">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A680" s="20" t="s">
+      <c r="A680" s="28" t="s">
         <v>379</v>
       </c>
       <c r="B680" s="3">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11109,7 +11188,7 @@
         <v>380</v>
       </c>
       <c r="B681" s="1">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11117,7 +11196,7 @@
         <v>381</v>
       </c>
       <c r="B682" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11125,7 +11204,7 @@
         <v>382</v>
       </c>
       <c r="B683" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11133,7 +11212,7 @@
         <v>383</v>
       </c>
       <c r="B684" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11141,7 +11220,7 @@
         <v>384</v>
       </c>
       <c r="B685" s="1">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11149,7 +11228,7 @@
         <v>385</v>
       </c>
       <c r="B686" s="1">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11157,7 +11236,7 @@
         <v>386</v>
       </c>
       <c r="B687" s="1">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11165,7 +11244,7 @@
         <v>387</v>
       </c>
       <c r="B688" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11173,7 +11252,7 @@
         <v>388</v>
       </c>
       <c r="B689" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11181,7 +11260,7 @@
         <v>389</v>
       </c>
       <c r="B690" s="1">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11189,7 +11268,7 @@
         <v>6053</v>
       </c>
       <c r="B691" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11197,7 +11276,7 @@
         <v>6056</v>
       </c>
       <c r="B692" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11205,7 +11284,7 @@
         <v>6059</v>
       </c>
       <c r="B693" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11213,7 +11292,7 @@
         <v>6062</v>
       </c>
       <c r="B694" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11221,7 +11300,7 @@
         <v>6065</v>
       </c>
       <c r="B695" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11229,7 +11308,7 @@
         <v>6071</v>
       </c>
       <c r="B696" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="697" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11237,7 +11316,7 @@
         <v>6074</v>
       </c>
       <c r="B697" s="1">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11245,7 +11324,7 @@
         <v>6077</v>
       </c>
       <c r="B698" s="1">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11253,7 +11332,7 @@
         <v>6080</v>
       </c>
       <c r="B699" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11261,7 +11340,7 @@
         <v>6083</v>
       </c>
       <c r="B700" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11269,7 +11348,7 @@
         <v>6086</v>
       </c>
       <c r="B701" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11277,7 +11356,7 @@
         <v>6089</v>
       </c>
       <c r="B702" s="1">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11285,7 +11364,7 @@
         <v>6098</v>
       </c>
       <c r="B703" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11293,7 +11372,7 @@
         <v>6101</v>
       </c>
       <c r="B704" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="705" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11301,7 +11380,7 @@
         <v>6107</v>
       </c>
       <c r="B705" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="706" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11309,7 +11388,7 @@
         <v>6535</v>
       </c>
       <c r="B706" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="707" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11317,7 +11396,7 @@
         <v>6555</v>
       </c>
       <c r="B707" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="708" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11325,7 +11404,7 @@
         <v>6567</v>
       </c>
       <c r="B708" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="709" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11333,7 +11412,7 @@
         <v>6569</v>
       </c>
       <c r="B709" s="1">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="710" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11341,7 +11420,7 @@
         <v>6571</v>
       </c>
       <c r="B710" s="1">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="711" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11349,7 +11428,7 @@
         <v>6607</v>
       </c>
       <c r="B711" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="712" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11357,7 +11436,7 @@
         <v>6623</v>
       </c>
       <c r="B712" s="1">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="713" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11365,7 +11444,7 @@
         <v>6627</v>
       </c>
       <c r="B713" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="714" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11373,7 +11452,7 @@
         <v>6635</v>
       </c>
       <c r="B714" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="715" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11381,7 +11460,7 @@
         <v>6731</v>
       </c>
       <c r="B715" s="1">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="716" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11389,7 +11468,7 @@
         <v>6747</v>
       </c>
       <c r="B716" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="717" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11397,7 +11476,7 @@
         <v>6787</v>
       </c>
       <c r="B717" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="718" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11405,7 +11484,7 @@
         <v>6795</v>
       </c>
       <c r="B718" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="719" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11413,7 +11492,7 @@
         <v>6811</v>
       </c>
       <c r="B719" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="720" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11421,7 +11500,7 @@
         <v>6819</v>
       </c>
       <c r="B720" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="721" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11429,7 +11508,7 @@
         <v>4892</v>
       </c>
       <c r="B721" s="1">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="722" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11437,7 +11516,7 @@
         <v>5029</v>
       </c>
       <c r="B722" s="1">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="723" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11445,7 +11524,7 @@
         <v>5050</v>
       </c>
       <c r="B723" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="724" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11453,7 +11532,7 @@
         <v>5030</v>
       </c>
       <c r="B724" s="1">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="725" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11461,7 +11540,7 @@
         <v>5031</v>
       </c>
       <c r="B725" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="726" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11469,7 +11548,7 @@
         <v>5035</v>
       </c>
       <c r="B726" s="1">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="727" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11477,7 +11556,7 @@
         <v>5041</v>
       </c>
       <c r="B727" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="728" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11485,7 +11564,7 @@
         <v>5048</v>
       </c>
       <c r="B728" s="1">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="729" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11493,7 +11572,7 @@
         <v>5045</v>
       </c>
       <c r="B729" s="1">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="730" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11501,7 +11580,7 @@
         <v>5034</v>
       </c>
       <c r="B730" s="1">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="731" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11509,7 +11588,7 @@
         <v>5036</v>
       </c>
       <c r="B731" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="732" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11517,7 +11596,7 @@
         <v>5042</v>
       </c>
       <c r="B732" s="1">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="733" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11525,7 +11604,7 @@
         <v>5047</v>
       </c>
       <c r="B733" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="734" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11533,7 +11612,7 @@
         <v>5049</v>
       </c>
       <c r="B734" s="1">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="735" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11541,7 +11620,7 @@
         <v>5005</v>
       </c>
       <c r="B735" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="736" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11549,7 +11628,7 @@
         <v>5015</v>
       </c>
       <c r="B736" s="1">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="737" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11557,7 +11636,7 @@
         <v>5007</v>
       </c>
       <c r="B737" s="1">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="738" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11565,7 +11644,7 @@
         <v>5008</v>
       </c>
       <c r="B738" s="1">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="739" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11573,7 +11652,7 @@
         <v>6241</v>
       </c>
       <c r="B739" s="1">
-        <v>194</v>
+        <v>199</v>
       </c>
     </row>
     <row r="740" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11581,7 +11660,7 @@
         <v>6259</v>
       </c>
       <c r="B740" s="1">
-        <v>210</v>
+        <v>217</v>
       </c>
     </row>
     <row r="741" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11589,7 +11668,7 @@
         <v>6249</v>
       </c>
       <c r="B741" s="1">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="742" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11597,7 +11676,7 @@
         <v>5555</v>
       </c>
       <c r="B742" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="743" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11605,7 +11684,7 @@
         <v>5535</v>
       </c>
       <c r="B743" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="744" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11613,7 +11692,7 @@
         <v>5567</v>
       </c>
       <c r="B744" s="1">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="745" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11621,7 +11700,7 @@
         <v>5527</v>
       </c>
       <c r="B745" s="1">
-        <v>100</v>
+        <v>103</v>
       </c>
     </row>
     <row r="746" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11629,7 +11708,7 @@
         <v>5563</v>
       </c>
       <c r="B746" s="1">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="747" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11637,7 +11716,7 @@
         <v>4452</v>
       </c>
       <c r="B747" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="748" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11645,7 +11724,7 @@
         <v>4359</v>
       </c>
       <c r="B748" s="1">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="749" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -11653,7 +11732,7 @@
         <v>4360</v>
       </c>
       <c r="B749" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="750" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11661,7 +11740,7 @@
         <v>4361</v>
       </c>
       <c r="B750" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="751" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11669,7 +11748,7 @@
         <v>4362</v>
       </c>
       <c r="B751" s="1">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="752" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11677,7 +11756,7 @@
         <v>4358</v>
       </c>
       <c r="B752" s="1">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="753" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11685,7 +11764,7 @@
         <v>4453</v>
       </c>
       <c r="B753" s="1">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="754" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11693,7 +11772,7 @@
         <v>4449</v>
       </c>
       <c r="B754" s="1">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="755" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11701,7 +11780,7 @@
         <v>4363</v>
       </c>
       <c r="B755" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="756" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11709,7 +11788,7 @@
         <v>4364</v>
       </c>
       <c r="B756" s="1">
-        <v>107</v>
+        <v>110</v>
       </c>
     </row>
     <row r="757" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11717,7 +11796,7 @@
         <v>4610</v>
       </c>
       <c r="B757" s="1">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="758" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11725,7 +11804,7 @@
         <v>4457</v>
       </c>
       <c r="B758" s="1">
-        <v>110</v>
+        <v>113</v>
       </c>
     </row>
     <row r="759" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11733,7 +11812,7 @@
         <v>4613</v>
       </c>
       <c r="B759" s="1">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="760" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11741,7 +11820,7 @@
         <v>3356</v>
       </c>
       <c r="B760" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="761" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11749,7 +11828,7 @@
         <v>3305</v>
       </c>
       <c r="B761" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="762" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11757,7 +11836,7 @@
         <v>3392</v>
       </c>
       <c r="B762" s="1">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="763" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11765,7 +11844,7 @@
         <v>3445</v>
       </c>
       <c r="B763" s="1">
-        <v>117</v>
+        <v>121</v>
       </c>
     </row>
     <row r="764" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11773,7 +11852,7 @@
         <v>3355</v>
       </c>
       <c r="B764" s="1">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="765" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11781,7 +11860,7 @@
         <v>3453</v>
       </c>
       <c r="B765" s="1">
-        <v>127</v>
+        <v>131</v>
       </c>
     </row>
     <row r="766" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11789,7 +11868,7 @@
         <v>3286</v>
       </c>
       <c r="B766" s="1">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="767" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11797,7 +11876,7 @@
         <v>3450</v>
       </c>
       <c r="B767" s="1">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="768" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11805,7 +11884,7 @@
         <v>3357</v>
       </c>
       <c r="B768" s="1">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="769" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11813,7 +11892,7 @@
         <v>3397</v>
       </c>
       <c r="B769" s="1">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="770" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11821,7 +11900,7 @@
         <v>3393</v>
       </c>
       <c r="B770" s="1">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="771" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11829,7 +11908,7 @@
         <v>3421</v>
       </c>
       <c r="B771" s="1">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="772" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11837,7 +11916,7 @@
         <v>3426</v>
       </c>
       <c r="B772" s="1">
-        <v>138</v>
+        <v>143</v>
       </c>
     </row>
     <row r="773" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11845,7 +11924,7 @@
         <v>3446</v>
       </c>
       <c r="B773" s="1">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="774" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11853,7 +11932,7 @@
         <v>3458</v>
       </c>
       <c r="B774" s="1">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="775" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11861,7 +11940,7 @@
         <v>3464</v>
       </c>
       <c r="B775" s="1">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="776" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11869,7 +11948,7 @@
         <v>3478</v>
       </c>
       <c r="B776" s="1">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="777" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11877,7 +11956,7 @@
         <v>6662</v>
       </c>
       <c r="B777" s="1">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="778" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11885,7 +11964,7 @@
         <v>3461</v>
       </c>
       <c r="B778" s="1">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
     <row r="779" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11893,7 +11972,7 @@
         <v>3477</v>
       </c>
       <c r="B779" s="1">
-        <v>176</v>
+        <v>181</v>
       </c>
     </row>
     <row r="780" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11901,7 +11980,7 @@
         <v>3472</v>
       </c>
       <c r="B780" s="1">
-        <v>160</v>
+        <v>165</v>
       </c>
     </row>
     <row r="781" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11909,7 +11988,7 @@
         <v>3176</v>
       </c>
       <c r="B781" s="1">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="782" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11917,7 +11996,7 @@
         <v>3206</v>
       </c>
       <c r="B782" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="783" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11925,7 +12004,7 @@
         <v>3239</v>
       </c>
       <c r="B783" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="784" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11933,7 +12012,7 @@
         <v>3208</v>
       </c>
       <c r="B784" s="1">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="785" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11941,7 +12020,7 @@
         <v>3241</v>
       </c>
       <c r="B785" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="786" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11949,15 +12028,15 @@
         <v>3237</v>
       </c>
       <c r="B786" s="1">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="787" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A787" s="2">
+      <c r="A787" s="9">
         <v>3269</v>
       </c>
       <c r="B787" s="3">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="788" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11965,7 +12044,7 @@
         <v>3303</v>
       </c>
       <c r="B788" s="1">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="789" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11973,7 +12052,7 @@
         <v>3352</v>
       </c>
       <c r="B789" s="1">
-        <v>104</v>
+        <v>107</v>
       </c>
     </row>
     <row r="790" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11981,7 +12060,7 @@
         <v>3238</v>
       </c>
       <c r="B790" s="1">
-        <v>85</v>
+        <v>88</v>
       </c>
     </row>
     <row r="791" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11989,7 +12068,7 @@
         <v>3347</v>
       </c>
       <c r="B791" s="1">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="792" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -11997,7 +12076,7 @@
         <v>390</v>
       </c>
       <c r="B792" s="1">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="793" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12005,7 +12084,7 @@
         <v>391</v>
       </c>
       <c r="B793" s="1">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="794" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12013,7 +12092,7 @@
         <v>392</v>
       </c>
       <c r="B794" s="1">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="795" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12021,7 +12100,7 @@
         <v>393</v>
       </c>
       <c r="B795" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="796" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12029,7 +12108,7 @@
         <v>394</v>
       </c>
       <c r="B796" s="1">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="797" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12037,7 +12116,7 @@
         <v>395</v>
       </c>
       <c r="B797" s="1">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="798" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12045,7 +12124,7 @@
         <v>396</v>
       </c>
       <c r="B798" s="1">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="799" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12053,7 +12132,7 @@
         <v>397</v>
       </c>
       <c r="B799" s="1">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="800" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12061,7 +12140,7 @@
         <v>398</v>
       </c>
       <c r="B800" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="801" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12069,7 +12148,7 @@
         <v>399</v>
       </c>
       <c r="B801" s="1">
-        <v>500</v>
+        <v>540</v>
       </c>
     </row>
     <row r="802" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12077,7 +12156,7 @@
         <v>400</v>
       </c>
       <c r="B802" s="1">
-        <v>607</v>
+        <v>655</v>
       </c>
     </row>
     <row r="803" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -12085,7 +12164,7 @@
         <v>401</v>
       </c>
       <c r="B803" s="19">
-        <v>2085</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="804" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12093,7 +12172,7 @@
         <v>402</v>
       </c>
       <c r="B804" s="1">
-        <v>722</v>
+        <v>780</v>
       </c>
     </row>
     <row r="805" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12101,7 +12180,7 @@
         <v>403</v>
       </c>
       <c r="B805" s="1">
-        <v>853</v>
+        <v>921</v>
       </c>
     </row>
     <row r="806" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12109,7 +12188,7 @@
         <v>404</v>
       </c>
       <c r="B806" s="19">
-        <v>1021</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="807" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12117,7 +12196,7 @@
         <v>405</v>
       </c>
       <c r="B807" s="19">
-        <v>1062</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="808" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12125,7 +12204,7 @@
         <v>406</v>
       </c>
       <c r="B808" s="1">
-        <v>884</v>
+        <v>954</v>
       </c>
     </row>
     <row r="809" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12133,7 +12212,7 @@
         <v>407</v>
       </c>
       <c r="B809" s="19">
-        <v>1119</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="810" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12141,7 +12220,7 @@
         <v>408</v>
       </c>
       <c r="B810" s="19">
-        <v>2585</v>
+        <v>2791</v>
       </c>
     </row>
     <row r="811" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12149,7 +12228,7 @@
         <v>409</v>
       </c>
       <c r="B811" s="19">
-        <v>1548</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="812" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12157,7 +12236,7 @@
         <v>410</v>
       </c>
       <c r="B812" s="19">
-        <v>2824</v>
+        <v>3050</v>
       </c>
     </row>
     <row r="813" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12165,7 +12244,7 @@
         <v>411</v>
       </c>
       <c r="B813" s="19">
-        <v>4309</v>
+        <v>4653</v>
       </c>
     </row>
     <row r="814" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -12173,15 +12252,15 @@
         <v>412</v>
       </c>
       <c r="B814" s="19">
-        <v>4041</v>
+        <v>4365</v>
       </c>
     </row>
     <row r="815" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A815" s="20" t="s">
         <v>413</v>
       </c>
-      <c r="B815" s="1">
-        <v>936</v>
+      <c r="B815" s="19">
+        <v>1011</v>
       </c>
     </row>
     <row r="816" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12189,7 +12268,7 @@
         <v>414</v>
       </c>
       <c r="B816" s="19">
-        <v>1041</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="817" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12197,7 +12276,7 @@
         <v>415</v>
       </c>
       <c r="B817" s="1">
-        <v>580</v>
+        <v>626</v>
       </c>
     </row>
     <row r="818" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12205,7 +12284,7 @@
         <v>416</v>
       </c>
       <c r="B818" s="19">
-        <v>1164</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="819" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12213,7 +12292,7 @@
         <v>417</v>
       </c>
       <c r="B819" s="19">
-        <v>1699</v>
+        <v>1835</v>
       </c>
     </row>
     <row r="820" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12221,7 +12300,7 @@
         <v>418</v>
       </c>
       <c r="B820" s="19">
-        <v>2293</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="821" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12229,23 +12308,23 @@
         <v>419</v>
       </c>
       <c r="B821" s="19">
-        <v>1949</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="822" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A822" s="20" t="s">
         <v>420</v>
       </c>
-      <c r="B822" s="1">
-        <v>935</v>
+      <c r="B822" s="19">
+        <v>1010</v>
       </c>
     </row>
     <row r="823" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A823" s="20" t="s">
         <v>421</v>
       </c>
-      <c r="B823" s="1">
-        <v>936</v>
+      <c r="B823" s="19">
+        <v>1011</v>
       </c>
     </row>
     <row r="824" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12253,7 +12332,7 @@
         <v>422</v>
       </c>
       <c r="B824" s="1">
-        <v>918</v>
+        <v>992</v>
       </c>
     </row>
     <row r="825" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12261,7 +12340,7 @@
         <v>423</v>
       </c>
       <c r="B825" s="19">
-        <v>1094</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="826" spans="1:2" ht="27.6" x14ac:dyDescent="0.25">
@@ -12269,7 +12348,7 @@
         <v>424</v>
       </c>
       <c r="B826" s="19">
-        <v>1430</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="827" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12277,7 +12356,7 @@
         <v>425</v>
       </c>
       <c r="B827" s="1">
-        <v>193</v>
+        <v>209</v>
       </c>
     </row>
     <row r="828" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12285,7 +12364,7 @@
         <v>426</v>
       </c>
       <c r="B828" s="1">
-        <v>314</v>
+        <v>339</v>
       </c>
     </row>
     <row r="829" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12293,7 +12372,7 @@
         <v>427</v>
       </c>
       <c r="B829" s="1">
-        <v>280</v>
+        <v>302</v>
       </c>
     </row>
     <row r="830" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12301,7 +12380,7 @@
         <v>428</v>
       </c>
       <c r="B830" s="1">
-        <v>363</v>
+        <v>393</v>
       </c>
     </row>
     <row r="831" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12309,7 +12388,7 @@
         <v>429</v>
       </c>
       <c r="B831" s="1">
-        <v>401</v>
+        <v>433</v>
       </c>
     </row>
     <row r="832" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12317,7 +12396,7 @@
         <v>430</v>
       </c>
       <c r="B832" s="1">
-        <v>359</v>
+        <v>388</v>
       </c>
     </row>
     <row r="833" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12325,7 +12404,7 @@
         <v>431</v>
       </c>
       <c r="B833" s="1">
-        <v>535</v>
+        <v>578</v>
       </c>
     </row>
     <row r="834" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12333,7 +12412,7 @@
         <v>432</v>
       </c>
       <c r="B834" s="1">
-        <v>565</v>
+        <v>610</v>
       </c>
     </row>
     <row r="835" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12341,7 +12420,7 @@
         <v>433</v>
       </c>
       <c r="B835" s="1">
-        <v>615</v>
+        <v>664</v>
       </c>
     </row>
     <row r="836" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12349,7 +12428,7 @@
         <v>434</v>
       </c>
       <c r="B836" s="1">
-        <v>634</v>
+        <v>684</v>
       </c>
     </row>
     <row r="837" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12357,15 +12436,15 @@
         <v>435</v>
       </c>
       <c r="B837" s="1">
-        <v>677</v>
+        <v>731</v>
       </c>
     </row>
     <row r="838" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A838" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="B838" s="1">
-        <v>939</v>
+      <c r="B838" s="19">
+        <v>1014</v>
       </c>
     </row>
     <row r="839" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12373,7 +12452,7 @@
         <v>437</v>
       </c>
       <c r="B839" s="19">
-        <v>2097</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="840" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12381,7 +12460,7 @@
         <v>438</v>
       </c>
       <c r="B840" s="1">
-        <v>529</v>
+        <v>571</v>
       </c>
     </row>
     <row r="841" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12389,7 +12468,7 @@
         <v>439</v>
       </c>
       <c r="B841" s="1">
-        <v>535</v>
+        <v>578</v>
       </c>
     </row>
     <row r="842" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12397,7 +12476,7 @@
         <v>440</v>
       </c>
       <c r="B842" s="1">
-        <v>429</v>
+        <v>464</v>
       </c>
     </row>
     <row r="843" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12405,7 +12484,7 @@
         <v>441</v>
       </c>
       <c r="B843" s="1">
-        <v>652</v>
+        <v>705</v>
       </c>
     </row>
     <row r="844" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12413,7 +12492,7 @@
         <v>442</v>
       </c>
       <c r="B844" s="1">
-        <v>539</v>
+        <v>582</v>
       </c>
     </row>
     <row r="845" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12421,7 +12500,7 @@
         <v>443</v>
       </c>
       <c r="B845" s="1">
-        <v>708</v>
+        <v>765</v>
       </c>
     </row>
     <row r="846" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12429,7 +12508,7 @@
         <v>444</v>
       </c>
       <c r="B846" s="19">
-        <v>1082</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="847" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12437,7 +12516,7 @@
         <v>445</v>
       </c>
       <c r="B847" s="19">
-        <v>1347</v>
+        <v>1454</v>
       </c>
     </row>
     <row r="848" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12453,7 +12532,7 @@
         <v>447</v>
       </c>
       <c r="B849" s="19">
-        <v>1911</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="850" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12461,7 +12540,7 @@
         <v>448</v>
       </c>
       <c r="B850" s="1">
-        <v>617</v>
+        <v>666</v>
       </c>
     </row>
     <row r="851" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12469,7 +12548,7 @@
         <v>449</v>
       </c>
       <c r="B851" s="1">
-        <v>771</v>
+        <v>833</v>
       </c>
     </row>
     <row r="852" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12477,7 +12556,7 @@
         <v>450</v>
       </c>
       <c r="B852" s="1">
-        <v>835</v>
+        <v>902</v>
       </c>
     </row>
     <row r="853" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12485,7 +12564,7 @@
         <v>451</v>
       </c>
       <c r="B853" s="1">
-        <v>482</v>
+        <v>521</v>
       </c>
     </row>
     <row r="854" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12493,7 +12572,7 @@
         <v>452</v>
       </c>
       <c r="B854" s="1">
-        <v>537</v>
+        <v>580</v>
       </c>
     </row>
     <row r="855" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12501,7 +12580,7 @@
         <v>453</v>
       </c>
       <c r="B855" s="1">
-        <v>586</v>
+        <v>633</v>
       </c>
     </row>
     <row r="856" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12509,7 +12588,7 @@
         <v>454</v>
       </c>
       <c r="B856" s="1">
-        <v>470</v>
+        <v>507</v>
       </c>
     </row>
     <row r="857" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12517,7 +12596,7 @@
         <v>455</v>
       </c>
       <c r="B857" s="1">
-        <v>769</v>
+        <v>831</v>
       </c>
     </row>
     <row r="858" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12525,7 +12604,7 @@
         <v>456</v>
       </c>
       <c r="B858" s="19">
-        <v>1056</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="859" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
@@ -12533,335 +12612,359 @@
         <v>457</v>
       </c>
       <c r="B859" s="19">
-        <v>1088</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="860" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A860" s="20" t="s">
-        <v>458</v>
+        <v>498</v>
       </c>
       <c r="B860" s="1">
-        <v>87</v>
+        <v>253</v>
       </c>
     </row>
     <row r="861" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A861" s="20" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B861" s="1">
-        <v>110</v>
+        <v>94</v>
       </c>
     </row>
     <row r="862" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A862" s="20" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B862" s="1">
-        <v>183</v>
+        <v>118</v>
       </c>
     </row>
     <row r="863" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A863" s="20" t="s">
-        <v>461</v>
+      <c r="A863" s="29" t="s">
+        <v>499</v>
       </c>
       <c r="B863" s="1">
-        <v>232</v>
+        <v>198</v>
       </c>
     </row>
     <row r="864" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A864" s="20" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="B864" s="1">
-        <v>146</v>
+        <v>250</v>
       </c>
     </row>
     <row r="865" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A865" s="20" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="B865" s="1">
-        <v>137</v>
+        <v>158</v>
       </c>
     </row>
     <row r="866" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A866" s="20" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="B866" s="1">
-        <v>216</v>
+        <v>148</v>
       </c>
     </row>
     <row r="867" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A867" s="20" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="B867" s="1">
-        <v>256</v>
+        <v>233</v>
       </c>
     </row>
     <row r="868" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A868" s="20" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="B868" s="1">
-        <v>406</v>
+        <v>276</v>
       </c>
     </row>
     <row r="869" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A869" s="20" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="B869" s="1">
-        <v>599</v>
+        <v>439</v>
       </c>
     </row>
     <row r="870" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A870" s="20" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="B870" s="1">
-        <v>749</v>
+        <v>647</v>
       </c>
     </row>
     <row r="871" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A871" s="20" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="B871" s="1">
-        <v>476</v>
+        <v>809</v>
       </c>
     </row>
     <row r="872" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A872" s="20" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="B872" s="1">
-        <v>517</v>
+        <v>514</v>
       </c>
     </row>
     <row r="873" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A873" s="20" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="B873" s="1">
-        <v>538</v>
+        <v>558</v>
       </c>
     </row>
     <row r="874" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A874" s="20" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="B874" s="1">
-        <v>563</v>
+        <v>581</v>
       </c>
     </row>
     <row r="875" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A875" s="20" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="B875" s="1">
-        <v>536</v>
+        <v>608</v>
       </c>
     </row>
     <row r="876" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A876" s="20" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="B876" s="1">
-        <v>631</v>
+        <v>579</v>
       </c>
     </row>
     <row r="877" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A877" s="20" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="B877" s="1">
-        <v>740</v>
+        <v>682</v>
       </c>
     </row>
     <row r="878" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A878" s="20" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="B878" s="1">
-        <v>665</v>
+        <v>800</v>
       </c>
     </row>
     <row r="879" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A879" s="20" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B879" s="1">
-        <v>974</v>
+        <v>718</v>
       </c>
     </row>
     <row r="880" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A880" s="20" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="B880" s="19">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="881" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A881" s="20" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="B881" s="19">
-        <v>1276</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="882" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A882" s="20" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="B882" s="19">
-        <v>1357</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="883" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A883" s="20" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="B883" s="19">
-        <v>2363</v>
+        <v>1466</v>
       </c>
     </row>
     <row r="884" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A884" s="20" t="s">
-        <v>482</v>
-      </c>
-      <c r="B884" s="1">
-        <v>77</v>
+        <v>480</v>
+      </c>
+      <c r="B884" s="19">
+        <v>2552</v>
       </c>
     </row>
     <row r="885" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A885" s="20" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B885" s="1">
-        <v>90</v>
+        <v>83</v>
       </c>
     </row>
     <row r="886" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A886" s="20" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="B886" s="1">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="887" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A887" s="20" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B887" s="1">
-        <v>140</v>
+        <v>102</v>
       </c>
     </row>
     <row r="888" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A888" s="20" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B888" s="1">
-        <v>79</v>
+        <v>152</v>
       </c>
     </row>
     <row r="889" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A889" s="20" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="B889" s="1">
-        <v>138</v>
+        <v>85</v>
       </c>
     </row>
     <row r="890" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A890" s="20" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="B890" s="1">
-        <v>138</v>
+        <v>149</v>
       </c>
     </row>
     <row r="891" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A891" s="20" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="B891" s="1">
-        <v>172</v>
+        <v>149</v>
       </c>
     </row>
     <row r="892" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A892" s="20" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="B892" s="1">
-        <v>172</v>
+        <v>185</v>
       </c>
     </row>
     <row r="893" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A893" s="20" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B893" s="1">
-        <v>298</v>
+        <v>185</v>
       </c>
     </row>
     <row r="894" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A894" s="20" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B894" s="1">
-        <v>44</v>
+        <v>322</v>
       </c>
     </row>
     <row r="895" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A895" s="20" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="B895" s="1">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="896" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A896" s="20" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B896" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="897" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A897" s="20" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B897" s="1">
-        <v>76</v>
+        <v>44</v>
       </c>
     </row>
     <row r="898" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A898" s="20" t="s">
-        <v>496</v>
+        <v>493</v>
       </c>
       <c r="B898" s="1">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="899" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A899" s="20" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B899" s="1">
-        <v>97</v>
+        <v>63</v>
       </c>
     </row>
     <row r="900" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A900" s="20" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="B900" s="1">
-        <v>73</v>
+        <v>82</v>
+      </c>
+    </row>
+    <row r="901" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A901" s="20" t="s">
+        <v>495</v>
+      </c>
+      <c r="B901" s="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="902" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A902" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="B902" s="1">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="903" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A903" s="20" t="s">
+        <v>497</v>
+      </c>
+      <c r="B903" s="1">
+        <v>79</v>
       </c>
     </row>
   </sheetData>

--- a/api/files/prices.xlsx
+++ b/api/files/prices.xlsx
@@ -1,26 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29923"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\la union\Desktop\la_union_api_prices\api\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mamustin\Desktop\la_union_api_prices\api\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC28AF02-48C1-4F0D-A56F-0C404BD574D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB43041A-8785-4EA3-BD73-2905A7194E72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -1915,7 +1910,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t>USD 312</t>
+      <t>USD 1.011</t>
     </r>
     <r>
       <rPr>
@@ -1928,80 +1923,16 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>USD 87</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>USD 114</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>USD 1.011</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>USD 682</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t>1</t>
-    </r>
+    <t>USD 682</t>
+  </si>
+  <si>
+    <t>USD 114</t>
+  </si>
+  <si>
+    <t>USD 87</t>
+  </si>
+  <si>
+    <t>USD 312</t>
   </si>
 </sst>
 </file>
@@ -2215,8 +2146,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="28">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2295,6 +2226,9 @@
       <alignment horizontal="left" vertical="top" indent="3" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2757,13 +2691,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B903"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2">
         <v>110375</v>
       </c>
@@ -2771,7 +2705,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>117809</v>
       </c>
@@ -2779,7 +2713,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="2">
         <v>110371</v>
       </c>
@@ -2787,7 +2721,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>117808</v>
       </c>
@@ -2795,7 +2729,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>110540</v>
       </c>
@@ -2803,7 +2737,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>110376</v>
       </c>
@@ -2811,7 +2745,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>110372</v>
       </c>
@@ -2819,7 +2753,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>141148</v>
       </c>
@@ -2827,7 +2761,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>141202</v>
       </c>
@@ -2835,7 +2769,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>110373</v>
       </c>
@@ -2843,7 +2777,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>117820</v>
       </c>
@@ -2851,7 +2785,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>110529</v>
       </c>
@@ -2859,7 +2793,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>117822</v>
       </c>
@@ -2867,7 +2801,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>110325</v>
       </c>
@@ -2875,7 +2809,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>110374</v>
       </c>
@@ -2883,7 +2817,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>107830</v>
       </c>
@@ -2891,7 +2825,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>117830</v>
       </c>
@@ -2899,7 +2833,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>117833</v>
       </c>
@@ -2907,7 +2841,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>141048</v>
       </c>
@@ -2915,7 +2849,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>108794</v>
       </c>
@@ -2923,7 +2857,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>111463</v>
       </c>
@@ -2931,7 +2865,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>141823</v>
       </c>
@@ -2939,7 +2873,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>111466</v>
       </c>
@@ -2947,7 +2881,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>106855</v>
       </c>
@@ -2955,7 +2889,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>118330</v>
       </c>
@@ -2963,7 +2897,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>108711</v>
       </c>
@@ -2971,7 +2905,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>111462</v>
       </c>
@@ -2979,7 +2913,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="2">
         <v>117831</v>
       </c>
@@ -2987,7 +2921,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="2">
         <v>107236</v>
       </c>
@@ -2995,7 +2929,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="2">
         <v>117821</v>
       </c>
@@ -3003,7 +2937,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="2">
         <v>110787</v>
       </c>
@@ -3011,7 +2945,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="2">
         <v>111469</v>
       </c>
@@ -3019,7 +2953,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="2">
         <v>118140</v>
       </c>
@@ -3027,7 +2961,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="2">
         <v>111468</v>
       </c>
@@ -3035,7 +2969,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="2">
         <v>105333</v>
       </c>
@@ -3043,7 +2977,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="2">
         <v>117787</v>
       </c>
@@ -3051,7 +2985,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="2">
         <v>111743</v>
       </c>
@@ -3059,7 +2993,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="2">
         <v>141271</v>
       </c>
@@ -3067,7 +3001,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="2">
         <v>111172</v>
       </c>
@@ -3075,7 +3009,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="2">
         <v>108795</v>
       </c>
@@ -3083,7 +3017,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="2">
         <v>111418</v>
       </c>
@@ -3091,7 +3025,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="2">
         <v>117785</v>
       </c>
@@ -3099,7 +3033,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="2">
         <v>105894</v>
       </c>
@@ -3107,7 +3041,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="2">
         <v>108303</v>
       </c>
@@ -3115,7 +3049,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="2">
         <v>107263</v>
       </c>
@@ -3123,7 +3057,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="2">
         <v>106698</v>
       </c>
@@ -3131,7 +3065,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="2">
         <v>118298</v>
       </c>
@@ -3139,7 +3073,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="2">
         <v>118337</v>
       </c>
@@ -3147,7 +3081,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="2">
         <v>141066</v>
       </c>
@@ -3155,7 +3089,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="9">
         <v>110733</v>
       </c>
@@ -3163,7 +3097,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="2">
         <v>118338</v>
       </c>
@@ -3171,7 +3105,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="2">
         <v>108701</v>
       </c>
@@ -3179,7 +3113,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="2">
         <v>117706</v>
       </c>
@@ -3187,7 +3121,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="2">
         <v>117862</v>
       </c>
@@ -3195,7 +3129,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="2">
         <v>118094</v>
       </c>
@@ -3203,7 +3137,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="2">
         <v>107629</v>
       </c>
@@ -3211,7 +3145,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="2">
         <v>117861</v>
       </c>
@@ -3219,7 +3153,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="58" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="2">
         <v>117786</v>
       </c>
@@ -3227,7 +3161,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="2">
         <v>111467</v>
       </c>
@@ -3235,7 +3169,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="2">
         <v>108583</v>
       </c>
@@ -3243,7 +3177,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="2">
         <v>110581</v>
       </c>
@@ -3251,7 +3185,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="62" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="2">
         <v>110711</v>
       </c>
@@ -3259,7 +3193,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="63" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="2">
         <v>117935</v>
       </c>
@@ -3267,7 +3201,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="64" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="2">
         <v>118381</v>
       </c>
@@ -3275,7 +3209,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="65" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="2">
         <v>106565</v>
       </c>
@@ -3283,7 +3217,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="66" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="2">
         <v>108361</v>
       </c>
@@ -3291,7 +3225,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="67" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="2">
         <v>118382</v>
       </c>
@@ -3299,7 +3233,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="68" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="2">
         <v>118286</v>
       </c>
@@ -3307,7 +3241,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="69" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="2">
         <v>107495</v>
       </c>
@@ -3315,7 +3249,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="70" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="2">
         <v>110233</v>
       </c>
@@ -3323,7 +3257,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="71" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="2">
         <v>109493</v>
       </c>
@@ -3331,7 +3265,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="72" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="2">
         <v>110580</v>
       </c>
@@ -3339,7 +3273,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="73" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="2">
         <v>111110</v>
       </c>
@@ -3347,7 +3281,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="74" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="2">
         <v>118379</v>
       </c>
@@ -3355,7 +3289,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="75" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="2">
         <v>118392</v>
       </c>
@@ -3363,7 +3297,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="76" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="2">
         <v>117948</v>
       </c>
@@ -3371,7 +3305,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="77" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="2">
         <v>118383</v>
       </c>
@@ -3379,7 +3313,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="78" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="2">
         <v>118376</v>
       </c>
@@ -3387,7 +3321,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="79" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="2">
         <v>117859</v>
       </c>
@@ -3395,7 +3329,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="80" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="2">
         <v>118391</v>
       </c>
@@ -3403,7 +3337,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A81" s="2">
         <v>118621</v>
       </c>
@@ -3411,7 +3345,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A82" s="2">
         <v>118320</v>
       </c>
@@ -3419,7 +3353,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A83" s="2">
         <v>117789</v>
       </c>
@@ -3427,7 +3361,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A84" s="2">
         <v>141565</v>
       </c>
@@ -3435,7 +3369,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A85" s="2">
         <v>117840</v>
       </c>
@@ -3443,7 +3377,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="2">
         <v>111442</v>
       </c>
@@ -3451,7 +3385,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A87" s="2">
         <v>110745</v>
       </c>
@@ -3459,7 +3393,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="2">
         <v>110751</v>
       </c>
@@ -3467,7 +3401,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="2">
         <v>111434</v>
       </c>
@@ -3475,7 +3409,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A90" s="2">
         <v>111381</v>
       </c>
@@ -3483,7 +3417,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="2">
         <v>116241</v>
       </c>
@@ -3491,7 +3425,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A92" s="2">
         <v>109338</v>
       </c>
@@ -3499,7 +3433,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A93" s="2">
         <v>140922</v>
       </c>
@@ -3507,7 +3441,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A94" s="2">
         <v>108022</v>
       </c>
@@ -3515,7 +3449,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A95" s="2">
         <v>111532</v>
       </c>
@@ -3523,7 +3457,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A96" s="2">
         <v>111383</v>
       </c>
@@ -3531,7 +3465,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="2">
         <v>117854</v>
       </c>
@@ -3539,7 +3473,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A98" s="2">
         <v>111443</v>
       </c>
@@ -3547,7 +3481,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A99" s="2">
         <v>117315</v>
       </c>
@@ -3555,7 +3489,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="100" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A100" s="2">
         <v>110740</v>
       </c>
@@ -3563,7 +3497,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A101" s="2">
         <v>110762</v>
       </c>
@@ -3571,7 +3505,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A102" s="2">
         <v>100761</v>
       </c>
@@ -3579,7 +3513,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A103" s="2">
         <v>111435</v>
       </c>
@@ -3587,7 +3521,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A104" s="2">
         <v>117841</v>
       </c>
@@ -3595,7 +3529,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A105" s="2">
         <v>110743</v>
       </c>
@@ -3603,7 +3537,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A106" s="2">
         <v>117838</v>
       </c>
@@ -3611,7 +3545,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A107" s="9">
         <v>111433</v>
       </c>
@@ -3619,7 +3553,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="2">
         <v>111430</v>
       </c>
@@ -3627,7 +3561,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A109" s="2">
         <v>117834</v>
       </c>
@@ -3635,7 +3569,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A110" s="2">
         <v>117289</v>
       </c>
@@ -3643,7 +3577,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A111" s="2">
         <v>116527</v>
       </c>
@@ -3651,7 +3585,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A112" s="2">
         <v>107472</v>
       </c>
@@ -3659,7 +3593,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="113" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A113" s="2">
         <v>110746</v>
       </c>
@@ -3667,7 +3601,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="114" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A114" s="2">
         <v>111569</v>
       </c>
@@ -3675,7 +3609,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="115" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A115" s="2">
         <v>110742</v>
       </c>
@@ -3683,7 +3617,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="116" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="2">
         <v>118306</v>
       </c>
@@ -3691,7 +3625,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="117" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="2">
         <v>107474</v>
       </c>
@@ -3699,7 +3633,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="118" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A118" s="2">
         <v>111602</v>
       </c>
@@ -3707,7 +3641,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="119" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="2">
         <v>140923</v>
       </c>
@@ -3715,7 +3649,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="120" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A120" s="2">
         <v>111530</v>
       </c>
@@ -3723,7 +3657,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="121" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A121" s="2">
         <v>110752</v>
       </c>
@@ -3731,7 +3665,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="122" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A122" s="2">
         <v>141318</v>
       </c>
@@ -3739,7 +3673,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="123" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A123" s="2">
         <v>107890</v>
       </c>
@@ -3747,7 +3681,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="124" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A124" s="2">
         <v>141047</v>
       </c>
@@ -3755,7 +3689,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="125" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A125" s="2">
         <v>111439</v>
       </c>
@@ -3763,7 +3697,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="126" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A126" s="2">
         <v>110756</v>
       </c>
@@ -3771,7 +3705,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="127" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A127" s="2">
         <v>107886</v>
       </c>
@@ -3779,7 +3713,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="128" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A128" s="2">
         <v>110753</v>
       </c>
@@ -3787,7 +3721,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A129" s="2">
         <v>110750</v>
       </c>
@@ -3795,7 +3729,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="2">
         <v>111879</v>
       </c>
@@ -3803,7 +3737,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A131" s="2">
         <v>111437</v>
       </c>
@@ -3811,7 +3745,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A132" s="2">
         <v>110749</v>
       </c>
@@ -3819,7 +3753,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A133" s="2">
         <v>111447</v>
       </c>
@@ -3827,7 +3761,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A134" s="2">
         <v>107532</v>
       </c>
@@ -3835,7 +3769,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="135" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A135" s="2">
         <v>109933</v>
       </c>
@@ -3843,7 +3777,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="136" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A136" s="2">
         <v>111655</v>
       </c>
@@ -3851,7 +3785,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="137" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A137" s="2">
         <v>111438</v>
       </c>
@@ -3859,7 +3793,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="138" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A138" s="2">
         <v>110747</v>
       </c>
@@ -3867,7 +3801,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="139" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A139" s="2">
         <v>111445</v>
       </c>
@@ -3875,7 +3809,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="140" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A140" s="2">
         <v>106955</v>
       </c>
@@ -3883,7 +3817,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="141" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="2">
         <v>110313</v>
       </c>
@@ -3891,7 +3825,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="142" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A142" s="2">
         <v>117853</v>
       </c>
@@ -3899,7 +3833,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="143" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A143" s="2">
         <v>110339</v>
       </c>
@@ -3907,7 +3841,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="144" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A144" s="2">
         <v>117856</v>
       </c>
@@ -3915,7 +3849,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="145" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="2">
         <v>117855</v>
       </c>
@@ -3923,7 +3857,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="146" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="2">
         <v>108772</v>
       </c>
@@ -3931,7 +3865,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="147" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A147" s="2">
         <v>108592</v>
       </c>
@@ -3939,7 +3873,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="148" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="2">
         <v>111876</v>
       </c>
@@ -3947,7 +3881,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="149" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A149" s="2">
         <v>110741</v>
       </c>
@@ -3955,7 +3889,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="150" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A150" s="2">
         <v>107888</v>
       </c>
@@ -3963,7 +3897,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="151" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A151" s="2">
         <v>111436</v>
       </c>
@@ -3971,7 +3905,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="152" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="2">
         <v>111660</v>
       </c>
@@ -3979,7 +3913,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="153" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A153" s="2">
         <v>111441</v>
       </c>
@@ -3987,7 +3921,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="154" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A154" s="2">
         <v>118222</v>
       </c>
@@ -3995,7 +3929,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="155" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A155" s="2">
         <v>110755</v>
       </c>
@@ -4003,7 +3937,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A156" s="2">
         <v>107109</v>
       </c>
@@ -4011,7 +3945,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A157" s="2">
         <v>118304</v>
       </c>
@@ -4019,7 +3953,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="158" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A158" s="2">
         <v>110895</v>
       </c>
@@ -4027,7 +3961,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="159" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A159" s="2">
         <v>111850</v>
       </c>
@@ -4035,7 +3969,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="160" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="2">
         <v>108770</v>
       </c>
@@ -4043,7 +3977,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="161" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A161" s="2">
         <v>107892</v>
       </c>
@@ -4051,7 +3985,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="162" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A162" s="2">
         <v>111440</v>
       </c>
@@ -4059,7 +3993,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="163" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="2">
         <v>111690</v>
       </c>
@@ -4067,7 +4001,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="164" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A164" s="2">
         <v>107537</v>
       </c>
@@ -4075,7 +4009,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="165" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A165" s="2">
         <v>109646</v>
       </c>
@@ -4083,7 +4017,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="166" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A166" s="2">
         <v>109645</v>
       </c>
@@ -4091,7 +4025,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="167" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="2">
         <v>109647</v>
       </c>
@@ -4099,7 +4033,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="168" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A168" s="2">
         <v>105111</v>
       </c>
@@ -4107,7 +4041,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="169" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A169" s="2">
         <v>111182</v>
       </c>
@@ -4115,7 +4049,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="170" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A170" s="2">
         <v>109641</v>
       </c>
@@ -4123,7 +4057,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A171" s="2">
         <v>105705</v>
       </c>
@@ -4131,7 +4065,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="172" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A172" s="2">
         <v>109640</v>
       </c>
@@ -4139,7 +4073,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="173" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="2">
         <v>111330</v>
       </c>
@@ -4147,7 +4081,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="174" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="2">
         <v>108871</v>
       </c>
@@ -4155,7 +4089,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="175" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A175" s="2">
         <v>118166</v>
       </c>
@@ -4163,7 +4097,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="176" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="2">
         <v>118168</v>
       </c>
@@ -4171,7 +4105,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A177" s="2">
         <v>118171</v>
       </c>
@@ -4179,7 +4113,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="178" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A178" s="2">
         <v>118169</v>
       </c>
@@ -4187,7 +4121,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="179" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A179" s="2">
         <v>111813</v>
       </c>
@@ -4195,7 +4129,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="180" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A180" s="2">
         <v>118226</v>
       </c>
@@ -4203,7 +4137,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A181" s="2">
         <v>118253</v>
       </c>
@@ -4211,7 +4145,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A182" s="2">
         <v>118066</v>
       </c>
@@ -4219,7 +4153,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A183" s="5">
         <v>118257</v>
       </c>
@@ -4227,7 +4161,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>118119</v>
       </c>
@@ -4235,7 +4169,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>118187</v>
       </c>
@@ -4243,7 +4177,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>118229</v>
       </c>
@@ -4251,7 +4185,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A187" s="9">
         <v>118419</v>
       </c>
@@ -4259,7 +4193,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A188" s="2">
         <v>118333</v>
       </c>
@@ -4267,7 +4201,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A189" s="2">
         <v>118205</v>
       </c>
@@ -4275,7 +4209,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A190" s="2">
         <v>118113</v>
       </c>
@@ -4283,7 +4217,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A191" s="2">
         <v>118530</v>
       </c>
@@ -4291,7 +4225,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A192" s="2">
         <v>118528</v>
       </c>
@@ -4299,7 +4233,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A193" s="11">
         <v>118200</v>
       </c>
@@ -4307,7 +4241,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A194" s="2">
         <v>107921</v>
       </c>
@@ -4315,7 +4249,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A195" s="2">
         <v>118337</v>
       </c>
@@ -4323,7 +4257,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A196" s="2">
         <v>108961</v>
       </c>
@@ -4331,7 +4265,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A197" s="2">
         <v>105470</v>
       </c>
@@ -4339,7 +4273,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A198" s="2">
         <v>110063</v>
       </c>
@@ -4347,7 +4281,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A199" s="2">
         <v>105368</v>
       </c>
@@ -4355,7 +4289,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="200" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A200" s="2">
         <v>118497</v>
       </c>
@@ -4363,7 +4297,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A201" s="2">
         <v>118620</v>
       </c>
@@ -4371,7 +4305,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="2">
         <v>110841</v>
       </c>
@@ -4379,7 +4313,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="2">
         <v>110563</v>
       </c>
@@ -4387,7 +4321,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A204" s="2">
         <v>120002</v>
       </c>
@@ -4395,7 +4329,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="2">
         <v>124592</v>
       </c>
@@ -4403,7 +4337,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A206" s="2">
         <v>120050</v>
       </c>
@@ -4411,7 +4345,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A207" s="2">
         <v>120098</v>
       </c>
@@ -4419,7 +4353,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A208" s="2">
         <v>122968</v>
       </c>
@@ -4427,7 +4361,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="209" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A209" s="2">
         <v>122967</v>
       </c>
@@ -4435,7 +4369,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="210" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A210" s="2">
         <v>123492</v>
       </c>
@@ -4443,7 +4377,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="211" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A211" s="2">
         <v>123345</v>
       </c>
@@ -4451,7 +4385,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="212" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A212" s="2">
         <v>123343</v>
       </c>
@@ -4459,7 +4393,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="213" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A213" s="2">
         <v>120389</v>
       </c>
@@ -4467,7 +4401,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="214" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A214" s="2">
         <v>123822</v>
       </c>
@@ -4475,7 +4409,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="215" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A215" s="24">
         <v>124487</v>
       </c>
@@ -4483,7 +4417,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="216" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A216" s="13">
         <v>124486</v>
       </c>
@@ -4491,7 +4425,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="217" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A217" s="13">
         <v>121304</v>
       </c>
@@ -4499,7 +4433,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="218" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A218" s="13">
         <v>122673</v>
       </c>
@@ -4507,7 +4441,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="219" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A219" s="13">
         <v>122647</v>
       </c>
@@ -4515,7 +4449,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="220" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A220" s="13">
         <v>123313</v>
       </c>
@@ -4523,7 +4457,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="221" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A221" s="13">
         <v>123012</v>
       </c>
@@ -4531,7 +4465,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="222" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A222" s="13">
         <v>122671</v>
       </c>
@@ -4539,7 +4473,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="223" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A223" s="13">
         <v>122962</v>
       </c>
@@ -4547,7 +4481,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="224" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A224" s="13">
         <v>120285</v>
       </c>
@@ -4555,7 +4489,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A225" s="13">
         <v>121307</v>
       </c>
@@ -4563,7 +4497,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A226" s="13">
         <v>123284</v>
       </c>
@@ -4571,7 +4505,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A227" s="13">
         <v>120028</v>
       </c>
@@ -4579,7 +4513,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A228" s="13">
         <v>120008</v>
       </c>
@@ -4587,7 +4521,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A229" s="13">
         <v>123153</v>
       </c>
@@ -4595,7 +4529,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A230" s="13">
         <v>124624</v>
       </c>
@@ -4603,7 +4537,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="13">
         <v>124594</v>
       </c>
@@ -4611,7 +4545,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="13">
         <v>123084</v>
       </c>
@@ -4619,7 +4553,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A233" s="13">
         <v>124247</v>
       </c>
@@ -4627,7 +4561,7 @@
         <v>505</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="13">
         <v>120339</v>
       </c>
@@ -4635,7 +4569,7 @@
         <v>460</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A235" s="13">
         <v>124248</v>
       </c>
@@ -4643,7 +4577,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A236" s="13">
         <v>124548</v>
       </c>
@@ -4651,7 +4585,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A237" s="13">
         <v>123445</v>
       </c>
@@ -4659,7 +4593,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A238" s="13">
         <v>124246</v>
       </c>
@@ -4667,7 +4601,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A239" s="13">
         <v>122188</v>
       </c>
@@ -4675,7 +4609,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A240" s="13">
         <v>122195</v>
       </c>
@@ -4683,7 +4617,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="241" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A241" s="13">
         <v>122983</v>
       </c>
@@ -4691,7 +4625,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="242" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A242" s="13">
         <v>122984</v>
       </c>
@@ -4699,7 +4633,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="243" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A243" s="13">
         <v>123862</v>
       </c>
@@ -4707,7 +4641,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="244" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A244" s="13">
         <v>122650</v>
       </c>
@@ -4715,7 +4649,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="245" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A245" s="13">
         <v>124433</v>
       </c>
@@ -4723,7 +4657,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="246" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A246" s="13">
         <v>120995</v>
       </c>
@@ -4731,7 +4665,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="247" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A247" s="13">
         <v>123222</v>
       </c>
@@ -4739,7 +4673,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="248" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A248" s="13">
         <v>120240</v>
       </c>
@@ -4747,7 +4681,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="249" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A249" s="13">
         <v>123833</v>
       </c>
@@ -4755,7 +4689,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="250" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A250" s="13">
         <v>124477</v>
       </c>
@@ -4763,7 +4697,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="251" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A251" s="13">
         <v>123344</v>
       </c>
@@ -4771,7 +4705,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="252" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A252" s="13">
         <v>124475</v>
       </c>
@@ -4779,7 +4713,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="253" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A253" s="13">
         <v>121760</v>
       </c>
@@ -4787,7 +4721,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="254" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A254" s="13">
         <v>124476</v>
       </c>
@@ -4795,7 +4729,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="255" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A255" s="13">
         <v>124370</v>
       </c>
@@ -4803,7 +4737,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="256" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A256" s="13">
         <v>121651</v>
       </c>
@@ -4811,7 +4745,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="257" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A257" s="13">
         <v>124371</v>
       </c>
@@ -4819,7 +4753,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="258" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A258" s="13">
         <v>122703</v>
       </c>
@@ -4827,7 +4761,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="259" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A259" s="13">
         <v>123560</v>
       </c>
@@ -4835,7 +4769,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="260" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="13">
         <v>123561</v>
       </c>
@@ -4843,7 +4777,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="261" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="13">
         <v>160052</v>
       </c>
@@ -4851,7 +4785,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="262" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A262" s="13">
         <v>160054</v>
       </c>
@@ -4859,7 +4793,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="263" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="13">
         <v>160051</v>
       </c>
@@ -4867,7 +4801,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="264" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A264" s="14">
         <v>160055</v>
       </c>
@@ -4875,7 +4809,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="265" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A265" s="25">
         <v>1100000</v>
       </c>
@@ -4883,7 +4817,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A266" s="13">
         <v>1100403</v>
       </c>
@@ -4891,7 +4825,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A267" s="9">
         <v>1102700</v>
       </c>
@@ -4899,7 +4833,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="268" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A268" s="2">
         <v>1100401</v>
       </c>
@@ -4907,7 +4841,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="269" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A269" s="2">
         <v>1100402</v>
       </c>
@@ -4915,7 +4849,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="270" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A270" s="2">
         <v>1701535</v>
       </c>
@@ -4923,7 +4857,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="271" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A271" s="2">
         <v>1101350</v>
       </c>
@@ -4931,7 +4865,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="272" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A272" s="2">
         <v>1701510</v>
       </c>
@@ -4939,7 +4873,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="273" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A273" s="2">
         <v>1100051</v>
       </c>
@@ -4947,7 +4881,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="274" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A274" s="2">
         <v>1100050</v>
       </c>
@@ -4955,7 +4889,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="275" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A275" s="2">
         <v>1120001</v>
       </c>
@@ -4963,7 +4897,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="276" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A276" s="2">
         <v>1600050</v>
       </c>
@@ -4971,7 +4905,7 @@
         <v>864</v>
       </c>
     </row>
-    <row r="277" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A277" s="2">
         <v>1150005</v>
       </c>
@@ -4979,7 +4913,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="278" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A278" s="2">
         <v>1150000</v>
       </c>
@@ -4987,7 +4921,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="279" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A279" s="2">
         <v>1150003</v>
       </c>
@@ -4995,7 +4929,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="280" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A280" s="2">
         <v>1103003</v>
       </c>
@@ -5003,7 +4937,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="281" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A281" s="2">
         <v>1103002</v>
       </c>
@@ -5011,7 +4945,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="282" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A282" s="2">
         <v>1103001</v>
       </c>
@@ -5019,7 +4953,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="283" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A283" s="2">
         <v>1101150</v>
       </c>
@@ -5027,7 +4961,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="284" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A284" s="2">
         <v>1101160</v>
       </c>
@@ -5035,7 +4969,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="285" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A285" s="2">
         <v>1101202</v>
       </c>
@@ -5043,7 +4977,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="286" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A286" s="2">
         <v>1101201</v>
       </c>
@@ -5051,7 +4985,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="287" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A287" s="2">
         <v>1602023</v>
       </c>
@@ -5059,7 +4993,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="288" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A288" s="2">
         <v>1150014</v>
       </c>
@@ -5067,7 +5001,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="2">
         <v>1150015</v>
       </c>
@@ -5075,7 +5009,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="2">
         <v>1159305</v>
       </c>
@@ -5083,7 +5017,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A291" s="2">
         <v>1159211</v>
       </c>
@@ -5091,7 +5025,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="2">
         <v>1159320</v>
       </c>
@@ -5099,7 +5033,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A293" s="2">
         <v>1159210</v>
       </c>
@@ -5107,7 +5041,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A294" s="2">
         <v>1159324</v>
       </c>
@@ -5115,7 +5049,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A295" s="2">
         <v>1150315</v>
       </c>
@@ -5123,7 +5057,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A296" s="2">
         <v>1150020</v>
       </c>
@@ -5131,7 +5065,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A297" s="2">
         <v>1150124</v>
       </c>
@@ -5139,7 +5073,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A298" s="2">
         <v>1150032</v>
       </c>
@@ -5147,7 +5081,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A299" s="2">
         <v>1150030</v>
       </c>
@@ -5155,7 +5089,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A300" s="2">
         <v>1150900</v>
       </c>
@@ -5163,7 +5097,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A301" s="2">
         <v>1101800</v>
       </c>
@@ -5171,7 +5105,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A302" s="2">
         <v>1101410</v>
       </c>
@@ -5179,7 +5113,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A303" s="2">
         <v>1101422</v>
       </c>
@@ -5187,7 +5121,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A304" s="2">
         <v>1103005</v>
       </c>
@@ -5195,7 +5129,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A305" s="2">
         <v>1103004</v>
       </c>
@@ -5203,7 +5137,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A306" s="2">
         <v>1103006</v>
       </c>
@@ -5211,7 +5145,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A307" s="2">
         <v>1701530</v>
       </c>
@@ -5219,7 +5153,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A308" s="2">
         <v>1701515</v>
       </c>
@@ -5227,7 +5161,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A309" s="2">
         <v>1101250</v>
       </c>
@@ -5235,7 +5169,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A310" s="2">
         <v>1601002</v>
       </c>
@@ -5243,7 +5177,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A311" s="2">
         <v>1601003</v>
       </c>
@@ -5251,7 +5185,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A312" s="2">
         <v>1601004</v>
       </c>
@@ -5259,7 +5193,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="313" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A313" s="2">
         <v>1601005</v>
       </c>
@@ -5267,7 +5201,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="314" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A314" s="2">
         <v>1150022</v>
       </c>
@@ -5275,7 +5209,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="315" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A315" s="2">
         <v>1159330</v>
       </c>
@@ -5283,7 +5217,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="316" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A316" s="2">
         <v>1150201</v>
       </c>
@@ -5291,7 +5225,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="317" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A317" s="2">
         <v>1150200</v>
       </c>
@@ -5299,7 +5233,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="318" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="2">
         <v>1602025</v>
       </c>
@@ -5307,7 +5241,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="319" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="2">
         <v>1606094</v>
       </c>
@@ -5315,7 +5249,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="320" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A320" s="2">
         <v>1606095</v>
       </c>
@@ -5323,7 +5257,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="2">
         <v>1606097</v>
       </c>
@@ -5331,7 +5265,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A322" s="2">
         <v>1606096</v>
       </c>
@@ -5339,7 +5273,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A323" s="2">
         <v>1150041</v>
       </c>
@@ -5347,7 +5281,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A324" s="9">
         <v>1150043</v>
       </c>
@@ -5355,7 +5289,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A325" s="2">
         <v>1150411</v>
       </c>
@@ -5363,7 +5297,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A326" s="2">
         <v>1159230</v>
       </c>
@@ -5371,7 +5305,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A327" s="2">
         <v>1159201</v>
       </c>
@@ -5379,7 +5313,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A328" s="2">
         <v>1159200</v>
       </c>
@@ -5387,7 +5321,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A329" s="2">
         <v>1159220</v>
       </c>
@@ -5395,7 +5329,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A330" s="2">
         <v>1159323</v>
       </c>
@@ -5403,7 +5337,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A331" s="2">
         <v>1150320</v>
       </c>
@@ -5411,7 +5345,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A332" s="2">
         <v>1150300</v>
       </c>
@@ -5419,7 +5353,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A333" s="2">
         <v>1150050</v>
       </c>
@@ -5427,7 +5361,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A334" s="2">
         <v>1150060</v>
       </c>
@@ -5435,7 +5369,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A335" s="2">
         <v>1150062</v>
       </c>
@@ -5443,7 +5377,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A336" s="2">
         <v>1150061</v>
       </c>
@@ -5451,7 +5385,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A337" s="2">
         <v>1150211</v>
       </c>
@@ -5459,7 +5393,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A338" s="2">
         <v>1150415</v>
       </c>
@@ -5467,7 +5401,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A339" s="2">
         <v>1159325</v>
       </c>
@@ -5475,7 +5409,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A340" s="2">
         <v>1101414</v>
       </c>
@@ -5483,7 +5417,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A341" s="2">
         <v>1101415</v>
       </c>
@@ -5491,7 +5425,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A342" s="2">
         <v>1608000</v>
       </c>
@@ -5499,7 +5433,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A343" s="2">
         <v>1150192</v>
       </c>
@@ -5507,7 +5441,7 @@
         <v>761</v>
       </c>
     </row>
-    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A344" s="2">
         <v>1101300</v>
       </c>
@@ -5515,7 +5449,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A345" s="2">
         <v>1102600</v>
       </c>
@@ -5523,7 +5457,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A346" s="2">
         <v>1151004</v>
       </c>
@@ -5531,7 +5465,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="2">
         <v>1151003</v>
       </c>
@@ -5539,7 +5473,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="2">
         <v>1151002</v>
       </c>
@@ -5547,7 +5481,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A349" s="2">
         <v>1159336</v>
       </c>
@@ -5555,7 +5489,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="2">
         <v>1159215</v>
       </c>
@@ -5563,7 +5497,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A351" s="2">
         <v>1150221</v>
       </c>
@@ -5571,7 +5505,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A352" s="2">
         <v>1159333</v>
       </c>
@@ -5579,7 +5513,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A353" s="2">
         <v>1151102</v>
       </c>
@@ -5587,7 +5521,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A354" s="2">
         <v>1150095</v>
       </c>
@@ -5595,7 +5529,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A355" s="2">
         <v>1150080</v>
       </c>
@@ -5603,7 +5537,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A356" s="2">
         <v>1150417</v>
       </c>
@@ -5611,7 +5545,7 @@
         <v>1158</v>
       </c>
     </row>
-    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A357" s="2">
         <v>1606098</v>
       </c>
@@ -5619,7 +5553,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A358" s="2">
         <v>1606099</v>
       </c>
@@ -5627,7 +5561,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A359" s="2">
         <v>1603001</v>
       </c>
@@ -5635,7 +5569,7 @@
         <v>3055</v>
       </c>
     </row>
-    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A360" s="2">
         <v>1606072</v>
       </c>
@@ -5643,7 +5577,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A361" s="2">
         <v>1650010</v>
       </c>
@@ -5651,7 +5585,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A362" s="2">
         <v>1606011</v>
       </c>
@@ -5659,7 +5593,7 @@
         <v>5121</v>
       </c>
     </row>
-    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A363" s="2">
         <v>1606010</v>
       </c>
@@ -5667,7 +5601,7 @@
         <v>5117</v>
       </c>
     </row>
-    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A364" s="2">
         <v>1150233</v>
       </c>
@@ -5675,7 +5609,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A365" s="2">
         <v>1150420</v>
       </c>
@@ -5683,7 +5617,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A366" s="2">
         <v>1150240</v>
       </c>
@@ -5691,7 +5625,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A367" s="2">
         <v>1150242</v>
       </c>
@@ -5699,7 +5633,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="368" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A368" s="2">
         <v>1150100</v>
       </c>
@@ -5707,7 +5641,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A369" s="2">
         <v>1150413</v>
       </c>
@@ -5715,7 +5649,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A370" s="2">
         <v>1159101</v>
       </c>
@@ -5723,7 +5657,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A371" s="2">
         <v>1159091</v>
       </c>
@@ -5731,7 +5665,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A372" s="2">
         <v>1150101</v>
       </c>
@@ -5739,7 +5673,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A373" s="2">
         <v>1150106</v>
       </c>
@@ -5747,7 +5681,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A374" s="2">
         <v>1150414</v>
       </c>
@@ -5755,7 +5689,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A375" s="2">
         <v>1159111</v>
       </c>
@@ -5763,7 +5697,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="2">
         <v>1159102</v>
       </c>
@@ -5771,7 +5705,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="2">
         <v>1159213</v>
       </c>
@@ -5779,7 +5713,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A378" s="2">
         <v>1159212</v>
       </c>
@@ -5787,7 +5721,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="2">
         <v>1159214</v>
       </c>
@@ -5795,7 +5729,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A380" s="2">
         <v>1151800</v>
       </c>
@@ -5803,7 +5737,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A381" s="2">
         <v>1151801</v>
       </c>
@@ -5811,7 +5745,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A382" s="2">
         <v>1602003</v>
       </c>
@@ -5819,7 +5753,7 @@
         <v>1624</v>
       </c>
     </row>
-    <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A383" s="2">
         <v>1606075</v>
       </c>
@@ -5827,7 +5761,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A384" s="2">
         <v>1606080</v>
       </c>
@@ -5835,7 +5769,7 @@
         <v>2351</v>
       </c>
     </row>
-    <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A385" s="2">
         <v>1656085</v>
       </c>
@@ -5843,7 +5777,7 @@
         <v>2884</v>
       </c>
     </row>
-    <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A386" s="2">
         <v>1150422</v>
       </c>
@@ -5851,7 +5785,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A387" s="2">
         <v>1150423</v>
       </c>
@@ -5859,7 +5793,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A388" s="2">
         <v>1159309</v>
       </c>
@@ -5867,7 +5801,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A389" s="2">
         <v>1159308</v>
       </c>
@@ -5875,7 +5809,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A390" s="2">
         <v>1154902</v>
       </c>
@@ -5883,7 +5817,7 @@
         <v>1836</v>
       </c>
     </row>
-    <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A391" s="2">
         <v>1150425</v>
       </c>
@@ -5891,7 +5825,7 @@
         <v>1881</v>
       </c>
     </row>
-    <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A392" s="2">
         <v>1152800</v>
       </c>
@@ -5899,7 +5833,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A393" s="2">
         <v>1153812</v>
       </c>
@@ -5907,7 +5841,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A394" s="2">
         <v>1153814</v>
       </c>
@@ -5915,7 +5849,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A395" s="2">
         <v>1150153</v>
       </c>
@@ -5923,7 +5857,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A396" s="2">
         <v>1150155</v>
       </c>
@@ -5931,7 +5865,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A397" s="2">
         <v>1150401</v>
       </c>
@@ -5939,7 +5873,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A398" s="2">
         <v>1159010</v>
       </c>
@@ -5947,7 +5881,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A399" s="2">
         <v>1153810</v>
       </c>
@@ -5955,7 +5889,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="400" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A400" s="2">
         <v>1150130</v>
       </c>
@@ -5963,7 +5897,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A401" s="2">
         <v>1150131</v>
       </c>
@@ -5971,7 +5905,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A402" s="2">
         <v>1150132</v>
       </c>
@@ -5979,7 +5913,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A403" s="2">
         <v>1150412</v>
       </c>
@@ -5987,7 +5921,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A404" s="2">
         <v>1150410</v>
       </c>
@@ -5995,7 +5929,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="2">
         <v>1606074</v>
       </c>
@@ -6003,7 +5937,7 @@
         <v>2145</v>
       </c>
     </row>
-    <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="2">
         <v>1656095</v>
       </c>
@@ -6011,7 +5945,7 @@
         <v>3586</v>
       </c>
     </row>
-    <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A407" s="2">
         <v>1153813</v>
       </c>
@@ -6019,7 +5953,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="2">
         <v>1150142</v>
       </c>
@@ -6027,7 +5961,7 @@
         <v>1715</v>
       </c>
     </row>
-    <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A409" s="2">
         <v>1155196</v>
       </c>
@@ -6035,7 +5969,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A410" s="2">
         <v>1159327</v>
       </c>
@@ -6043,7 +5977,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A411" s="2">
         <v>1650100</v>
       </c>
@@ -6051,7 +5985,7 @@
         <v>5038</v>
       </c>
     </row>
-    <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A412" s="2">
         <v>1656096</v>
       </c>
@@ -6059,7 +5993,7 @@
         <v>7011</v>
       </c>
     </row>
-    <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A413" s="2">
         <v>1150161</v>
       </c>
@@ -6067,7 +6001,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A414" s="2">
         <v>1150163</v>
       </c>
@@ -6075,7 +6009,7 @@
         <v>1944</v>
       </c>
     </row>
-    <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A415" s="2">
         <v>1606090</v>
       </c>
@@ -6083,7 +6017,7 @@
         <v>4821</v>
       </c>
     </row>
-    <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A416" s="2">
         <v>1606092</v>
       </c>
@@ -6091,7 +6025,7 @@
         <v>4889</v>
       </c>
     </row>
-    <row r="417" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A417" s="2">
         <v>1150172</v>
       </c>
@@ -6099,7 +6033,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="418" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A418" s="2">
         <v>1150173</v>
       </c>
@@ -6107,7 +6041,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="419" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A419" s="2">
         <v>1154127</v>
       </c>
@@ -6115,7 +6049,7 @@
         <v>4508</v>
       </c>
     </row>
-    <row r="420" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A420" s="2">
         <v>1155000</v>
       </c>
@@ -6123,7 +6057,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="421" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A421" s="2">
         <v>1155010</v>
       </c>
@@ -6131,7 +6065,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="422" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A422" s="2">
         <v>1111120</v>
       </c>
@@ -6139,7 +6073,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="423" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A423" s="2">
         <v>1111080</v>
       </c>
@@ -6147,7 +6081,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="424" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A424" s="2">
         <v>1111050</v>
       </c>
@@ -6155,7 +6089,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="425" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A425" s="2">
         <v>1111060</v>
       </c>
@@ -6163,7 +6097,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="426" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A426" s="2">
         <v>1166060</v>
       </c>
@@ -6171,7 +6105,7 @@
         <v>1278</v>
       </c>
     </row>
-    <row r="427" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A427" s="2">
         <v>1155035</v>
       </c>
@@ -6179,7 +6113,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="428" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A428" s="2">
         <v>1155020</v>
       </c>
@@ -6187,7 +6121,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="429" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A429" s="2">
         <v>1155030</v>
       </c>
@@ -6195,7 +6129,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="430" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A430" s="2">
         <v>1168013</v>
       </c>
@@ -6203,7 +6137,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="431" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A431" s="2">
         <v>1102800</v>
       </c>
@@ -6211,7 +6145,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="432" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A432" s="2">
         <v>1100600</v>
       </c>
@@ -6219,7 +6153,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A433" s="2">
         <v>1701433</v>
       </c>
@@ -6227,7 +6161,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="2">
         <v>1111110</v>
       </c>
@@ -6235,7 +6169,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="2">
         <v>1111010</v>
       </c>
@@ -6243,7 +6177,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A436" s="2">
         <v>1166020</v>
       </c>
@@ -6251,7 +6185,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="2">
         <v>1310004</v>
       </c>
@@ -6259,7 +6193,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A438" s="2">
         <v>1166030</v>
       </c>
@@ -6267,7 +6201,7 @@
         <v>2047</v>
       </c>
     </row>
-    <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A439" s="2">
         <v>1166040</v>
       </c>
@@ -6275,7 +6209,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A440" s="2">
         <v>1310006</v>
       </c>
@@ -6283,7 +6217,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A441" s="2">
         <v>1166044</v>
       </c>
@@ -6291,7 +6225,7 @@
         <v>2362</v>
       </c>
     </row>
-    <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A442" s="2">
         <v>1166042</v>
       </c>
@@ -6299,7 +6233,7 @@
         <v>2711</v>
       </c>
     </row>
-    <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A443" s="2">
         <v>1111090</v>
       </c>
@@ -6307,7 +6241,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A444" s="2">
         <v>1153815</v>
       </c>
@@ -6315,7 +6249,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A445" s="2">
         <v>1101600</v>
       </c>
@@ -6323,7 +6257,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A446" s="2">
         <v>1101601</v>
       </c>
@@ -6331,7 +6265,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A447" s="2">
         <v>1100205</v>
       </c>
@@ -6339,7 +6273,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A448" s="2">
         <v>1102400</v>
       </c>
@@ -6347,7 +6281,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A449" s="2">
         <v>1103200</v>
       </c>
@@ -6355,7 +6289,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A450" s="2">
         <v>1103261</v>
       </c>
@@ -6363,7 +6297,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A451" s="2">
         <v>1111123</v>
       </c>
@@ -6371,7 +6305,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A452" s="2">
         <v>1111100</v>
       </c>
@@ -6379,7 +6313,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A453" s="2">
         <v>1161070</v>
       </c>
@@ -6387,7 +6321,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A454" s="2">
         <v>1153244</v>
       </c>
@@ -6395,7 +6329,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A455" s="2">
         <v>1153242</v>
       </c>
@@ -6403,7 +6337,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A456" s="2">
         <v>1163250</v>
       </c>
@@ -6411,7 +6345,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A457" s="2">
         <v>1155036</v>
       </c>
@@ -6419,7 +6353,7 @@
         <v>2862</v>
       </c>
     </row>
-    <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A458" s="2">
         <v>1163271</v>
       </c>
@@ -6427,7 +6361,7 @@
         <v>2658</v>
       </c>
     </row>
-    <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A459" s="2">
         <v>1153282</v>
       </c>
@@ -6435,7 +6369,7 @@
         <v>2630</v>
       </c>
     </row>
-    <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A460" s="2">
         <v>1155040</v>
       </c>
@@ -6443,7 +6377,7 @@
         <v>3329</v>
       </c>
     </row>
-    <row r="461" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A461" s="2">
         <v>1102500</v>
       </c>
@@ -6451,7 +6385,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="2">
         <v>1103250</v>
       </c>
@@ -6459,7 +6393,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="2">
         <v>1600010</v>
       </c>
@@ -6467,7 +6401,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A464" s="2">
         <v>1100811</v>
       </c>
@@ -6475,7 +6409,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="2">
         <v>1103257</v>
       </c>
@@ -6483,7 +6417,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A466" s="2">
         <v>1103255</v>
       </c>
@@ -6491,7 +6425,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A467" s="2">
         <v>1100215</v>
       </c>
@@ -6499,7 +6433,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="468" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A468" s="2">
         <v>1100040</v>
       </c>
@@ -6507,7 +6441,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="469" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A469" s="2">
         <v>1100844</v>
       </c>
@@ -6515,7 +6449,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A470" s="2">
         <v>1100225</v>
       </c>
@@ -6523,7 +6457,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A471" s="2">
         <v>1100030</v>
       </c>
@@ -6531,7 +6465,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A472" s="2">
         <v>1111122</v>
       </c>
@@ -6539,7 +6473,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="473" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A473" s="2">
         <v>1168012</v>
       </c>
@@ -6547,7 +6481,7 @@
         <v>3822</v>
       </c>
     </row>
-    <row r="474" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A474" s="2">
         <v>1168011</v>
       </c>
@@ -6555,7 +6489,7 @@
         <v>3484</v>
       </c>
     </row>
-    <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A475" s="2">
         <v>1157030</v>
       </c>
@@ -6563,7 +6497,7 @@
         <v>2797</v>
       </c>
     </row>
-    <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A476" s="2">
         <v>1159300</v>
       </c>
@@ -6571,7 +6505,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A477" s="2">
         <v>1157032</v>
       </c>
@@ -6579,7 +6513,7 @@
         <v>3146</v>
       </c>
     </row>
-    <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A478" s="2">
         <v>1154065</v>
       </c>
@@ -6587,7 +6521,7 @@
         <v>3518</v>
       </c>
     </row>
-    <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A479" s="2">
         <v>1320002</v>
       </c>
@@ -6595,7 +6529,7 @@
         <v>3223</v>
       </c>
     </row>
-    <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A480" s="2">
         <v>1152018</v>
       </c>
@@ -6603,7 +6537,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A481" s="2">
         <v>1100235</v>
       </c>
@@ -6611,7 +6545,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A482" s="2">
         <v>1159332</v>
       </c>
@@ -6619,7 +6553,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A483" s="2">
         <v>1159335</v>
       </c>
@@ -6627,7 +6561,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A484" s="2">
         <v>1703003</v>
       </c>
@@ -6635,7 +6569,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A485" s="2">
         <v>1157700</v>
       </c>
@@ -6643,7 +6577,7 @@
         <v>4026</v>
       </c>
     </row>
-    <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A486" s="2">
         <v>1163740</v>
       </c>
@@ -6651,7 +6585,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A487" s="2">
         <v>1163410</v>
       </c>
@@ -6659,7 +6593,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A488" s="2">
         <v>1163620</v>
       </c>
@@ -6667,7 +6601,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A489" s="2">
         <v>1163530</v>
       </c>
@@ -6675,7 +6609,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A490" s="2">
         <v>1168025</v>
       </c>
@@ -6683,7 +6617,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="2">
         <v>1163850</v>
       </c>
@@ -6691,7 +6625,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="2">
         <v>1167010</v>
       </c>
@@ -6699,7 +6633,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="493" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A493" s="2">
         <v>1310002</v>
       </c>
@@ -6707,7 +6641,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="2">
         <v>1157041</v>
       </c>
@@ -6715,7 +6649,7 @@
         <v>2404</v>
       </c>
     </row>
-    <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A495" s="2">
         <v>1155037</v>
       </c>
@@ -6723,7 +6657,7 @@
         <v>2951</v>
       </c>
     </row>
-    <row r="496" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A496" s="2">
         <v>1157040</v>
       </c>
@@ -6731,7 +6665,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A497" s="2">
         <v>1310001</v>
       </c>
@@ -6739,7 +6673,7 @@
         <v>3274</v>
       </c>
     </row>
-    <row r="498" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A498" s="2">
         <v>1156010</v>
       </c>
@@ -6747,7 +6681,7 @@
         <v>4886</v>
       </c>
     </row>
-    <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A499" s="2">
         <v>1181019</v>
       </c>
@@ -6755,7 +6689,7 @@
         <v>4387</v>
       </c>
     </row>
-    <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A500" s="2">
         <v>1182040</v>
       </c>
@@ -6763,7 +6697,7 @@
         <v>6443</v>
       </c>
     </row>
-    <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A501" s="2">
         <v>1181015</v>
       </c>
@@ -6771,7 +6705,7 @@
         <v>2734</v>
       </c>
     </row>
-    <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A502" s="2">
         <v>1181017</v>
       </c>
@@ -6779,7 +6713,7 @@
         <v>4335</v>
       </c>
     </row>
-    <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A503" s="2">
         <v>1181040</v>
       </c>
@@ -6787,7 +6721,7 @@
         <v>3368</v>
       </c>
     </row>
-    <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A504" s="2">
         <v>1168020</v>
       </c>
@@ -6795,7 +6729,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A505" s="2">
         <v>1168010</v>
       </c>
@@ -6803,7 +6737,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A506" s="2">
         <v>6009</v>
       </c>
@@ -6811,7 +6745,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A507" s="2">
         <v>70012</v>
       </c>
@@ -6819,7 +6753,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A508" s="2">
         <v>1016</v>
       </c>
@@ -6827,7 +6761,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A509" s="2">
         <v>65016</v>
       </c>
@@ -6835,7 +6769,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A510" s="2">
         <v>70016</v>
       </c>
@@ -6843,7 +6777,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A511" s="2">
         <v>14175</v>
       </c>
@@ -6851,7 +6785,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A512" s="18" t="s">
         <v>0</v>
       </c>
@@ -6859,7 +6793,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="513" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A513" s="2">
         <v>130024</v>
       </c>
@@ -6867,7 +6801,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A514" s="2">
         <v>19524</v>
       </c>
@@ -6875,7 +6809,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A515" s="18" t="s">
         <v>1</v>
       </c>
@@ -6883,7 +6817,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A516" s="2">
         <v>13188</v>
       </c>
@@ -6891,7 +6825,7 @@
         <v>3798</v>
       </c>
     </row>
-    <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A517" s="18" t="s">
         <v>2</v>
       </c>
@@ -6899,7 +6833,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A518" s="18" t="s">
         <v>3</v>
       </c>
@@ -6907,7 +6841,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A519" s="18" t="s">
         <v>4</v>
       </c>
@@ -6915,7 +6849,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="520" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="18" t="s">
         <v>5</v>
       </c>
@@ -6923,7 +6857,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="18" t="s">
         <v>6</v>
       </c>
@@ -6931,7 +6865,7 @@
         <v>1801</v>
       </c>
     </row>
-    <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A522" s="18" t="s">
         <v>7</v>
       </c>
@@ -6939,7 +6873,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="18" t="s">
         <v>8</v>
       </c>
@@ -6947,7 +6881,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A524" s="18" t="s">
         <v>9</v>
       </c>
@@ -6955,7 +6889,7 @@
         <v>2550</v>
       </c>
     </row>
-    <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A525" s="18" t="s">
         <v>10</v>
       </c>
@@ -6963,7 +6897,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A526" s="18" t="s">
         <v>11</v>
       </c>
@@ -6971,7 +6905,7 @@
         <v>5342</v>
       </c>
     </row>
-    <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A527" s="2">
         <v>29525</v>
       </c>
@@ -6979,7 +6913,7 @@
         <v>5622</v>
       </c>
     </row>
-    <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A528" s="2">
         <v>29529</v>
       </c>
@@ -6987,7 +6921,7 @@
         <v>4108</v>
       </c>
     </row>
-    <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A529" s="2">
         <v>7500412</v>
       </c>
@@ -6995,7 +6929,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A530" s="2">
         <v>7500413</v>
       </c>
@@ -7003,7 +6937,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A531" s="2">
         <v>7500476</v>
       </c>
@@ -7011,7 +6945,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A532" s="2">
         <v>8004516</v>
       </c>
@@ -7019,7 +6953,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A533" s="2">
         <v>8004858</v>
       </c>
@@ -7027,7 +6961,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="534" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A534" s="2">
         <v>7516056</v>
       </c>
@@ -7035,13 +6969,13 @@
         <v>544</v>
       </c>
     </row>
-    <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A535" s="2">
         <v>8004674</v>
       </c>
       <c r="B535" s="19"/>
     </row>
-    <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A536" s="2">
         <v>7516006</v>
       </c>
@@ -7049,7 +6983,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A537" s="2">
         <v>7500178</v>
       </c>
@@ -7057,7 +6991,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A538" s="2">
         <v>7500584</v>
       </c>
@@ -7065,7 +6999,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A539" s="2">
         <v>7500589</v>
       </c>
@@ -7073,7 +7007,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="540" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A540" s="2">
         <v>7500151</v>
       </c>
@@ -7081,7 +7015,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A541" s="2">
         <v>7500149</v>
       </c>
@@ -7089,7 +7023,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A542" s="2">
         <v>7500148</v>
       </c>
@@ -7097,7 +7031,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A543" s="2">
         <v>7500150</v>
       </c>
@@ -7105,7 +7039,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A544" s="2">
         <v>8004903</v>
       </c>
@@ -7113,7 +7047,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A545" s="2">
         <v>3166</v>
       </c>
@@ -7121,15 +7055,15 @@
         <v>176</v>
       </c>
     </row>
-    <row r="546" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A546" s="2">
         <v>3205</v>
       </c>
-      <c r="B546" s="26" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B546" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A547" s="20">
         <v>3147</v>
       </c>
@@ -7137,7 +7071,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A548" s="2">
         <v>104058</v>
       </c>
@@ -7145,7 +7079,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="20">
         <v>3148</v>
       </c>
@@ -7153,7 +7087,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="2">
         <v>4214</v>
       </c>
@@ -7161,7 +7095,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A551" s="2">
         <v>103269</v>
       </c>
@@ -7169,7 +7103,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="2">
         <v>2802</v>
       </c>
@@ -7177,7 +7111,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A553" s="2">
         <v>2800</v>
       </c>
@@ -7185,7 +7119,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A554" s="18" t="s">
         <v>12</v>
       </c>
@@ -7193,7 +7127,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A555" s="18" t="s">
         <v>13</v>
       </c>
@@ -7201,7 +7135,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A556" s="18" t="s">
         <v>14</v>
       </c>
@@ -7209,7 +7143,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A557" s="18" t="s">
         <v>15</v>
       </c>
@@ -7217,7 +7151,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A558" s="18" t="s">
         <v>16</v>
       </c>
@@ -7225,7 +7159,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A559" s="18" t="s">
         <v>17</v>
       </c>
@@ -7233,7 +7167,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A560" s="18" t="s">
         <v>18</v>
       </c>
@@ -7241,7 +7175,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A561" s="18" t="s">
         <v>19</v>
       </c>
@@ -7249,7 +7183,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A562" s="18" t="s">
         <v>20</v>
       </c>
@@ -7257,7 +7191,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A563" s="18" t="s">
         <v>21</v>
       </c>
@@ -7265,7 +7199,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A564" s="18" t="s">
         <v>22</v>
       </c>
@@ -7273,7 +7207,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="565" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A565" s="18" t="s">
         <v>23</v>
       </c>
@@ -7281,7 +7215,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A566" s="18" t="s">
         <v>24</v>
       </c>
@@ -7289,7 +7223,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A567" s="18" t="s">
         <v>25</v>
       </c>
@@ -7297,7 +7231,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A568" s="18" t="s">
         <v>26</v>
       </c>
@@ -7305,7 +7239,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A569" s="18" t="s">
         <v>27</v>
       </c>
@@ -7313,7 +7247,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A570" s="18" t="s">
         <v>28</v>
       </c>
@@ -7321,7 +7255,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A571" s="18" t="s">
         <v>29</v>
       </c>
@@ -7329,7 +7263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A572" s="18" t="s">
         <v>30</v>
       </c>
@@ -7337,7 +7271,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A573" s="18" t="s">
         <v>31</v>
       </c>
@@ -7345,7 +7279,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A574" s="18" t="s">
         <v>32</v>
       </c>
@@ -7353,7 +7287,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A575" s="18" t="s">
         <v>33</v>
       </c>
@@ -7361,7 +7295,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A576" s="18" t="s">
         <v>34</v>
       </c>
@@ -7369,7 +7303,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A577" s="18" t="s">
         <v>35</v>
       </c>
@@ -7377,7 +7311,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="18" t="s">
         <v>36</v>
       </c>
@@ -7385,7 +7319,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="18" t="s">
         <v>37</v>
       </c>
@@ -7393,7 +7327,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A580" s="18" t="s">
         <v>38</v>
       </c>
@@ -7401,7 +7335,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="18" t="s">
         <v>39</v>
       </c>
@@ -7409,7 +7343,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A582" s="18" t="s">
         <v>40</v>
       </c>
@@ -7417,7 +7351,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A583" s="18" t="s">
         <v>41</v>
       </c>
@@ -7425,7 +7359,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A584" s="18" t="s">
         <v>42</v>
       </c>
@@ -7433,7 +7367,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A585" s="18" t="s">
         <v>43</v>
       </c>
@@ -7441,7 +7375,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A586" s="18" t="s">
         <v>44</v>
       </c>
@@ -7449,7 +7383,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A587" s="18" t="s">
         <v>45</v>
       </c>
@@ -7457,7 +7391,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A588" s="18" t="s">
         <v>46</v>
       </c>
@@ -7465,7 +7399,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A589" s="18" t="s">
         <v>47</v>
       </c>
@@ -7473,7 +7407,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A590" s="18" t="s">
         <v>48</v>
       </c>
@@ -7481,7 +7415,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A591" s="18" t="s">
         <v>49</v>
       </c>
@@ -7489,7 +7423,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A592" s="18" t="s">
         <v>50</v>
       </c>
@@ -7497,7 +7431,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A593" s="18" t="s">
         <v>51</v>
       </c>
@@ -7505,7 +7439,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A594" s="18" t="s">
         <v>52</v>
       </c>
@@ -7513,7 +7447,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A595" s="18" t="s">
         <v>53</v>
       </c>
@@ -7521,7 +7455,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A596" s="18" t="s">
         <v>54</v>
       </c>
@@ -7529,7 +7463,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A597" s="18" t="s">
         <v>55</v>
       </c>
@@ -7537,7 +7471,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A598" s="18" t="s">
         <v>56</v>
       </c>
@@ -7545,7 +7479,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A599" s="18" t="s">
         <v>57</v>
       </c>
@@ -7553,7 +7487,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A600" s="18" t="s">
         <v>58</v>
       </c>
@@ -7561,7 +7495,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A601" s="18" t="s">
         <v>59</v>
       </c>
@@ -7569,7 +7503,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A602" s="18" t="s">
         <v>60</v>
       </c>
@@ -7577,7 +7511,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A603" s="18" t="s">
         <v>61</v>
       </c>
@@ -7585,7 +7519,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="604" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A604" s="18" t="s">
         <v>62</v>
       </c>
@@ -7593,7 +7527,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="605" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A605" s="18" t="s">
         <v>63</v>
       </c>
@@ -7601,7 +7535,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="606" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A606" s="18" t="s">
         <v>64</v>
       </c>
@@ -7609,7 +7543,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="607" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="18" t="s">
         <v>65</v>
       </c>
@@ -7617,7 +7551,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="608" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="18" t="s">
         <v>66</v>
       </c>
@@ -7625,7 +7559,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="609" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A609" s="18" t="s">
         <v>67</v>
       </c>
@@ -7633,7 +7567,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="610" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="18" t="s">
         <v>68</v>
       </c>
@@ -7641,7 +7575,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="611" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A611" s="18" t="s">
         <v>69</v>
       </c>
@@ -7649,7 +7583,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="612" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A612" s="18" t="s">
         <v>70</v>
       </c>
@@ -7657,7 +7591,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="613" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A613" s="18" t="s">
         <v>71</v>
       </c>
@@ -7665,7 +7599,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="614" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A614" s="18" t="s">
         <v>72</v>
       </c>
@@ -7673,7 +7607,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="615" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A615" s="18" t="s">
         <v>73</v>
       </c>
@@ -7681,7 +7615,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="616" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A616" s="18" t="s">
         <v>74</v>
       </c>
@@ -7689,7 +7623,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="617" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A617" s="2">
         <v>6053</v>
       </c>
@@ -7697,7 +7631,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="618" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A618" s="2">
         <v>6056</v>
       </c>
@@ -7705,7 +7639,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="619" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A619" s="2">
         <v>6059</v>
       </c>
@@ -7713,7 +7647,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="620" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A620" s="2">
         <v>6062</v>
       </c>
@@ -7721,7 +7655,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="621" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A621" s="2">
         <v>6065</v>
       </c>
@@ -7729,7 +7663,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="622" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A622" s="2">
         <v>6071</v>
       </c>
@@ -7737,7 +7671,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="623" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A623" s="2">
         <v>6074</v>
       </c>
@@ -7745,7 +7679,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="624" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A624" s="2">
         <v>6077</v>
       </c>
@@ -7753,7 +7687,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="625" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A625" s="2">
         <v>6080</v>
       </c>
@@ -7761,7 +7695,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="626" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A626" s="2">
         <v>6083</v>
       </c>
@@ -7769,7 +7703,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="627" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A627" s="2">
         <v>6086</v>
       </c>
@@ -7777,7 +7711,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="628" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A628" s="2">
         <v>6089</v>
       </c>
@@ -7785,7 +7719,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="629" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A629" s="2">
         <v>6098</v>
       </c>
@@ -7793,7 +7727,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="630" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="2">
         <v>6101</v>
       </c>
@@ -7801,7 +7735,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="631" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="2">
         <v>6107</v>
       </c>
@@ -7809,7 +7743,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="632" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="2">
         <v>6535</v>
       </c>
@@ -7817,7 +7751,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="633" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A633" s="2">
         <v>6555</v>
       </c>
@@ -7825,7 +7759,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="634" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="2">
         <v>6567</v>
       </c>
@@ -7833,7 +7767,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="635" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A635" s="2">
         <v>6569</v>
       </c>
@@ -7841,7 +7775,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="636" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="2">
         <v>6571</v>
       </c>
@@ -7849,7 +7783,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="637" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="2">
         <v>6607</v>
       </c>
@@ -7857,7 +7791,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A638" s="2">
         <v>6623</v>
       </c>
@@ -7865,7 +7799,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="2">
         <v>6627</v>
       </c>
@@ -7873,7 +7807,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A640" s="2">
         <v>6635</v>
       </c>
@@ -7881,7 +7815,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A641" s="2">
         <v>6731</v>
       </c>
@@ -7889,7 +7823,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A642" s="2">
         <v>6747</v>
       </c>
@@ -7897,7 +7831,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A643" s="2">
         <v>6787</v>
       </c>
@@ -7905,7 +7839,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A644" s="2">
         <v>6795</v>
       </c>
@@ -7913,7 +7847,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A645" s="2">
         <v>6811</v>
       </c>
@@ -7921,15 +7855,15 @@
         <v>85</v>
       </c>
     </row>
-    <row r="646" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A646" s="2">
         <v>6819</v>
       </c>
-      <c r="B646" s="26" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B646" s="27" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A647" s="2">
         <v>4892</v>
       </c>
@@ -7937,7 +7871,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A648" s="2">
         <v>5029</v>
       </c>
@@ -7945,7 +7879,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A649" s="2">
         <v>5050</v>
       </c>
@@ -7953,7 +7887,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A650" s="2">
         <v>5030</v>
       </c>
@@ -7961,7 +7895,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A651" s="2">
         <v>5031</v>
       </c>
@@ -7969,7 +7903,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A652" s="2">
         <v>5035</v>
       </c>
@@ -7977,7 +7911,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A653" s="2">
         <v>5041</v>
       </c>
@@ -7985,7 +7919,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A654" s="2">
         <v>5048</v>
       </c>
@@ -7993,7 +7927,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A655" s="2">
         <v>5045</v>
       </c>
@@ -8001,7 +7935,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A656" s="2">
         <v>5034</v>
       </c>
@@ -8009,7 +7943,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="657" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A657" s="2">
         <v>5036</v>
       </c>
@@ -8017,7 +7951,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="658" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A658" s="2">
         <v>5042</v>
       </c>
@@ -8025,7 +7959,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="659" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A659" s="2">
         <v>5047</v>
       </c>
@@ -8033,7 +7967,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="660" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A660" s="2">
         <v>5049</v>
       </c>
@@ -8041,7 +7975,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="661" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A661" s="2">
         <v>5005</v>
       </c>
@@ -8049,7 +7983,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="662" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A662" s="2">
         <v>5015</v>
       </c>
@@ -8057,7 +7991,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="663" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A663" s="2">
         <v>5007</v>
       </c>
@@ -8065,7 +7999,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="664" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A664" s="2">
         <v>5008</v>
       </c>
@@ -8073,7 +8007,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="665" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="2">
         <v>6241</v>
       </c>
@@ -8081,7 +8015,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="666" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="2">
         <v>6259</v>
       </c>
@@ -8089,7 +8023,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="667" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A667" s="2">
         <v>6249</v>
       </c>
@@ -8097,7 +8031,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="668" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="2">
         <v>5555</v>
       </c>
@@ -8105,7 +8039,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="669" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A669" s="2">
         <v>5535</v>
       </c>
@@ -8113,7 +8047,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="670" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A670" s="2">
         <v>5567</v>
       </c>
@@ -8121,7 +8055,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="671" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A671" s="2">
         <v>5527</v>
       </c>
@@ -8129,7 +8063,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="672" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A672" s="2">
         <v>5563</v>
       </c>
@@ -8137,7 +8071,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A673" s="2">
         <v>4452</v>
       </c>
@@ -8145,7 +8079,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A674" s="2">
         <v>4359</v>
       </c>
@@ -8153,7 +8087,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A675" s="2">
         <v>4360</v>
       </c>
@@ -8161,7 +8095,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A676" s="2">
         <v>4361</v>
       </c>
@@ -8169,7 +8103,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A677" s="2">
         <v>4362</v>
       </c>
@@ -8177,7 +8111,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A678" s="2">
         <v>4358</v>
       </c>
@@ -8185,7 +8119,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A679" s="2">
         <v>4453</v>
       </c>
@@ -8193,7 +8127,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A680" s="2">
         <v>4449</v>
       </c>
@@ -8201,7 +8135,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A681" s="2">
         <v>4363</v>
       </c>
@@ -8209,7 +8143,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A682" s="2">
         <v>4364</v>
       </c>
@@ -8217,7 +8151,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A683" s="2">
         <v>4610</v>
       </c>
@@ -8225,7 +8159,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A684" s="2">
         <v>4457</v>
       </c>
@@ -8233,7 +8167,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A685" s="2">
         <v>4613</v>
       </c>
@@ -8241,7 +8175,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="2">
         <v>3356</v>
       </c>
@@ -8249,7 +8183,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A687" s="2">
         <v>3305</v>
       </c>
@@ -8257,7 +8191,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A688" s="2">
         <v>3392</v>
       </c>
@@ -8265,7 +8199,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A689" s="2">
         <v>3445</v>
       </c>
@@ -8273,7 +8207,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A690" s="2">
         <v>3355</v>
       </c>
@@ -8281,7 +8215,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A691" s="2">
         <v>3453</v>
       </c>
@@ -8289,7 +8223,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A692" s="2">
         <v>3286</v>
       </c>
@@ -8297,7 +8231,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A693" s="2">
         <v>3450</v>
       </c>
@@ -8305,7 +8239,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="2">
         <v>3357</v>
       </c>
@@ -8313,7 +8247,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="2">
         <v>3397</v>
       </c>
@@ -8321,7 +8255,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A696" s="2">
         <v>3393</v>
       </c>
@@ -8329,15 +8263,15 @@
         <v>111</v>
       </c>
     </row>
-    <row r="697" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="2">
         <v>3421</v>
       </c>
-      <c r="B697" s="26" t="s">
+      <c r="B697" s="27" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A698" s="2">
         <v>3426</v>
       </c>
@@ -8345,7 +8279,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A699" s="2">
         <v>3446</v>
       </c>
@@ -8353,7 +8287,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A700" s="2">
         <v>3458</v>
       </c>
@@ -8361,7 +8295,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A701" s="2">
         <v>3464</v>
       </c>
@@ -8369,7 +8303,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A702" s="2">
         <v>3478</v>
       </c>
@@ -8377,7 +8311,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A703" s="2">
         <v>6662</v>
       </c>
@@ -8385,7 +8319,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A704" s="2">
         <v>3461</v>
       </c>
@@ -8393,7 +8327,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="705" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A705" s="2">
         <v>3477</v>
       </c>
@@ -8401,7 +8335,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="706" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A706" s="2">
         <v>3472</v>
       </c>
@@ -8409,7 +8343,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="707" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A707" s="2">
         <v>3176</v>
       </c>
@@ -8417,7 +8351,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="708" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A708" s="2">
         <v>3206</v>
       </c>
@@ -8425,7 +8359,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="709" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A709" s="2">
         <v>3239</v>
       </c>
@@ -8433,7 +8367,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="710" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A710" s="2">
         <v>3208</v>
       </c>
@@ -8441,7 +8375,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="711" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A711" s="2">
         <v>3241</v>
       </c>
@@ -8449,7 +8383,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="712" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A712" s="2">
         <v>3237</v>
       </c>
@@ -8457,7 +8391,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="713" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A713" s="2">
         <v>3269</v>
       </c>
@@ -8465,7 +8399,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="714" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A714" s="2">
         <v>3303</v>
       </c>
@@ -8473,7 +8407,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="715" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A715" s="2">
         <v>3352</v>
       </c>
@@ -8481,7 +8415,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="716" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A716" s="2">
         <v>3238</v>
       </c>
@@ -8489,7 +8423,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="717" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A717" s="2">
         <v>3347</v>
       </c>
@@ -8497,7 +8431,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="718" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A718" s="18" t="s">
         <v>75</v>
       </c>
@@ -8505,7 +8439,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="719" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A719" s="18" t="s">
         <v>76</v>
       </c>
@@ -8513,7 +8447,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="720" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A720" s="18" t="s">
         <v>77</v>
       </c>
@@ -8521,7 +8455,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="721" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A721" s="18" t="s">
         <v>78</v>
       </c>
@@ -8529,7 +8463,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="722" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A722" s="18" t="s">
         <v>79</v>
       </c>
@@ -8537,7 +8471,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="723" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A723" s="18" t="s">
         <v>80</v>
       </c>
@@ -8545,7 +8479,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="724" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A724" s="18" t="s">
         <v>81</v>
       </c>
@@ -8553,7 +8487,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="725" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A725" s="18" t="s">
         <v>82</v>
       </c>
@@ -8561,7 +8495,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="726" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A726" s="18" t="s">
         <v>83</v>
       </c>
@@ -8569,7 +8503,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="727" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A727" s="18" t="s">
         <v>84</v>
       </c>
@@ -8577,7 +8511,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="728" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A728" s="18" t="s">
         <v>85</v>
       </c>
@@ -8585,7 +8519,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="729" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A729" s="18" t="s">
         <v>86</v>
       </c>
@@ -8593,7 +8527,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="730" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A730" s="18" t="s">
         <v>87</v>
       </c>
@@ -8601,7 +8535,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="731" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A731" s="18" t="s">
         <v>88</v>
       </c>
@@ -8609,7 +8543,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="732" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A732" s="18" t="s">
         <v>89</v>
       </c>
@@ -8617,7 +8551,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="733" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A733" s="18" t="s">
         <v>90</v>
       </c>
@@ -8625,7 +8559,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="734" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A734" s="18" t="s">
         <v>91</v>
       </c>
@@ -8633,7 +8567,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="735" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A735" s="18" t="s">
         <v>92</v>
       </c>
@@ -8641,7 +8575,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="736" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A736" s="18" t="s">
         <v>93</v>
       </c>
@@ -8649,7 +8583,7 @@
         <v>2791</v>
       </c>
     </row>
-    <row r="737" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A737" s="18" t="s">
         <v>94</v>
       </c>
@@ -8657,7 +8591,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="738" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A738" s="18" t="s">
         <v>95</v>
       </c>
@@ -8665,7 +8599,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="739" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A739" s="18" t="s">
         <v>96</v>
       </c>
@@ -8673,7 +8607,7 @@
         <v>4653</v>
       </c>
     </row>
-    <row r="740" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A740" s="18" t="s">
         <v>97</v>
       </c>
@@ -8681,7 +8615,7 @@
         <v>4365</v>
       </c>
     </row>
-    <row r="741" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A741" s="18" t="s">
         <v>98</v>
       </c>
@@ -8689,7 +8623,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="742" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A742" s="18" t="s">
         <v>99</v>
       </c>
@@ -8697,7 +8631,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="743" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A743" s="18" t="s">
         <v>100</v>
       </c>
@@ -8705,7 +8639,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="744" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A744" s="18" t="s">
         <v>101</v>
       </c>
@@ -8713,7 +8647,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="745" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A745" s="18" t="s">
         <v>102</v>
       </c>
@@ -8721,7 +8655,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="746" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A746" s="18" t="s">
         <v>103</v>
       </c>
@@ -8729,7 +8663,7 @@
         <v>2476</v>
       </c>
     </row>
-    <row r="747" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A747" s="18" t="s">
         <v>104</v>
       </c>
@@ -8737,7 +8671,7 @@
         <v>2105</v>
       </c>
     </row>
-    <row r="748" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A748" s="18" t="s">
         <v>105</v>
       </c>
@@ -8745,15 +8679,15 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="749" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A749" s="18" t="s">
         <v>106</v>
       </c>
       <c r="B749" s="26" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="750" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="750" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A750" s="18" t="s">
         <v>107</v>
       </c>
@@ -8761,7 +8695,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="751" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A751" s="18" t="s">
         <v>108</v>
       </c>
@@ -8769,7 +8703,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="752" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A752" s="18" t="s">
         <v>109</v>
       </c>
@@ -8777,7 +8711,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="753" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A753" s="18" t="s">
         <v>110</v>
       </c>
@@ -8785,7 +8719,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="754" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A754" s="18" t="s">
         <v>111</v>
       </c>
@@ -8793,7 +8727,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="755" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A755" s="18" t="s">
         <v>112</v>
       </c>
@@ -8801,7 +8735,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="756" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A756" s="18" t="s">
         <v>113</v>
       </c>
@@ -8809,7 +8743,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="757" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A757" s="18" t="s">
         <v>114</v>
       </c>
@@ -8817,7 +8751,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="758" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A758" s="18" t="s">
         <v>115</v>
       </c>
@@ -8825,7 +8759,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="759" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A759" s="18" t="s">
         <v>116</v>
       </c>
@@ -8833,7 +8767,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="760" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A760" s="18" t="s">
         <v>117</v>
       </c>
@@ -8841,7 +8775,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="761" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A761" s="18" t="s">
         <v>118</v>
       </c>
@@ -8849,7 +8783,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="762" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A762" s="18" t="s">
         <v>119</v>
       </c>
@@ -8857,7 +8791,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="763" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A763" s="18" t="s">
         <v>120</v>
       </c>
@@ -8865,7 +8799,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="764" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A764" s="18" t="s">
         <v>121</v>
       </c>
@@ -8873,7 +8807,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="765" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A765" s="18" t="s">
         <v>122</v>
       </c>
@@ -8881,7 +8815,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="766" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A766" s="18" t="s">
         <v>123</v>
       </c>
@@ -8889,7 +8823,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="767" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A767" s="18" t="s">
         <v>124</v>
       </c>
@@ -8897,7 +8831,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="768" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A768" s="18" t="s">
         <v>125</v>
       </c>
@@ -8905,7 +8839,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="769" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A769" s="18" t="s">
         <v>126</v>
       </c>
@@ -8913,7 +8847,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="770" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A770" s="18" t="s">
         <v>127</v>
       </c>
@@ -8921,7 +8855,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="771" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A771" s="18" t="s">
         <v>128</v>
       </c>
@@ -8929,7 +8863,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="772" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A772" s="18" t="s">
         <v>129</v>
       </c>
@@ -8937,7 +8871,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="773" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A773" s="18" t="s">
         <v>130</v>
       </c>
@@ -8945,7 +8879,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="774" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A774" s="18" t="s">
         <v>131</v>
       </c>
@@ -8953,7 +8887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="775" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A775" s="18" t="s">
         <v>132</v>
       </c>
@@ -8961,7 +8895,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="776" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A776" s="18" t="s">
         <v>133</v>
       </c>
@@ -8969,7 +8903,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="777" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A777" s="18" t="s">
         <v>134</v>
       </c>
@@ -8977,7 +8911,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="778" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A778" s="18" t="s">
         <v>135</v>
       </c>
@@ -8985,7 +8919,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="779" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A779" s="18" t="s">
         <v>136</v>
       </c>
@@ -8993,7 +8927,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="780" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A780" s="18" t="s">
         <v>137</v>
       </c>
@@ -9001,7 +8935,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="781" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A781" s="18" t="s">
         <v>138</v>
       </c>
@@ -9009,7 +8943,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="782" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A782" s="18" t="s">
         <v>139</v>
       </c>
@@ -9017,7 +8951,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="783" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A783" s="18" t="s">
         <v>140</v>
       </c>
@@ -9025,7 +8959,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="784" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A784" s="18" t="s">
         <v>141</v>
       </c>
@@ -9033,7 +8967,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="785" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A785" s="18" t="s">
         <v>142</v>
       </c>
@@ -9041,7 +8975,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="786" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A786" s="18" t="s">
         <v>183</v>
       </c>
@@ -9049,7 +8983,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="787" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A787" s="18" t="s">
         <v>143</v>
       </c>
@@ -9057,7 +8991,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="788" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A788" s="18" t="s">
         <v>144</v>
       </c>
@@ -9065,7 +8999,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="789" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A789" s="23" t="s">
         <v>184</v>
       </c>
@@ -9073,7 +9007,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="790" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A790" s="18" t="s">
         <v>145</v>
       </c>
@@ -9081,7 +9015,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="791" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A791" s="18" t="s">
         <v>146</v>
       </c>
@@ -9089,7 +9023,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="792" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A792" s="18" t="s">
         <v>147</v>
       </c>
@@ -9097,7 +9031,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="793" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A793" s="18" t="s">
         <v>148</v>
       </c>
@@ -9105,7 +9039,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="794" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A794" s="18" t="s">
         <v>149</v>
       </c>
@@ -9113,7 +9047,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="795" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A795" s="18" t="s">
         <v>150</v>
       </c>
@@ -9121,7 +9055,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="796" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A796" s="18" t="s">
         <v>151</v>
       </c>
@@ -9129,7 +9063,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="797" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A797" s="18" t="s">
         <v>152</v>
       </c>
@@ -9137,7 +9071,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="798" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A798" s="18" t="s">
         <v>153</v>
       </c>
@@ -9145,7 +9079,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="799" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A799" s="18" t="s">
         <v>154</v>
       </c>
@@ -9153,7 +9087,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="800" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A800" s="18" t="s">
         <v>155</v>
       </c>
@@ -9161,7 +9095,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="801" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A801" s="18" t="s">
         <v>156</v>
       </c>
@@ -9169,7 +9103,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="802" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A802" s="18" t="s">
         <v>157</v>
       </c>
@@ -9177,15 +9111,15 @@
         <v>579</v>
       </c>
     </row>
-    <row r="803" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:2" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A803" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="B803" s="26" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="804" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B803" s="27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="804" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A804" s="18" t="s">
         <v>159</v>
       </c>
@@ -9193,7 +9127,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="805" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A805" s="18" t="s">
         <v>160</v>
       </c>
@@ -9201,7 +9135,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="806" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A806" s="18" t="s">
         <v>161</v>
       </c>
@@ -9209,7 +9143,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="807" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A807" s="18" t="s">
         <v>162</v>
       </c>
@@ -9217,7 +9151,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="808" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A808" s="18" t="s">
         <v>163</v>
       </c>
@@ -9225,7 +9159,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="809" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A809" s="18" t="s">
         <v>164</v>
       </c>
@@ -9233,7 +9167,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="810" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A810" s="18" t="s">
         <v>165</v>
       </c>
@@ -9241,7 +9175,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="811" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A811" s="18" t="s">
         <v>166</v>
       </c>
@@ -9249,7 +9183,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="812" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A812" s="18" t="s">
         <v>167</v>
       </c>
@@ -9257,7 +9191,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="813" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A813" s="18" t="s">
         <v>168</v>
       </c>
@@ -9265,7 +9199,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="814" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A814" s="18" t="s">
         <v>169</v>
       </c>
@@ -9273,7 +9207,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="815" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A815" s="18" t="s">
         <v>170</v>
       </c>
@@ -9281,7 +9215,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="816" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A816" s="18" t="s">
         <v>171</v>
       </c>
@@ -9289,7 +9223,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="817" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A817" s="18" t="s">
         <v>172</v>
       </c>
@@ -9297,7 +9231,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="818" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A818" s="18" t="s">
         <v>173</v>
       </c>
@@ -9305,7 +9239,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="819" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A819" s="18" t="s">
         <v>174</v>
       </c>
@@ -9313,7 +9247,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="820" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A820" s="18" t="s">
         <v>175</v>
       </c>
@@ -9321,7 +9255,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="821" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A821" s="18" t="s">
         <v>185</v>
       </c>
@@ -9329,7 +9263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="822" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A822" s="18" t="s">
         <v>176</v>
       </c>
@@ -9337,7 +9271,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="823" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A823" s="18" t="s">
         <v>177</v>
       </c>
@@ -9345,7 +9279,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="824" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A824" s="18" t="s">
         <v>178</v>
       </c>
@@ -9353,7 +9287,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="825" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A825" s="18" t="s">
         <v>186</v>
       </c>
@@ -9361,7 +9295,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="826" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A826" s="18" t="s">
         <v>179</v>
       </c>
@@ -9369,7 +9303,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="827" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A827" s="18" t="s">
         <v>180</v>
       </c>
@@ -9377,7 +9311,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="828" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A828" s="18" t="s">
         <v>181</v>
       </c>
@@ -9385,7 +9319,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="829" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A829" s="18" t="s">
         <v>182</v>
       </c>
@@ -9393,7 +9327,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="830" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A830" s="18" t="s">
         <v>113</v>
       </c>
@@ -9401,7 +9335,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="831" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A831" s="18" t="s">
         <v>114</v>
       </c>
@@ -9409,7 +9343,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="832" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A832" s="18" t="s">
         <v>115</v>
       </c>
@@ -9417,7 +9351,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="833" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A833" s="18" t="s">
         <v>116</v>
       </c>
@@ -9425,7 +9359,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="834" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A834" s="18" t="s">
         <v>117</v>
       </c>
@@ -9433,7 +9367,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="835" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A835" s="18" t="s">
         <v>118</v>
       </c>
@@ -9441,7 +9375,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="836" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A836" s="18" t="s">
         <v>119</v>
       </c>
@@ -9449,7 +9383,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="837" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A837" s="18" t="s">
         <v>120</v>
       </c>
@@ -9457,7 +9391,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="838" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A838" s="18" t="s">
         <v>121</v>
       </c>
@@ -9465,7 +9399,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="839" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A839" s="18" t="s">
         <v>122</v>
       </c>
@@ -9473,7 +9407,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="840" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A840" s="18" t="s">
         <v>123</v>
       </c>
@@ -9481,7 +9415,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="841" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A841" s="18" t="s">
         <v>124</v>
       </c>
@@ -9489,7 +9423,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="842" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A842" s="18" t="s">
         <v>125</v>
       </c>
@@ -9497,7 +9431,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="843" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A843" s="18" t="s">
         <v>126</v>
       </c>
@@ -9505,7 +9439,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="844" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A844" s="18" t="s">
         <v>127</v>
       </c>
@@ -9513,7 +9447,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="845" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A845" s="18" t="s">
         <v>128</v>
       </c>
@@ -9521,7 +9455,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="846" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A846" s="18" t="s">
         <v>129</v>
       </c>
@@ -9529,7 +9463,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="847" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A847" s="18" t="s">
         <v>130</v>
       </c>
@@ -9537,7 +9471,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="848" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A848" s="18" t="s">
         <v>131</v>
       </c>
@@ -9545,7 +9479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="849" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A849" s="18" t="s">
         <v>132</v>
       </c>
@@ -9553,7 +9487,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="850" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A850" s="18" t="s">
         <v>133</v>
       </c>
@@ -9561,7 +9495,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="851" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A851" s="18" t="s">
         <v>134</v>
       </c>
@@ -9569,7 +9503,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="852" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A852" s="18" t="s">
         <v>135</v>
       </c>
@@ -9577,7 +9511,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="853" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A853" s="18" t="s">
         <v>136</v>
       </c>
@@ -9585,7 +9519,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="854" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A854" s="18" t="s">
         <v>137</v>
       </c>
@@ -9593,7 +9527,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="855" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A855" s="18" t="s">
         <v>138</v>
       </c>
@@ -9601,7 +9535,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="856" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A856" s="18" t="s">
         <v>139</v>
       </c>
@@ -9609,7 +9543,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="857" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A857" s="18" t="s">
         <v>140</v>
       </c>
@@ -9617,7 +9551,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="858" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A858" s="18" t="s">
         <v>141</v>
       </c>
@@ -9625,7 +9559,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="859" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A859" s="18" t="s">
         <v>142</v>
       </c>
@@ -9633,7 +9567,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="860" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A860" s="18" t="s">
         <v>183</v>
       </c>
@@ -9641,7 +9575,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="861" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A861" s="18" t="s">
         <v>143</v>
       </c>
@@ -9649,7 +9583,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="862" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A862" s="18" t="s">
         <v>144</v>
       </c>
@@ -9657,7 +9591,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="863" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A863" s="23" t="s">
         <v>184</v>
       </c>
@@ -9665,7 +9599,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="864" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A864" s="18" t="s">
         <v>145</v>
       </c>
@@ -9673,7 +9607,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="865" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A865" s="18" t="s">
         <v>146</v>
       </c>
@@ -9681,7 +9615,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="866" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A866" s="18" t="s">
         <v>147</v>
       </c>
@@ -9689,7 +9623,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="867" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A867" s="18" t="s">
         <v>148</v>
       </c>
@@ -9697,7 +9631,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="868" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A868" s="18" t="s">
         <v>149</v>
       </c>
@@ -9705,7 +9639,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="869" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A869" s="18" t="s">
         <v>150</v>
       </c>
@@ -9713,7 +9647,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="870" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A870" s="18" t="s">
         <v>151</v>
       </c>
@@ -9721,7 +9655,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="871" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A871" s="18" t="s">
         <v>152</v>
       </c>
@@ -9729,7 +9663,7 @@
         <v>809</v>
       </c>
     </row>
-    <row r="872" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A872" s="18" t="s">
         <v>153</v>
       </c>
@@ -9737,7 +9671,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="873" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A873" s="18" t="s">
         <v>154</v>
       </c>
@@ -9745,7 +9679,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="874" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A874" s="18" t="s">
         <v>155</v>
       </c>
@@ -9753,7 +9687,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="875" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A875" s="18" t="s">
         <v>156</v>
       </c>
@@ -9761,7 +9695,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="876" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A876" s="18" t="s">
         <v>157</v>
       </c>
@@ -9769,7 +9703,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="877" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A877" s="18" t="s">
         <v>158</v>
       </c>
@@ -9777,7 +9711,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="878" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A878" s="18" t="s">
         <v>159</v>
       </c>
@@ -9785,7 +9719,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="879" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A879" s="18" t="s">
         <v>160</v>
       </c>
@@ -9793,7 +9727,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="880" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A880" s="18" t="s">
         <v>161</v>
       </c>
@@ -9801,7 +9735,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="881" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A881" s="18" t="s">
         <v>162</v>
       </c>
@@ -9809,7 +9743,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="882" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A882" s="18" t="s">
         <v>163</v>
       </c>
@@ -9817,7 +9751,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="883" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A883" s="18" t="s">
         <v>164</v>
       </c>
@@ -9825,7 +9759,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="884" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A884" s="18" t="s">
         <v>165</v>
       </c>
@@ -9833,7 +9767,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="885" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A885" s="18" t="s">
         <v>166</v>
       </c>
@@ -9841,7 +9775,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="886" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A886" s="18" t="s">
         <v>167</v>
       </c>
@@ -9849,7 +9783,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="887" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A887" s="18" t="s">
         <v>168</v>
       </c>
@@ -9857,7 +9791,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="888" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A888" s="18" t="s">
         <v>169</v>
       </c>
@@ -9865,7 +9799,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="889" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A889" s="18" t="s">
         <v>170</v>
       </c>
@@ -9873,7 +9807,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="890" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A890" s="18" t="s">
         <v>171</v>
       </c>
@@ -9881,7 +9815,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="891" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A891" s="18" t="s">
         <v>172</v>
       </c>
@@ -9889,7 +9823,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="892" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A892" s="18" t="s">
         <v>173</v>
       </c>
@@ -9897,7 +9831,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="893" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A893" s="18" t="s">
         <v>174</v>
       </c>
@@ -9905,7 +9839,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="894" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A894" s="18" t="s">
         <v>175</v>
       </c>
@@ -9913,7 +9847,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="895" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A895" s="18" t="s">
         <v>185</v>
       </c>
@@ -9921,7 +9855,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="896" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A896" s="18" t="s">
         <v>176</v>
       </c>
@@ -9929,7 +9863,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="897" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A897" s="18" t="s">
         <v>177</v>
       </c>
@@ -9937,7 +9871,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="898" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A898" s="18" t="s">
         <v>178</v>
       </c>
@@ -9945,7 +9879,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="899" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A899" s="18" t="s">
         <v>186</v>
       </c>
@@ -9953,7 +9887,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="900" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A900" s="18" t="s">
         <v>179</v>
       </c>
@@ -9961,7 +9895,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="901" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A901" s="18" t="s">
         <v>180</v>
       </c>
@@ -9969,7 +9903,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="902" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A902" s="18" t="s">
         <v>181</v>
       </c>
@@ -9977,7 +9911,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="903" spans="1:2" ht="13.8" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A903" s="18" t="s">
         <v>182</v>
       </c>
